--- a/Week_8/Capstone Timesheet_Ripal Patel.xlsx
+++ b/Week_8/Capstone Timesheet_Ripal Patel.xlsx
@@ -1,25 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Humber\Semester 3\Capstone Project\HealthCare Plus\Week_8\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="8380"/>
-  </bookViews>
   <sheets>
-    <sheet name="HTTP-5310- Capstone_Timesheet" sheetId="1" r:id="rId1"/>
+    <sheet state="visible" name="HTTP-5310- Capstone_Timesheet" sheetId="1" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <definedNames/>
+  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="75">
   <si>
     <t>Week_1</t>
   </si>
@@ -233,61 +225,73 @@
   <si>
     <t>Create Health Record UI</t>
   </si>
+  <si>
+    <t>Create Find-Dotcor Page UI</t>
+  </si>
+  <si>
+    <t>Create Services Page UI</t>
+  </si>
+  <si>
+    <t>Create Book-appointment Form UI</t>
+  </si>
+  <si>
+    <t>Create Contact US Page UI</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="dd\-mmm"/>
-    <numFmt numFmtId="165" formatCode="d\-mmm"/>
+    <numFmt numFmtId="164" formatCode="dd-mmm"/>
+    <numFmt numFmtId="165" formatCode="d-mmm"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="14"/>
+      <sz val="14.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="14"/>
+      <sz val="14.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="14"/>
+      <sz val="14.0"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="14"/>
+      <sz val="14.0"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="12.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="12.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="12.0"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="12.0"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
@@ -297,7 +301,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -361,13 +365,7 @@
     </fill>
   </fills>
   <borders count="3">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -381,214 +379,247 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="77">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+  <cellXfs count="78">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf borderId="1" fillId="4" fontId="2" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf borderId="1" fillId="4" fontId="2" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf borderId="1" fillId="4" fontId="2" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="6" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf borderId="1" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="1" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="1" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="1" fillId="6" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf borderId="1" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf borderId="2" fillId="6" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf borderId="1" fillId="6" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="1" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="1" fillId="6" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="1" fillId="6" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf borderId="1" fillId="7" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="6" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf borderId="1" fillId="7" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf borderId="1" fillId="7" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="2" fillId="7" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="1" fillId="7" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="1" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf borderId="1" fillId="8" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="165" fontId="6" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf borderId="1" fillId="8" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf borderId="1" fillId="8" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf borderId="1" fillId="9" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="1" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="1" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="2" fillId="9" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf borderId="1" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf borderId="1" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf borderId="1" fillId="9" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf borderId="1" fillId="9" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="1" fillId="10" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="1" fillId="10" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf borderId="1" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf borderId="1" fillId="10" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf borderId="1" fillId="10" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf borderId="1" fillId="10" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="10" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="10" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="10" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="11" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="11" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="11" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="11" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="11" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="11" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="11" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="11" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="11" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="11" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="11" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="11" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="11" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="9" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="9" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="9" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="9" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="9" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="9" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="9" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -596,7 +627,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -786,26 +817,23 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AA958"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="62.26953125" customWidth="1"/>
-    <col min="3" max="3" width="12.26953125" customWidth="1"/>
-    <col min="4" max="4" width="12.08984375" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="10.0"/>
+    <col customWidth="1" min="2" max="2" width="62.25"/>
+    <col customWidth="1" min="3" max="3" width="12.25"/>
+    <col customWidth="1" min="4" max="4" width="12.13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -842,13 +870,13 @@
       <c r="Z1" s="3"/>
       <c r="AA1" s="3"/>
     </row>
-    <row r="2" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2">
       <c r="A2" s="4"/>
       <c r="B2" s="4" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="5">
-        <v>46037</v>
+        <v>46037.0</v>
       </c>
       <c r="D2" s="6">
         <v>1.3</v>
@@ -877,13 +905,13 @@
       <c r="Z2" s="3"/>
       <c r="AA2" s="3"/>
     </row>
-    <row r="3" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3">
       <c r="A3" s="4"/>
       <c r="B3" s="4" t="s">
         <v>5</v>
       </c>
       <c r="C3" s="5">
-        <v>46037</v>
+        <v>46037.0</v>
       </c>
       <c r="D3" s="6">
         <v>0.15</v>
@@ -912,16 +940,16 @@
       <c r="Z3" s="3"/>
       <c r="AA3" s="3"/>
     </row>
-    <row r="4" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4">
       <c r="A4" s="4"/>
       <c r="B4" s="4" t="s">
         <v>6</v>
       </c>
       <c r="C4" s="5">
-        <v>46037</v>
+        <v>46037.0</v>
       </c>
       <c r="D4" s="4">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
@@ -947,16 +975,16 @@
       <c r="Z4" s="3"/>
       <c r="AA4" s="3"/>
     </row>
-    <row r="5" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5">
       <c r="A5" s="4"/>
       <c r="B5" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="5">
-        <v>46037</v>
+        <v>46037.0</v>
       </c>
       <c r="D5" s="4">
-        <v>1.1499999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
@@ -982,13 +1010,13 @@
       <c r="Z5" s="3"/>
       <c r="AA5" s="3"/>
     </row>
-    <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6">
       <c r="A6" s="4"/>
       <c r="B6" s="4" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="5">
-        <v>46038</v>
+        <v>46038.0</v>
       </c>
       <c r="D6" s="4">
         <v>4.75</v>
@@ -1017,13 +1045,13 @@
       <c r="Z6" s="3"/>
       <c r="AA6" s="3"/>
     </row>
-    <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>46038</v>
+        <v>46038.0</v>
       </c>
       <c r="D7" s="4">
         <v>3.5</v>
@@ -1052,13 +1080,13 @@
       <c r="Z7" s="3"/>
       <c r="AA7" s="3"/>
     </row>
-    <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
         <v>10</v>
       </c>
       <c r="C8" s="5">
-        <v>46038</v>
+        <v>46038.0</v>
       </c>
       <c r="D8" s="4">
         <v>5.75</v>
@@ -1087,16 +1115,16 @@
       <c r="Z8" s="3"/>
       <c r="AA8" s="3"/>
     </row>
-    <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C9" s="5">
-        <v>46039</v>
+        <v>46039.0</v>
       </c>
       <c r="D9" s="4">
-        <v>5</v>
+        <v>5.0</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
@@ -1122,13 +1150,13 @@
       <c r="Z9" s="3"/>
       <c r="AA9" s="3"/>
     </row>
-    <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C10" s="5">
-        <v>46039</v>
+        <v>46039.0</v>
       </c>
       <c r="D10" s="4">
         <v>5.5</v>
@@ -1157,13 +1185,13 @@
       <c r="Z10" s="3"/>
       <c r="AA10" s="3"/>
     </row>
-    <row r="11" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11">
       <c r="A11" s="4"/>
       <c r="B11" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C11" s="5">
-        <v>46041</v>
+        <v>46041.0</v>
       </c>
       <c r="D11" s="4">
         <v>4.75</v>
@@ -1192,13 +1220,13 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
     </row>
-    <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12">
       <c r="A12" s="4"/>
       <c r="B12" s="4" t="s">
         <v>14</v>
       </c>
       <c r="C12" s="5">
-        <v>46043</v>
+        <v>46043.0</v>
       </c>
       <c r="D12" s="4">
         <v>4.75</v>
@@ -1227,7 +1255,7 @@
       <c r="Z12" s="3"/>
       <c r="AA12" s="3"/>
     </row>
-    <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="5"/>
@@ -1256,14 +1284,14 @@
       <c r="Z13" s="3"/>
       <c r="AA13" s="3"/>
     </row>
-    <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14">
       <c r="A14" s="7"/>
       <c r="B14" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="7">
-        <f>SUM(D2:D12)</f>
+        <f>sum(D2:D12)</f>
         <v>38.6</v>
       </c>
       <c r="E14" s="2"/>
@@ -1290,7 +1318,7 @@
       <c r="Z14" s="3"/>
       <c r="AA14" s="3"/>
     </row>
-    <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -1319,7 +1347,7 @@
       <c r="Z15" s="3"/>
       <c r="AA15" s="3"/>
     </row>
-    <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -1348,7 +1376,7 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
     </row>
-    <row r="17" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17">
       <c r="A17" s="9" t="s">
         <v>16</v>
       </c>
@@ -1385,13 +1413,13 @@
       <c r="Z17" s="3"/>
       <c r="AA17" s="3"/>
     </row>
-    <row r="18" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18">
       <c r="A18" s="10"/>
       <c r="B18" s="11" t="s">
         <v>17</v>
       </c>
       <c r="C18" s="12">
-        <v>46044</v>
+        <v>46044.0</v>
       </c>
       <c r="D18" s="13">
         <v>1.5</v>
@@ -1420,16 +1448,16 @@
       <c r="Z18" s="3"/>
       <c r="AA18" s="3"/>
     </row>
-    <row r="19" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19">
       <c r="A19" s="10"/>
       <c r="B19" s="11" t="s">
         <v>18</v>
       </c>
       <c r="C19" s="12">
-        <v>46044</v>
+        <v>46044.0</v>
       </c>
       <c r="D19" s="13">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
@@ -1455,16 +1483,16 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
     </row>
-    <row r="20" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20">
       <c r="A20" s="10"/>
       <c r="B20" s="11" t="s">
         <v>19</v>
       </c>
       <c r="C20" s="12">
-        <v>46044</v>
+        <v>46044.0</v>
       </c>
       <c r="D20" s="13">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
@@ -1490,16 +1518,16 @@
       <c r="Z20" s="3"/>
       <c r="AA20" s="3"/>
     </row>
-    <row r="21" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21">
       <c r="A21" s="10"/>
       <c r="B21" s="11" t="s">
         <v>20</v>
       </c>
       <c r="C21" s="12">
-        <v>46045</v>
+        <v>46045.0</v>
       </c>
       <c r="D21" s="13">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
@@ -1525,16 +1553,16 @@
       <c r="Z21" s="3"/>
       <c r="AA21" s="3"/>
     </row>
-    <row r="22" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22">
       <c r="A22" s="10"/>
       <c r="B22" s="11" t="s">
         <v>21</v>
       </c>
       <c r="C22" s="12">
-        <v>46045</v>
+        <v>46045.0</v>
       </c>
       <c r="D22" s="13">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
@@ -1560,13 +1588,13 @@
       <c r="Z22" s="3"/>
       <c r="AA22" s="3"/>
     </row>
-    <row r="23" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23">
       <c r="A23" s="10"/>
       <c r="B23" s="11" t="s">
         <v>22</v>
       </c>
       <c r="C23" s="12">
-        <v>46046</v>
+        <v>46046.0</v>
       </c>
       <c r="D23" s="13">
         <v>1.5</v>
@@ -1595,13 +1623,13 @@
       <c r="Z23" s="3"/>
       <c r="AA23" s="3"/>
     </row>
-    <row r="24" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24">
       <c r="A24" s="10"/>
       <c r="B24" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C24" s="12">
-        <v>46046</v>
+        <v>46046.0</v>
       </c>
       <c r="D24" s="13">
         <v>2.5</v>
@@ -1630,16 +1658,16 @@
       <c r="Z24" s="3"/>
       <c r="AA24" s="3"/>
     </row>
-    <row r="25" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25">
       <c r="A25" s="10"/>
       <c r="B25" s="11" t="s">
         <v>24</v>
       </c>
       <c r="C25" s="12">
-        <v>46046</v>
+        <v>46046.0</v>
       </c>
       <c r="D25" s="13">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
@@ -1665,13 +1693,13 @@
       <c r="Z25" s="3"/>
       <c r="AA25" s="3"/>
     </row>
-    <row r="26" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26">
       <c r="A26" s="10"/>
       <c r="B26" s="11" t="s">
         <v>25</v>
       </c>
       <c r="C26" s="12">
-        <v>46047</v>
+        <v>46047.0</v>
       </c>
       <c r="D26" s="13">
         <v>1.75</v>
@@ -1700,16 +1728,16 @@
       <c r="Z26" s="3"/>
       <c r="AA26" s="3"/>
     </row>
-    <row r="27" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="27">
       <c r="A27" s="10"/>
       <c r="B27" s="11" t="s">
         <v>26</v>
       </c>
       <c r="C27" s="12">
-        <v>46047</v>
+        <v>46047.0</v>
       </c>
       <c r="D27" s="13">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
@@ -1735,13 +1763,13 @@
       <c r="Z27" s="3"/>
       <c r="AA27" s="3"/>
     </row>
-    <row r="28" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="28">
       <c r="A28" s="10"/>
       <c r="B28" s="11" t="s">
         <v>27</v>
       </c>
       <c r="C28" s="12">
-        <v>46047</v>
+        <v>46047.0</v>
       </c>
       <c r="D28" s="13">
         <v>2.75</v>
@@ -1770,16 +1798,16 @@
       <c r="Z28" s="3"/>
       <c r="AA28" s="3"/>
     </row>
-    <row r="29" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="29">
       <c r="A29" s="14"/>
       <c r="B29" s="15" t="s">
         <v>28</v>
       </c>
       <c r="C29" s="16">
-        <v>46048</v>
+        <v>46048.0</v>
       </c>
       <c r="D29" s="17">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
@@ -1805,16 +1833,16 @@
       <c r="Z29" s="3"/>
       <c r="AA29" s="3"/>
     </row>
-    <row r="30" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="30">
       <c r="A30" s="14"/>
       <c r="B30" s="15" t="s">
         <v>29</v>
       </c>
       <c r="C30" s="16">
-        <v>46048</v>
+        <v>46048.0</v>
       </c>
       <c r="D30" s="17">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
@@ -1840,16 +1868,16 @@
       <c r="Z30" s="3"/>
       <c r="AA30" s="3"/>
     </row>
-    <row r="31" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="31">
       <c r="A31" s="14"/>
       <c r="B31" s="15" t="s">
         <v>30</v>
       </c>
       <c r="C31" s="16">
-        <v>46048</v>
+        <v>46048.0</v>
       </c>
       <c r="D31" s="17">
-        <v>1.1499999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
@@ -1875,13 +1903,13 @@
       <c r="Z31" s="3"/>
       <c r="AA31" s="3"/>
     </row>
-    <row r="32" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="32">
       <c r="A32" s="14"/>
       <c r="B32" s="15" t="s">
         <v>31</v>
       </c>
       <c r="C32" s="16">
-        <v>46049</v>
+        <v>46049.0</v>
       </c>
       <c r="D32" s="17">
         <v>2.5</v>
@@ -1910,13 +1938,13 @@
       <c r="Z32" s="3"/>
       <c r="AA32" s="3"/>
     </row>
-    <row r="33" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="33">
       <c r="A33" s="14"/>
       <c r="B33" s="18" t="s">
         <v>32</v>
       </c>
       <c r="C33" s="19">
-        <v>46049</v>
+        <v>46049.0</v>
       </c>
       <c r="D33" s="20">
         <v>3.75</v>
@@ -1945,14 +1973,14 @@
       <c r="Z33" s="3"/>
       <c r="AA33" s="3"/>
     </row>
-    <row r="34" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="34">
       <c r="A34" s="21"/>
       <c r="B34" s="21" t="s">
         <v>15</v>
       </c>
       <c r="C34" s="22"/>
       <c r="D34" s="21">
-        <f>SUM(D18:D33)</f>
+        <f>sum(D18:D33)</f>
         <v>33.4</v>
       </c>
       <c r="E34" s="2"/>
@@ -1979,7 +2007,7 @@
       <c r="Z34" s="3"/>
       <c r="AA34" s="3"/>
     </row>
-    <row r="35" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="35">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -2008,7 +2036,7 @@
       <c r="Z35" s="3"/>
       <c r="AA35" s="3"/>
     </row>
-    <row r="36" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="36">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -2037,7 +2065,7 @@
       <c r="Z36" s="3"/>
       <c r="AA36" s="3"/>
     </row>
-    <row r="37" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="37">
       <c r="A37" s="23" t="s">
         <v>33</v>
       </c>
@@ -2074,13 +2102,13 @@
       <c r="Z37" s="3"/>
       <c r="AA37" s="3"/>
     </row>
-    <row r="38" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="38">
       <c r="A38" s="24"/>
       <c r="B38" s="25" t="s">
         <v>34</v>
       </c>
       <c r="C38" s="26">
-        <v>46052</v>
+        <v>46052.0</v>
       </c>
       <c r="D38" s="27">
         <v>1.5</v>
@@ -2109,13 +2137,13 @@
       <c r="Z38" s="3"/>
       <c r="AA38" s="3"/>
     </row>
-    <row r="39" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="39">
       <c r="A39" s="24"/>
       <c r="B39" s="25" t="s">
         <v>35</v>
       </c>
       <c r="C39" s="26">
-        <v>46052</v>
+        <v>46052.0</v>
       </c>
       <c r="D39" s="27">
         <v>1.75</v>
@@ -2144,13 +2172,13 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
     </row>
-    <row r="40" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="40">
       <c r="A40" s="24"/>
       <c r="B40" s="25" t="s">
         <v>36</v>
       </c>
       <c r="C40" s="26">
-        <v>46052</v>
+        <v>46052.0</v>
       </c>
       <c r="D40" s="27">
         <v>2.15</v>
@@ -2179,13 +2207,13 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
     </row>
-    <row r="41" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="41">
       <c r="A41" s="24"/>
       <c r="B41" s="25" t="s">
         <v>37</v>
       </c>
       <c r="C41" s="26">
-        <v>46054</v>
+        <v>46054.0</v>
       </c>
       <c r="D41" s="27">
         <v>2.75</v>
@@ -2214,13 +2242,13 @@
       <c r="Z41" s="3"/>
       <c r="AA41" s="3"/>
     </row>
-    <row r="42" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="42">
       <c r="A42" s="24"/>
       <c r="B42" s="25" t="s">
         <v>38</v>
       </c>
       <c r="C42" s="26">
-        <v>46055</v>
+        <v>46055.0</v>
       </c>
       <c r="D42" s="27">
         <v>3.75</v>
@@ -2249,7 +2277,7 @@
       <c r="Z42" s="3"/>
       <c r="AA42" s="3"/>
     </row>
-    <row r="43" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="43">
       <c r="A43" s="3"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
@@ -2278,14 +2306,14 @@
       <c r="Z43" s="3"/>
       <c r="AA43" s="3"/>
     </row>
-    <row r="44" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="44">
       <c r="A44" s="28"/>
       <c r="B44" s="29" t="s">
         <v>15</v>
       </c>
       <c r="C44" s="30"/>
       <c r="D44" s="24">
-        <f>SUM(D38:D42)</f>
+        <f>sum(D38:D42)</f>
         <v>11.9</v>
       </c>
       <c r="E44" s="3"/>
@@ -2312,7 +2340,7 @@
       <c r="Z44" s="3"/>
       <c r="AA44" s="3"/>
     </row>
-    <row r="45" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="45">
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -2341,7 +2369,7 @@
       <c r="Z45" s="3"/>
       <c r="AA45" s="3"/>
     </row>
-    <row r="46" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="46">
       <c r="A46" s="3"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
@@ -2370,7 +2398,7 @@
       <c r="Z46" s="3"/>
       <c r="AA46" s="3"/>
     </row>
-    <row r="47" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="47">
       <c r="A47" s="31" t="s">
         <v>39</v>
       </c>
@@ -2407,13 +2435,13 @@
       <c r="Z47" s="3"/>
       <c r="AA47" s="3"/>
     </row>
-    <row r="48" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="48">
       <c r="A48" s="32"/>
       <c r="B48" s="33" t="s">
         <v>40</v>
       </c>
       <c r="C48" s="34">
-        <v>46059</v>
+        <v>46059.0</v>
       </c>
       <c r="D48" s="35">
         <v>3.75</v>
@@ -2442,13 +2470,13 @@
       <c r="Z48" s="3"/>
       <c r="AA48" s="3"/>
     </row>
-    <row r="49" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="49">
       <c r="A49" s="32"/>
       <c r="B49" s="33" t="s">
         <v>41</v>
       </c>
       <c r="C49" s="34">
-        <v>46061</v>
+        <v>46061.0</v>
       </c>
       <c r="D49" s="35">
         <v>3.25</v>
@@ -2477,13 +2505,13 @@
       <c r="Z49" s="3"/>
       <c r="AA49" s="3"/>
     </row>
-    <row r="50" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="50">
       <c r="A50" s="32"/>
       <c r="B50" s="33" t="s">
         <v>42</v>
       </c>
       <c r="C50" s="34">
-        <v>46061</v>
+        <v>46061.0</v>
       </c>
       <c r="D50" s="35">
         <v>4.5</v>
@@ -2512,13 +2540,13 @@
       <c r="Z50" s="3"/>
       <c r="AA50" s="3"/>
     </row>
-    <row r="51" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="51">
       <c r="A51" s="32"/>
       <c r="B51" s="33" t="s">
         <v>43</v>
       </c>
       <c r="C51" s="34">
-        <v>46062</v>
+        <v>46062.0</v>
       </c>
       <c r="D51" s="35">
         <v>3.75</v>
@@ -2547,13 +2575,13 @@
       <c r="Z51" s="3"/>
       <c r="AA51" s="3"/>
     </row>
-    <row r="52" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="52">
       <c r="A52" s="32"/>
       <c r="B52" s="33" t="s">
         <v>44</v>
       </c>
       <c r="C52" s="34">
-        <v>46063</v>
+        <v>46063.0</v>
       </c>
       <c r="D52" s="35">
         <v>3.5</v>
@@ -2582,7 +2610,7 @@
       <c r="Z52" s="3"/>
       <c r="AA52" s="3"/>
     </row>
-    <row r="53" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="53">
       <c r="A53" s="3"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
@@ -2611,14 +2639,14 @@
       <c r="Z53" s="3"/>
       <c r="AA53" s="3"/>
     </row>
-    <row r="54" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="54">
       <c r="A54" s="36"/>
       <c r="B54" s="37" t="s">
         <v>15</v>
       </c>
       <c r="C54" s="38"/>
       <c r="D54" s="39">
-        <f>SUM(D48:D52)</f>
+        <f>sum(D48:D52)</f>
         <v>18.75</v>
       </c>
       <c r="E54" s="3"/>
@@ -2645,7 +2673,7 @@
       <c r="Z54" s="3"/>
       <c r="AA54" s="3"/>
     </row>
-    <row r="55" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="55">
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -2674,7 +2702,7 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
     </row>
-    <row r="56" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="56">
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
@@ -2703,7 +2731,7 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
     </row>
-    <row r="57" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="57">
       <c r="A57" s="40" t="s">
         <v>45</v>
       </c>
@@ -2740,13 +2768,13 @@
       <c r="Z57" s="3"/>
       <c r="AA57" s="3"/>
     </row>
-    <row r="58" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="58">
       <c r="A58" s="41"/>
       <c r="B58" s="42" t="s">
         <v>46</v>
       </c>
       <c r="C58" s="43">
-        <v>46066</v>
+        <v>46066.0</v>
       </c>
       <c r="D58" s="44">
         <v>2.15</v>
@@ -2775,13 +2803,13 @@
       <c r="Z58" s="3"/>
       <c r="AA58" s="3"/>
     </row>
-    <row r="59" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="59">
       <c r="A59" s="41"/>
       <c r="B59" s="42" t="s">
         <v>47</v>
       </c>
       <c r="C59" s="43">
-        <v>46066</v>
+        <v>46066.0</v>
       </c>
       <c r="D59" s="44">
         <v>3.75</v>
@@ -2810,13 +2838,13 @@
       <c r="Z59" s="3"/>
       <c r="AA59" s="3"/>
     </row>
-    <row r="60" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="60">
       <c r="A60" s="41"/>
       <c r="B60" s="42" t="s">
         <v>48</v>
       </c>
       <c r="C60" s="43">
-        <v>46069</v>
+        <v>46069.0</v>
       </c>
       <c r="D60" s="44">
         <v>3.5</v>
@@ -2845,13 +2873,13 @@
       <c r="Z60" s="3"/>
       <c r="AA60" s="3"/>
     </row>
-    <row r="61" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="61">
       <c r="A61" s="41"/>
       <c r="B61" s="42" t="s">
         <v>49</v>
       </c>
       <c r="C61" s="43">
-        <v>46069</v>
+        <v>46069.0</v>
       </c>
       <c r="D61" s="44">
         <v>2.5</v>
@@ -2880,7 +2908,7 @@
       <c r="Z61" s="3"/>
       <c r="AA61" s="3"/>
     </row>
-    <row r="62" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="62">
       <c r="A62" s="3"/>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
@@ -2909,14 +2937,14 @@
       <c r="Z62" s="3"/>
       <c r="AA62" s="3"/>
     </row>
-    <row r="63" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="63">
       <c r="A63" s="45"/>
       <c r="B63" s="46" t="s">
         <v>15</v>
       </c>
       <c r="C63" s="47"/>
       <c r="D63" s="41">
-        <f>SUM(D58:D61)</f>
+        <f>sum(D58:D61)</f>
         <v>11.9</v>
       </c>
       <c r="E63" s="3"/>
@@ -2943,7 +2971,7 @@
       <c r="Z63" s="3"/>
       <c r="AA63" s="3"/>
     </row>
-    <row r="64" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="64">
       <c r="A64" s="3"/>
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
@@ -2972,7 +3000,7 @@
       <c r="Z64" s="3"/>
       <c r="AA64" s="3"/>
     </row>
-    <row r="65" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="65">
       <c r="A65" s="3"/>
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
@@ -3001,7 +3029,7 @@
       <c r="Z65" s="3"/>
       <c r="AA65" s="3"/>
     </row>
-    <row r="66" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="66">
       <c r="A66" s="48" t="s">
         <v>50</v>
       </c>
@@ -3038,13 +3066,13 @@
       <c r="Z66" s="3"/>
       <c r="AA66" s="3"/>
     </row>
-    <row r="67" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="67">
       <c r="A67" s="49"/>
       <c r="B67" s="50" t="s">
         <v>51</v>
       </c>
       <c r="C67" s="51">
-        <v>46073</v>
+        <v>46073.0</v>
       </c>
       <c r="D67" s="52">
         <v>1.75</v>
@@ -3073,16 +3101,16 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
     </row>
-    <row r="68" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="68">
       <c r="A68" s="49"/>
       <c r="B68" s="50" t="s">
         <v>52</v>
       </c>
       <c r="C68" s="51">
-        <v>46074</v>
+        <v>46074.0</v>
       </c>
       <c r="D68" s="52">
-        <v>2</v>
+        <v>2.0</v>
       </c>
       <c r="E68" s="3"/>
       <c r="G68" s="3"/>
@@ -3107,13 +3135,13 @@
       <c r="Z68" s="3"/>
       <c r="AA68" s="3"/>
     </row>
-    <row r="69" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="69">
       <c r="A69" s="49"/>
       <c r="B69" s="50" t="s">
         <v>53</v>
       </c>
       <c r="C69" s="51">
-        <v>46075</v>
+        <v>46075.0</v>
       </c>
       <c r="D69" s="52">
         <v>0.25</v>
@@ -3142,13 +3170,13 @@
       <c r="Z69" s="3"/>
       <c r="AA69" s="3"/>
     </row>
-    <row r="70" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="70">
       <c r="A70" s="49"/>
       <c r="B70" s="50" t="s">
         <v>54</v>
       </c>
       <c r="C70" s="51">
-        <v>46076</v>
+        <v>46076.0</v>
       </c>
       <c r="D70" s="52">
         <v>1.75</v>
@@ -3177,13 +3205,13 @@
       <c r="Z70" s="3"/>
       <c r="AA70" s="3"/>
     </row>
-    <row r="71" spans="1:27" ht="62" x14ac:dyDescent="0.35">
+    <row r="71">
       <c r="A71" s="49"/>
       <c r="B71" s="53" t="s">
         <v>55</v>
       </c>
       <c r="C71" s="51">
-        <v>46076</v>
+        <v>46076.0</v>
       </c>
       <c r="D71" s="52">
         <v>3.75</v>
@@ -3212,7 +3240,7 @@
       <c r="Z71" s="3"/>
       <c r="AA71" s="3"/>
     </row>
-    <row r="72" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="72">
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
@@ -3241,14 +3269,14 @@
       <c r="Z72" s="3"/>
       <c r="AA72" s="3"/>
     </row>
-    <row r="73" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="73">
       <c r="A73" s="54"/>
       <c r="B73" s="55" t="s">
         <v>15</v>
       </c>
       <c r="C73" s="56"/>
       <c r="D73" s="49">
-        <f>SUM(D67:D71)</f>
+        <f>sum(D67:D71)</f>
         <v>9.5</v>
       </c>
       <c r="E73" s="3"/>
@@ -3275,7 +3303,7 @@
       <c r="Z73" s="3"/>
       <c r="AA73" s="3"/>
     </row>
-    <row r="74" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="74">
       <c r="A74" s="3"/>
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
@@ -3304,7 +3332,7 @@
       <c r="Z74" s="3"/>
       <c r="AA74" s="3"/>
     </row>
-    <row r="75" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="75">
       <c r="A75" s="3"/>
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
@@ -3333,7 +3361,7 @@
       <c r="Z75" s="3"/>
       <c r="AA75" s="3"/>
     </row>
-    <row r="76" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="76">
       <c r="A76" s="57" t="s">
         <v>56</v>
       </c>
@@ -3370,13 +3398,13 @@
       <c r="Z76" s="3"/>
       <c r="AA76" s="3"/>
     </row>
-    <row r="77" spans="1:27" ht="62" x14ac:dyDescent="0.35">
+    <row r="77">
       <c r="A77" s="58"/>
       <c r="B77" s="59" t="s">
         <v>57</v>
       </c>
       <c r="C77" s="60">
-        <v>46080</v>
+        <v>46080.0</v>
       </c>
       <c r="D77" s="61">
         <v>3.75</v>
@@ -3405,13 +3433,13 @@
       <c r="Z77" s="3"/>
       <c r="AA77" s="3"/>
     </row>
-    <row r="78" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="78">
       <c r="A78" s="58"/>
       <c r="B78" s="62" t="s">
         <v>58</v>
       </c>
       <c r="C78" s="60">
-        <v>46081</v>
+        <v>46081.0</v>
       </c>
       <c r="D78" s="61">
         <v>1.75</v>
@@ -3440,13 +3468,13 @@
       <c r="Z78" s="3"/>
       <c r="AA78" s="3"/>
     </row>
-    <row r="79" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="79">
       <c r="A79" s="58"/>
       <c r="B79" s="62" t="s">
         <v>59</v>
       </c>
       <c r="C79" s="60">
-        <v>46081</v>
+        <v>46081.0</v>
       </c>
       <c r="D79" s="61">
         <v>2.15</v>
@@ -3475,13 +3503,13 @@
       <c r="Z79" s="3"/>
       <c r="AA79" s="3"/>
     </row>
-    <row r="80" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="80">
       <c r="A80" s="58"/>
       <c r="B80" s="62" t="s">
         <v>60</v>
       </c>
       <c r="C80" s="60">
-        <v>46081</v>
+        <v>46081.0</v>
       </c>
       <c r="D80" s="61">
         <v>0.45</v>
@@ -3510,13 +3538,13 @@
       <c r="Z80" s="3"/>
       <c r="AA80" s="3"/>
     </row>
-    <row r="81" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="81">
       <c r="A81" s="58"/>
       <c r="B81" s="59" t="s">
         <v>61</v>
       </c>
       <c r="C81" s="60">
-        <v>46082</v>
+        <v>46082.0</v>
       </c>
       <c r="D81" s="61">
         <v>2.5</v>
@@ -3545,13 +3573,13 @@
       <c r="Z81" s="3"/>
       <c r="AA81" s="3"/>
     </row>
-    <row r="82" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="82">
       <c r="A82" s="63"/>
       <c r="B82" s="64" t="s">
         <v>62</v>
       </c>
       <c r="C82" s="60">
-        <v>46083</v>
+        <v>46083.0</v>
       </c>
       <c r="D82" s="65">
         <v>3.75</v>
@@ -3580,13 +3608,13 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
     </row>
-    <row r="83" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="83">
       <c r="A83" s="63"/>
       <c r="B83" s="64" t="s">
         <v>63</v>
       </c>
       <c r="C83" s="60">
-        <v>46085</v>
+        <v>46085.0</v>
       </c>
       <c r="D83" s="65">
         <v>0.75</v>
@@ -3615,13 +3643,13 @@
       <c r="Z83" s="3"/>
       <c r="AA83" s="3"/>
     </row>
-    <row r="84" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="84">
       <c r="A84" s="63"/>
       <c r="B84" s="64" t="s">
         <v>64</v>
       </c>
       <c r="C84" s="60">
-        <v>46085</v>
+        <v>46085.0</v>
       </c>
       <c r="D84" s="65">
         <v>0.25</v>
@@ -3650,13 +3678,13 @@
       <c r="Z84" s="3"/>
       <c r="AA84" s="3"/>
     </row>
-    <row r="85" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="85">
       <c r="A85" s="63"/>
       <c r="B85" s="64" t="s">
         <v>65</v>
       </c>
       <c r="C85" s="60">
-        <v>46085</v>
+        <v>46085.0</v>
       </c>
       <c r="D85" s="65">
         <v>0.5</v>
@@ -3685,7 +3713,7 @@
       <c r="Z85" s="3"/>
       <c r="AA85" s="3"/>
     </row>
-    <row r="86" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="86">
       <c r="A86" s="66"/>
       <c r="B86" s="66"/>
       <c r="C86" s="66"/>
@@ -3714,14 +3742,14 @@
       <c r="Z86" s="3"/>
       <c r="AA86" s="3"/>
     </row>
-    <row r="87" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="87">
       <c r="A87" s="67"/>
       <c r="B87" s="68" t="s">
         <v>15</v>
       </c>
       <c r="C87" s="69"/>
       <c r="D87" s="58">
-        <f>SUM(D77:D82)</f>
+        <f>sum(D77:D82)</f>
         <v>14.35</v>
       </c>
       <c r="E87" s="3"/>
@@ -3748,7 +3776,7 @@
       <c r="Z87" s="3"/>
       <c r="AA87" s="3"/>
     </row>
-    <row r="88" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="88">
       <c r="A88" s="3"/>
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
@@ -3777,7 +3805,7 @@
       <c r="Z88" s="3"/>
       <c r="AA88" s="3"/>
     </row>
-    <row r="89" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="89">
       <c r="A89" s="3"/>
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
@@ -3806,7 +3834,7 @@
       <c r="Z89" s="3"/>
       <c r="AA89" s="3"/>
     </row>
-    <row r="90" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="90">
       <c r="A90" s="40" t="s">
         <v>66</v>
       </c>
@@ -3843,13 +3871,13 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
     </row>
-    <row r="91" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="91">
       <c r="A91" s="41"/>
       <c r="B91" s="70" t="s">
         <v>67</v>
       </c>
       <c r="C91" s="71">
-        <v>46087</v>
+        <v>46087.0</v>
       </c>
       <c r="D91" s="44">
         <v>1.75</v>
@@ -3878,13 +3906,13 @@
       <c r="Z91" s="3"/>
       <c r="AA91" s="3"/>
     </row>
-    <row r="92" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="92">
       <c r="A92" s="41"/>
       <c r="B92" s="72" t="s">
         <v>68</v>
       </c>
       <c r="C92" s="71">
-        <v>46087</v>
+        <v>46087.0</v>
       </c>
       <c r="D92" s="44">
         <v>2.5</v>
@@ -3913,13 +3941,13 @@
       <c r="Z92" s="3"/>
       <c r="AA92" s="3"/>
     </row>
-    <row r="93" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="93">
       <c r="A93" s="41"/>
       <c r="B93" s="72" t="s">
         <v>69</v>
       </c>
-      <c r="C93" s="71">
-        <v>46087</v>
+      <c r="C93" s="73">
+        <v>46087.0</v>
       </c>
       <c r="D93" s="44">
         <v>2.15</v>
@@ -3948,13 +3976,13 @@
       <c r="Z93" s="3"/>
       <c r="AA93" s="3"/>
     </row>
-    <row r="94" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="94">
       <c r="A94" s="41"/>
       <c r="B94" s="72" t="s">
         <v>70</v>
       </c>
-      <c r="C94" s="71">
-        <v>46087</v>
+      <c r="C94" s="73">
+        <v>46087.0</v>
       </c>
       <c r="D94" s="44">
         <v>2.75</v>
@@ -3983,11 +4011,17 @@
       <c r="Z94" s="3"/>
       <c r="AA94" s="3"/>
     </row>
-    <row r="95" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="95">
       <c r="A95" s="41"/>
-      <c r="B95" s="70"/>
-      <c r="C95" s="71"/>
-      <c r="D95" s="44"/>
+      <c r="B95" s="70" t="s">
+        <v>71</v>
+      </c>
+      <c r="C95" s="73">
+        <v>46088.0</v>
+      </c>
+      <c r="D95" s="44">
+        <v>2.0</v>
+      </c>
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
       <c r="G95" s="3"/>
@@ -4012,11 +4046,17 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
     </row>
-    <row r="96" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
-      <c r="A96" s="73"/>
-      <c r="B96" s="74"/>
-      <c r="C96" s="71"/>
-      <c r="D96" s="75"/>
+    <row r="96">
+      <c r="A96" s="74"/>
+      <c r="B96" s="70" t="s">
+        <v>72</v>
+      </c>
+      <c r="C96" s="73">
+        <v>46088.0</v>
+      </c>
+      <c r="D96" s="75">
+        <v>1.75</v>
+      </c>
       <c r="E96" s="3"/>
       <c r="F96" s="3"/>
       <c r="G96" s="3"/>
@@ -4041,11 +4081,17 @@
       <c r="Z96" s="3"/>
       <c r="AA96" s="3"/>
     </row>
-    <row r="97" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
-      <c r="A97" s="73"/>
-      <c r="B97" s="74"/>
-      <c r="C97" s="71"/>
-      <c r="D97" s="75"/>
+    <row r="97">
+      <c r="A97" s="74"/>
+      <c r="B97" s="70" t="s">
+        <v>73</v>
+      </c>
+      <c r="C97" s="73">
+        <v>46088.0</v>
+      </c>
+      <c r="D97" s="75">
+        <v>1.15</v>
+      </c>
       <c r="E97" s="3"/>
       <c r="F97" s="3"/>
       <c r="G97" s="3"/>
@@ -4070,11 +4116,17 @@
       <c r="Z97" s="3"/>
       <c r="AA97" s="3"/>
     </row>
-    <row r="98" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
-      <c r="A98" s="73"/>
-      <c r="B98" s="74"/>
-      <c r="C98" s="71"/>
-      <c r="D98" s="75"/>
+    <row r="98">
+      <c r="A98" s="74"/>
+      <c r="B98" s="70" t="s">
+        <v>74</v>
+      </c>
+      <c r="C98" s="73">
+        <v>46088.0</v>
+      </c>
+      <c r="D98" s="75">
+        <v>0.75</v>
+      </c>
       <c r="E98" s="3"/>
       <c r="F98" s="3"/>
       <c r="G98" s="3"/>
@@ -4099,9 +4151,9 @@
       <c r="Z98" s="3"/>
       <c r="AA98" s="3"/>
     </row>
-    <row r="99" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
-      <c r="A99" s="73"/>
-      <c r="B99" s="74"/>
+    <row r="99">
+      <c r="A99" s="74"/>
+      <c r="B99" s="76"/>
       <c r="C99" s="71"/>
       <c r="D99" s="75"/>
       <c r="E99" s="3"/>
@@ -4128,11 +4180,11 @@
       <c r="Z99" s="3"/>
       <c r="AA99" s="3"/>
     </row>
-    <row r="100" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
-      <c r="A100" s="76"/>
-      <c r="B100" s="76"/>
-      <c r="C100" s="76"/>
-      <c r="D100" s="76"/>
+    <row r="100">
+      <c r="A100" s="77"/>
+      <c r="B100" s="77"/>
+      <c r="C100" s="77"/>
+      <c r="D100" s="77"/>
       <c r="E100" s="3"/>
       <c r="F100" s="3"/>
       <c r="G100" s="3"/>
@@ -4157,15 +4209,15 @@
       <c r="Z100" s="3"/>
       <c r="AA100" s="3"/>
     </row>
-    <row r="101" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="101">
       <c r="A101" s="45"/>
       <c r="B101" s="46" t="s">
         <v>15</v>
       </c>
       <c r="C101" s="47"/>
       <c r="D101" s="41">
-        <f>SUM(D91:D96)</f>
-        <v>9.15</v>
+        <f>sum(D91:D96)</f>
+        <v>12.9</v>
       </c>
       <c r="E101" s="3"/>
       <c r="F101" s="3"/>
@@ -4191,7 +4243,7 @@
       <c r="Z101" s="3"/>
       <c r="AA101" s="3"/>
     </row>
-    <row r="102" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="102">
       <c r="A102" s="3"/>
       <c r="B102" s="3"/>
       <c r="C102" s="3"/>
@@ -4220,7 +4272,7 @@
       <c r="Z102" s="3"/>
       <c r="AA102" s="3"/>
     </row>
-    <row r="103" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="103">
       <c r="A103" s="3"/>
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
@@ -4249,7 +4301,7 @@
       <c r="Z103" s="3"/>
       <c r="AA103" s="3"/>
     </row>
-    <row r="104" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="104">
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
       <c r="C104" s="3"/>
@@ -4278,7 +4330,7 @@
       <c r="Z104" s="3"/>
       <c r="AA104" s="3"/>
     </row>
-    <row r="105" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="105">
       <c r="A105" s="3"/>
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
@@ -4307,7 +4359,7 @@
       <c r="Z105" s="3"/>
       <c r="AA105" s="3"/>
     </row>
-    <row r="106" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="106">
       <c r="A106" s="3"/>
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
@@ -4336,7 +4388,7 @@
       <c r="Z106" s="3"/>
       <c r="AA106" s="3"/>
     </row>
-    <row r="107" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="107">
       <c r="A107" s="3"/>
       <c r="B107" s="3"/>
       <c r="C107" s="3"/>
@@ -4365,7 +4417,7 @@
       <c r="Z107" s="3"/>
       <c r="AA107" s="3"/>
     </row>
-    <row r="108" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="108">
       <c r="A108" s="3"/>
       <c r="B108" s="3"/>
       <c r="C108" s="3"/>
@@ -4394,7 +4446,7 @@
       <c r="Z108" s="3"/>
       <c r="AA108" s="3"/>
     </row>
-    <row r="109" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="109">
       <c r="A109" s="3"/>
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
@@ -4423,7 +4475,7 @@
       <c r="Z109" s="3"/>
       <c r="AA109" s="3"/>
     </row>
-    <row r="110" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="110">
       <c r="A110" s="3"/>
       <c r="B110" s="3"/>
       <c r="C110" s="3"/>
@@ -4452,7 +4504,7 @@
       <c r="Z110" s="3"/>
       <c r="AA110" s="3"/>
     </row>
-    <row r="111" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="111">
       <c r="A111" s="3"/>
       <c r="B111" s="3"/>
       <c r="C111" s="3"/>
@@ -4481,7 +4533,7 @@
       <c r="Z111" s="3"/>
       <c r="AA111" s="3"/>
     </row>
-    <row r="112" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="112">
       <c r="A112" s="3"/>
       <c r="B112" s="3"/>
       <c r="C112" s="3"/>
@@ -4510,7 +4562,7 @@
       <c r="Z112" s="3"/>
       <c r="AA112" s="3"/>
     </row>
-    <row r="113" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="113">
       <c r="A113" s="3"/>
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
@@ -4539,7 +4591,7 @@
       <c r="Z113" s="3"/>
       <c r="AA113" s="3"/>
     </row>
-    <row r="114" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="114">
       <c r="A114" s="3"/>
       <c r="B114" s="3"/>
       <c r="C114" s="3"/>
@@ -4568,7 +4620,7 @@
       <c r="Z114" s="3"/>
       <c r="AA114" s="3"/>
     </row>
-    <row r="115" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="115">
       <c r="A115" s="3"/>
       <c r="B115" s="3"/>
       <c r="C115" s="3"/>
@@ -4597,7 +4649,7 @@
       <c r="Z115" s="3"/>
       <c r="AA115" s="3"/>
     </row>
-    <row r="116" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="116">
       <c r="A116" s="3"/>
       <c r="B116" s="3"/>
       <c r="C116" s="3"/>
@@ -4626,7 +4678,7 @@
       <c r="Z116" s="3"/>
       <c r="AA116" s="3"/>
     </row>
-    <row r="117" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="117">
       <c r="A117" s="3"/>
       <c r="B117" s="3"/>
       <c r="C117" s="3"/>
@@ -4655,7 +4707,7 @@
       <c r="Z117" s="3"/>
       <c r="AA117" s="3"/>
     </row>
-    <row r="118" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="118">
       <c r="A118" s="3"/>
       <c r="B118" s="3"/>
       <c r="C118" s="3"/>
@@ -4684,7 +4736,7 @@
       <c r="Z118" s="3"/>
       <c r="AA118" s="3"/>
     </row>
-    <row r="119" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="119">
       <c r="A119" s="3"/>
       <c r="B119" s="3"/>
       <c r="C119" s="3"/>
@@ -4713,7 +4765,7 @@
       <c r="Z119" s="3"/>
       <c r="AA119" s="3"/>
     </row>
-    <row r="120" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="120">
       <c r="A120" s="3"/>
       <c r="B120" s="3"/>
       <c r="C120" s="3"/>
@@ -4742,7 +4794,7 @@
       <c r="Z120" s="3"/>
       <c r="AA120" s="3"/>
     </row>
-    <row r="121" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="121">
       <c r="A121" s="3"/>
       <c r="B121" s="3"/>
       <c r="C121" s="3"/>
@@ -4771,7 +4823,7 @@
       <c r="Z121" s="3"/>
       <c r="AA121" s="3"/>
     </row>
-    <row r="122" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="122">
       <c r="A122" s="3"/>
       <c r="B122" s="3"/>
       <c r="C122" s="3"/>
@@ -4800,7 +4852,7 @@
       <c r="Z122" s="3"/>
       <c r="AA122" s="3"/>
     </row>
-    <row r="123" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="123">
       <c r="A123" s="3"/>
       <c r="B123" s="3"/>
       <c r="C123" s="3"/>
@@ -4829,7 +4881,7 @@
       <c r="Z123" s="3"/>
       <c r="AA123" s="3"/>
     </row>
-    <row r="124" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="124">
       <c r="A124" s="3"/>
       <c r="B124" s="3"/>
       <c r="C124" s="3"/>
@@ -4858,7 +4910,7 @@
       <c r="Z124" s="3"/>
       <c r="AA124" s="3"/>
     </row>
-    <row r="125" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="125">
       <c r="A125" s="3"/>
       <c r="B125" s="3"/>
       <c r="C125" s="3"/>
@@ -4887,7 +4939,7 @@
       <c r="Z125" s="3"/>
       <c r="AA125" s="3"/>
     </row>
-    <row r="126" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="126">
       <c r="A126" s="3"/>
       <c r="B126" s="3"/>
       <c r="C126" s="3"/>
@@ -4916,7 +4968,7 @@
       <c r="Z126" s="3"/>
       <c r="AA126" s="3"/>
     </row>
-    <row r="127" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="127">
       <c r="A127" s="3"/>
       <c r="B127" s="3"/>
       <c r="C127" s="3"/>
@@ -4945,7 +4997,7 @@
       <c r="Z127" s="3"/>
       <c r="AA127" s="3"/>
     </row>
-    <row r="128" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="128">
       <c r="A128" s="3"/>
       <c r="B128" s="3"/>
       <c r="C128" s="3"/>
@@ -4974,7 +5026,7 @@
       <c r="Z128" s="3"/>
       <c r="AA128" s="3"/>
     </row>
-    <row r="129" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="129">
       <c r="A129" s="3"/>
       <c r="B129" s="3"/>
       <c r="C129" s="3"/>
@@ -5003,7 +5055,7 @@
       <c r="Z129" s="3"/>
       <c r="AA129" s="3"/>
     </row>
-    <row r="130" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="130">
       <c r="A130" s="3"/>
       <c r="B130" s="3"/>
       <c r="C130" s="3"/>
@@ -5032,7 +5084,7 @@
       <c r="Z130" s="3"/>
       <c r="AA130" s="3"/>
     </row>
-    <row r="131" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="131">
       <c r="A131" s="3"/>
       <c r="B131" s="3"/>
       <c r="C131" s="3"/>
@@ -5061,7 +5113,7 @@
       <c r="Z131" s="3"/>
       <c r="AA131" s="3"/>
     </row>
-    <row r="132" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="132">
       <c r="A132" s="3"/>
       <c r="B132" s="3"/>
       <c r="C132" s="3"/>
@@ -5090,7 +5142,7 @@
       <c r="Z132" s="3"/>
       <c r="AA132" s="3"/>
     </row>
-    <row r="133" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="133">
       <c r="A133" s="3"/>
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
@@ -5119,7 +5171,7 @@
       <c r="Z133" s="3"/>
       <c r="AA133" s="3"/>
     </row>
-    <row r="134" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="134">
       <c r="A134" s="3"/>
       <c r="B134" s="3"/>
       <c r="C134" s="3"/>
@@ -5148,7 +5200,7 @@
       <c r="Z134" s="3"/>
       <c r="AA134" s="3"/>
     </row>
-    <row r="135" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="135">
       <c r="A135" s="3"/>
       <c r="B135" s="3"/>
       <c r="C135" s="3"/>
@@ -5177,7 +5229,7 @@
       <c r="Z135" s="3"/>
       <c r="AA135" s="3"/>
     </row>
-    <row r="136" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="136">
       <c r="A136" s="3"/>
       <c r="B136" s="3"/>
       <c r="C136" s="3"/>
@@ -5206,7 +5258,7 @@
       <c r="Z136" s="3"/>
       <c r="AA136" s="3"/>
     </row>
-    <row r="137" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="137">
       <c r="A137" s="3"/>
       <c r="B137" s="3"/>
       <c r="C137" s="3"/>
@@ -5235,7 +5287,7 @@
       <c r="Z137" s="3"/>
       <c r="AA137" s="3"/>
     </row>
-    <row r="138" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="138">
       <c r="A138" s="3"/>
       <c r="B138" s="3"/>
       <c r="C138" s="3"/>
@@ -5264,7 +5316,7 @@
       <c r="Z138" s="3"/>
       <c r="AA138" s="3"/>
     </row>
-    <row r="139" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="139">
       <c r="A139" s="3"/>
       <c r="B139" s="3"/>
       <c r="C139" s="3"/>
@@ -5293,7 +5345,7 @@
       <c r="Z139" s="3"/>
       <c r="AA139" s="3"/>
     </row>
-    <row r="140" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="140">
       <c r="A140" s="3"/>
       <c r="B140" s="3"/>
       <c r="C140" s="3"/>
@@ -5322,7 +5374,7 @@
       <c r="Z140" s="3"/>
       <c r="AA140" s="3"/>
     </row>
-    <row r="141" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="141">
       <c r="A141" s="3"/>
       <c r="B141" s="3"/>
       <c r="C141" s="3"/>
@@ -5351,7 +5403,7 @@
       <c r="Z141" s="3"/>
       <c r="AA141" s="3"/>
     </row>
-    <row r="142" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="142">
       <c r="A142" s="3"/>
       <c r="B142" s="3"/>
       <c r="C142" s="3"/>
@@ -5380,7 +5432,7 @@
       <c r="Z142" s="3"/>
       <c r="AA142" s="3"/>
     </row>
-    <row r="143" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="143">
       <c r="A143" s="3"/>
       <c r="B143" s="3"/>
       <c r="C143" s="3"/>
@@ -5409,7 +5461,7 @@
       <c r="Z143" s="3"/>
       <c r="AA143" s="3"/>
     </row>
-    <row r="144" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="144">
       <c r="A144" s="3"/>
       <c r="B144" s="3"/>
       <c r="C144" s="3"/>
@@ -5438,7 +5490,7 @@
       <c r="Z144" s="3"/>
       <c r="AA144" s="3"/>
     </row>
-    <row r="145" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="145">
       <c r="A145" s="3"/>
       <c r="B145" s="3"/>
       <c r="C145" s="3"/>
@@ -5467,7 +5519,7 @@
       <c r="Z145" s="3"/>
       <c r="AA145" s="3"/>
     </row>
-    <row r="146" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="146">
       <c r="A146" s="3"/>
       <c r="B146" s="3"/>
       <c r="C146" s="3"/>
@@ -5496,7 +5548,7 @@
       <c r="Z146" s="3"/>
       <c r="AA146" s="3"/>
     </row>
-    <row r="147" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="147">
       <c r="A147" s="3"/>
       <c r="B147" s="3"/>
       <c r="C147" s="3"/>
@@ -5525,7 +5577,7 @@
       <c r="Z147" s="3"/>
       <c r="AA147" s="3"/>
     </row>
-    <row r="148" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="148">
       <c r="A148" s="3"/>
       <c r="B148" s="3"/>
       <c r="C148" s="3"/>
@@ -5554,7 +5606,7 @@
       <c r="Z148" s="3"/>
       <c r="AA148" s="3"/>
     </row>
-    <row r="149" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="149">
       <c r="A149" s="3"/>
       <c r="B149" s="3"/>
       <c r="C149" s="3"/>
@@ -5583,7 +5635,7 @@
       <c r="Z149" s="3"/>
       <c r="AA149" s="3"/>
     </row>
-    <row r="150" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="150">
       <c r="A150" s="3"/>
       <c r="B150" s="3"/>
       <c r="C150" s="3"/>
@@ -5612,7 +5664,7 @@
       <c r="Z150" s="3"/>
       <c r="AA150" s="3"/>
     </row>
-    <row r="151" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="151">
       <c r="A151" s="3"/>
       <c r="B151" s="3"/>
       <c r="C151" s="3"/>
@@ -5641,7 +5693,7 @@
       <c r="Z151" s="3"/>
       <c r="AA151" s="3"/>
     </row>
-    <row r="152" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="152">
       <c r="A152" s="3"/>
       <c r="B152" s="3"/>
       <c r="C152" s="3"/>
@@ -5670,7 +5722,7 @@
       <c r="Z152" s="3"/>
       <c r="AA152" s="3"/>
     </row>
-    <row r="153" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="153">
       <c r="A153" s="3"/>
       <c r="B153" s="3"/>
       <c r="C153" s="3"/>
@@ -5699,7 +5751,7 @@
       <c r="Z153" s="3"/>
       <c r="AA153" s="3"/>
     </row>
-    <row r="154" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="154">
       <c r="A154" s="3"/>
       <c r="B154" s="3"/>
       <c r="C154" s="3"/>
@@ -5728,7 +5780,7 @@
       <c r="Z154" s="3"/>
       <c r="AA154" s="3"/>
     </row>
-    <row r="155" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="155">
       <c r="A155" s="3"/>
       <c r="B155" s="3"/>
       <c r="C155" s="3"/>
@@ -5757,7 +5809,7 @@
       <c r="Z155" s="3"/>
       <c r="AA155" s="3"/>
     </row>
-    <row r="156" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="156">
       <c r="A156" s="3"/>
       <c r="B156" s="3"/>
       <c r="C156" s="3"/>
@@ -5786,7 +5838,7 @@
       <c r="Z156" s="3"/>
       <c r="AA156" s="3"/>
     </row>
-    <row r="157" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="157">
       <c r="A157" s="3"/>
       <c r="B157" s="3"/>
       <c r="C157" s="3"/>
@@ -5815,7 +5867,7 @@
       <c r="Z157" s="3"/>
       <c r="AA157" s="3"/>
     </row>
-    <row r="158" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="158">
       <c r="A158" s="3"/>
       <c r="B158" s="3"/>
       <c r="C158" s="3"/>
@@ -5844,7 +5896,7 @@
       <c r="Z158" s="3"/>
       <c r="AA158" s="3"/>
     </row>
-    <row r="159" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="159">
       <c r="A159" s="3"/>
       <c r="B159" s="3"/>
       <c r="C159" s="3"/>
@@ -5873,7 +5925,7 @@
       <c r="Z159" s="3"/>
       <c r="AA159" s="3"/>
     </row>
-    <row r="160" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="160">
       <c r="A160" s="3"/>
       <c r="B160" s="3"/>
       <c r="C160" s="3"/>
@@ -5902,7 +5954,7 @@
       <c r="Z160" s="3"/>
       <c r="AA160" s="3"/>
     </row>
-    <row r="161" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="161">
       <c r="A161" s="3"/>
       <c r="B161" s="3"/>
       <c r="C161" s="3"/>
@@ -5931,7 +5983,7 @@
       <c r="Z161" s="3"/>
       <c r="AA161" s="3"/>
     </row>
-    <row r="162" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="162">
       <c r="A162" s="3"/>
       <c r="B162" s="3"/>
       <c r="C162" s="3"/>
@@ -5960,7 +6012,7 @@
       <c r="Z162" s="3"/>
       <c r="AA162" s="3"/>
     </row>
-    <row r="163" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="163">
       <c r="A163" s="3"/>
       <c r="B163" s="3"/>
       <c r="C163" s="3"/>
@@ -5989,7 +6041,7 @@
       <c r="Z163" s="3"/>
       <c r="AA163" s="3"/>
     </row>
-    <row r="164" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="164">
       <c r="A164" s="3"/>
       <c r="B164" s="3"/>
       <c r="C164" s="3"/>
@@ -6018,7 +6070,7 @@
       <c r="Z164" s="3"/>
       <c r="AA164" s="3"/>
     </row>
-    <row r="165" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="165">
       <c r="A165" s="3"/>
       <c r="B165" s="3"/>
       <c r="C165" s="3"/>
@@ -6047,7 +6099,7 @@
       <c r="Z165" s="3"/>
       <c r="AA165" s="3"/>
     </row>
-    <row r="166" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="166">
       <c r="A166" s="3"/>
       <c r="B166" s="3"/>
       <c r="C166" s="3"/>
@@ -6076,7 +6128,7 @@
       <c r="Z166" s="3"/>
       <c r="AA166" s="3"/>
     </row>
-    <row r="167" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="167">
       <c r="A167" s="3"/>
       <c r="B167" s="3"/>
       <c r="C167" s="3"/>
@@ -6105,7 +6157,7 @@
       <c r="Z167" s="3"/>
       <c r="AA167" s="3"/>
     </row>
-    <row r="168" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="168">
       <c r="A168" s="3"/>
       <c r="B168" s="3"/>
       <c r="C168" s="3"/>
@@ -6134,7 +6186,7 @@
       <c r="Z168" s="3"/>
       <c r="AA168" s="3"/>
     </row>
-    <row r="169" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="169">
       <c r="A169" s="3"/>
       <c r="B169" s="3"/>
       <c r="C169" s="3"/>
@@ -6163,7 +6215,7 @@
       <c r="Z169" s="3"/>
       <c r="AA169" s="3"/>
     </row>
-    <row r="170" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="170">
       <c r="A170" s="3"/>
       <c r="B170" s="3"/>
       <c r="C170" s="3"/>
@@ -6192,7 +6244,7 @@
       <c r="Z170" s="3"/>
       <c r="AA170" s="3"/>
     </row>
-    <row r="171" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="171">
       <c r="A171" s="3"/>
       <c r="B171" s="3"/>
       <c r="C171" s="3"/>
@@ -6221,7 +6273,7 @@
       <c r="Z171" s="3"/>
       <c r="AA171" s="3"/>
     </row>
-    <row r="172" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="172">
       <c r="A172" s="3"/>
       <c r="B172" s="3"/>
       <c r="C172" s="3"/>
@@ -6250,7 +6302,7 @@
       <c r="Z172" s="3"/>
       <c r="AA172" s="3"/>
     </row>
-    <row r="173" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="173">
       <c r="A173" s="3"/>
       <c r="B173" s="3"/>
       <c r="C173" s="3"/>
@@ -6279,7 +6331,7 @@
       <c r="Z173" s="3"/>
       <c r="AA173" s="3"/>
     </row>
-    <row r="174" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="174">
       <c r="A174" s="3"/>
       <c r="B174" s="3"/>
       <c r="C174" s="3"/>
@@ -6308,7 +6360,7 @@
       <c r="Z174" s="3"/>
       <c r="AA174" s="3"/>
     </row>
-    <row r="175" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="175">
       <c r="A175" s="3"/>
       <c r="B175" s="3"/>
       <c r="C175" s="3"/>
@@ -6337,7 +6389,7 @@
       <c r="Z175" s="3"/>
       <c r="AA175" s="3"/>
     </row>
-    <row r="176" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="176">
       <c r="A176" s="3"/>
       <c r="B176" s="3"/>
       <c r="C176" s="3"/>
@@ -6366,7 +6418,7 @@
       <c r="Z176" s="3"/>
       <c r="AA176" s="3"/>
     </row>
-    <row r="177" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="177">
       <c r="A177" s="3"/>
       <c r="B177" s="3"/>
       <c r="C177" s="3"/>
@@ -6395,7 +6447,7 @@
       <c r="Z177" s="3"/>
       <c r="AA177" s="3"/>
     </row>
-    <row r="178" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="178">
       <c r="A178" s="3"/>
       <c r="B178" s="3"/>
       <c r="C178" s="3"/>
@@ -6424,7 +6476,7 @@
       <c r="Z178" s="3"/>
       <c r="AA178" s="3"/>
     </row>
-    <row r="179" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="179">
       <c r="A179" s="3"/>
       <c r="B179" s="3"/>
       <c r="C179" s="3"/>
@@ -6453,7 +6505,7 @@
       <c r="Z179" s="3"/>
       <c r="AA179" s="3"/>
     </row>
-    <row r="180" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="180">
       <c r="A180" s="3"/>
       <c r="B180" s="3"/>
       <c r="C180" s="3"/>
@@ -6482,7 +6534,7 @@
       <c r="Z180" s="3"/>
       <c r="AA180" s="3"/>
     </row>
-    <row r="181" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="181">
       <c r="A181" s="3"/>
       <c r="B181" s="3"/>
       <c r="C181" s="3"/>
@@ -6511,7 +6563,7 @@
       <c r="Z181" s="3"/>
       <c r="AA181" s="3"/>
     </row>
-    <row r="182" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="182">
       <c r="A182" s="3"/>
       <c r="B182" s="3"/>
       <c r="C182" s="3"/>
@@ -6540,7 +6592,7 @@
       <c r="Z182" s="3"/>
       <c r="AA182" s="3"/>
     </row>
-    <row r="183" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="183">
       <c r="A183" s="3"/>
       <c r="B183" s="3"/>
       <c r="C183" s="3"/>
@@ -6569,7 +6621,7 @@
       <c r="Z183" s="3"/>
       <c r="AA183" s="3"/>
     </row>
-    <row r="184" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="184">
       <c r="A184" s="3"/>
       <c r="B184" s="3"/>
       <c r="C184" s="3"/>
@@ -6598,7 +6650,7 @@
       <c r="Z184" s="3"/>
       <c r="AA184" s="3"/>
     </row>
-    <row r="185" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="185">
       <c r="A185" s="3"/>
       <c r="B185" s="3"/>
       <c r="C185" s="3"/>
@@ -6627,7 +6679,7 @@
       <c r="Z185" s="3"/>
       <c r="AA185" s="3"/>
     </row>
-    <row r="186" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="186">
       <c r="A186" s="3"/>
       <c r="B186" s="3"/>
       <c r="C186" s="3"/>
@@ -6656,7 +6708,7 @@
       <c r="Z186" s="3"/>
       <c r="AA186" s="3"/>
     </row>
-    <row r="187" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="187">
       <c r="A187" s="3"/>
       <c r="B187" s="3"/>
       <c r="C187" s="3"/>
@@ -6685,7 +6737,7 @@
       <c r="Z187" s="3"/>
       <c r="AA187" s="3"/>
     </row>
-    <row r="188" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="188">
       <c r="A188" s="3"/>
       <c r="B188" s="3"/>
       <c r="C188" s="3"/>
@@ -6714,7 +6766,7 @@
       <c r="Z188" s="3"/>
       <c r="AA188" s="3"/>
     </row>
-    <row r="189" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="189">
       <c r="A189" s="3"/>
       <c r="B189" s="3"/>
       <c r="C189" s="3"/>
@@ -6743,7 +6795,7 @@
       <c r="Z189" s="3"/>
       <c r="AA189" s="3"/>
     </row>
-    <row r="190" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="190">
       <c r="A190" s="3"/>
       <c r="B190" s="3"/>
       <c r="C190" s="3"/>
@@ -6772,7 +6824,7 @@
       <c r="Z190" s="3"/>
       <c r="AA190" s="3"/>
     </row>
-    <row r="191" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="191">
       <c r="A191" s="3"/>
       <c r="B191" s="3"/>
       <c r="C191" s="3"/>
@@ -6801,7 +6853,7 @@
       <c r="Z191" s="3"/>
       <c r="AA191" s="3"/>
     </row>
-    <row r="192" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="192">
       <c r="A192" s="3"/>
       <c r="B192" s="3"/>
       <c r="C192" s="3"/>
@@ -6830,7 +6882,7 @@
       <c r="Z192" s="3"/>
       <c r="AA192" s="3"/>
     </row>
-    <row r="193" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="193">
       <c r="A193" s="3"/>
       <c r="B193" s="3"/>
       <c r="C193" s="3"/>
@@ -6859,7 +6911,7 @@
       <c r="Z193" s="3"/>
       <c r="AA193" s="3"/>
     </row>
-    <row r="194" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="194">
       <c r="A194" s="3"/>
       <c r="B194" s="3"/>
       <c r="C194" s="3"/>
@@ -6888,7 +6940,7 @@
       <c r="Z194" s="3"/>
       <c r="AA194" s="3"/>
     </row>
-    <row r="195" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="195">
       <c r="A195" s="3"/>
       <c r="B195" s="3"/>
       <c r="C195" s="3"/>
@@ -6917,7 +6969,7 @@
       <c r="Z195" s="3"/>
       <c r="AA195" s="3"/>
     </row>
-    <row r="196" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="196">
       <c r="A196" s="3"/>
       <c r="B196" s="3"/>
       <c r="C196" s="3"/>
@@ -6946,7 +6998,7 @@
       <c r="Z196" s="3"/>
       <c r="AA196" s="3"/>
     </row>
-    <row r="197" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="197">
       <c r="A197" s="3"/>
       <c r="B197" s="3"/>
       <c r="C197" s="3"/>
@@ -6975,7 +7027,7 @@
       <c r="Z197" s="3"/>
       <c r="AA197" s="3"/>
     </row>
-    <row r="198" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="198">
       <c r="A198" s="3"/>
       <c r="B198" s="3"/>
       <c r="C198" s="3"/>
@@ -7004,7 +7056,7 @@
       <c r="Z198" s="3"/>
       <c r="AA198" s="3"/>
     </row>
-    <row r="199" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="199">
       <c r="A199" s="3"/>
       <c r="B199" s="3"/>
       <c r="C199" s="3"/>
@@ -7033,7 +7085,7 @@
       <c r="Z199" s="3"/>
       <c r="AA199" s="3"/>
     </row>
-    <row r="200" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="200">
       <c r="A200" s="3"/>
       <c r="B200" s="3"/>
       <c r="C200" s="3"/>
@@ -7062,7 +7114,7 @@
       <c r="Z200" s="3"/>
       <c r="AA200" s="3"/>
     </row>
-    <row r="201" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="201">
       <c r="A201" s="3"/>
       <c r="B201" s="3"/>
       <c r="C201" s="3"/>
@@ -7091,7 +7143,7 @@
       <c r="Z201" s="3"/>
       <c r="AA201" s="3"/>
     </row>
-    <row r="202" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="202">
       <c r="A202" s="3"/>
       <c r="B202" s="3"/>
       <c r="C202" s="3"/>
@@ -7120,7 +7172,7 @@
       <c r="Z202" s="3"/>
       <c r="AA202" s="3"/>
     </row>
-    <row r="203" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="203">
       <c r="A203" s="3"/>
       <c r="B203" s="3"/>
       <c r="C203" s="3"/>
@@ -7149,7 +7201,7 @@
       <c r="Z203" s="3"/>
       <c r="AA203" s="3"/>
     </row>
-    <row r="204" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="204">
       <c r="A204" s="3"/>
       <c r="B204" s="3"/>
       <c r="C204" s="3"/>
@@ -7178,7 +7230,7 @@
       <c r="Z204" s="3"/>
       <c r="AA204" s="3"/>
     </row>
-    <row r="205" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="205">
       <c r="A205" s="3"/>
       <c r="B205" s="3"/>
       <c r="C205" s="3"/>
@@ -7207,7 +7259,7 @@
       <c r="Z205" s="3"/>
       <c r="AA205" s="3"/>
     </row>
-    <row r="206" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="206">
       <c r="A206" s="3"/>
       <c r="B206" s="3"/>
       <c r="C206" s="3"/>
@@ -7236,7 +7288,7 @@
       <c r="Z206" s="3"/>
       <c r="AA206" s="3"/>
     </row>
-    <row r="207" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="207">
       <c r="A207" s="3"/>
       <c r="B207" s="3"/>
       <c r="C207" s="3"/>
@@ -7265,7 +7317,7 @@
       <c r="Z207" s="3"/>
       <c r="AA207" s="3"/>
     </row>
-    <row r="208" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="208">
       <c r="A208" s="3"/>
       <c r="B208" s="3"/>
       <c r="C208" s="3"/>
@@ -7294,7 +7346,7 @@
       <c r="Z208" s="3"/>
       <c r="AA208" s="3"/>
     </row>
-    <row r="209" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="209">
       <c r="A209" s="3"/>
       <c r="B209" s="3"/>
       <c r="C209" s="3"/>
@@ -7323,7 +7375,7 @@
       <c r="Z209" s="3"/>
       <c r="AA209" s="3"/>
     </row>
-    <row r="210" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="210">
       <c r="A210" s="3"/>
       <c r="B210" s="3"/>
       <c r="C210" s="3"/>
@@ -7352,7 +7404,7 @@
       <c r="Z210" s="3"/>
       <c r="AA210" s="3"/>
     </row>
-    <row r="211" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="211">
       <c r="A211" s="3"/>
       <c r="B211" s="3"/>
       <c r="C211" s="3"/>
@@ -7381,7 +7433,7 @@
       <c r="Z211" s="3"/>
       <c r="AA211" s="3"/>
     </row>
-    <row r="212" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="212">
       <c r="A212" s="3"/>
       <c r="B212" s="3"/>
       <c r="C212" s="3"/>
@@ -7410,7 +7462,7 @@
       <c r="Z212" s="3"/>
       <c r="AA212" s="3"/>
     </row>
-    <row r="213" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="213">
       <c r="A213" s="3"/>
       <c r="B213" s="3"/>
       <c r="C213" s="3"/>
@@ -7439,7 +7491,7 @@
       <c r="Z213" s="3"/>
       <c r="AA213" s="3"/>
     </row>
-    <row r="214" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="214">
       <c r="A214" s="3"/>
       <c r="B214" s="3"/>
       <c r="C214" s="3"/>
@@ -7468,7 +7520,7 @@
       <c r="Z214" s="3"/>
       <c r="AA214" s="3"/>
     </row>
-    <row r="215" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="215">
       <c r="A215" s="3"/>
       <c r="B215" s="3"/>
       <c r="C215" s="3"/>
@@ -7497,7 +7549,7 @@
       <c r="Z215" s="3"/>
       <c r="AA215" s="3"/>
     </row>
-    <row r="216" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="216">
       <c r="A216" s="3"/>
       <c r="B216" s="3"/>
       <c r="C216" s="3"/>
@@ -7526,7 +7578,7 @@
       <c r="Z216" s="3"/>
       <c r="AA216" s="3"/>
     </row>
-    <row r="217" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="217">
       <c r="A217" s="3"/>
       <c r="B217" s="3"/>
       <c r="C217" s="3"/>
@@ -7555,7 +7607,7 @@
       <c r="Z217" s="3"/>
       <c r="AA217" s="3"/>
     </row>
-    <row r="218" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="218">
       <c r="A218" s="3"/>
       <c r="B218" s="3"/>
       <c r="C218" s="3"/>
@@ -7584,7 +7636,7 @@
       <c r="Z218" s="3"/>
       <c r="AA218" s="3"/>
     </row>
-    <row r="219" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="219">
       <c r="A219" s="3"/>
       <c r="B219" s="3"/>
       <c r="C219" s="3"/>
@@ -7613,7 +7665,7 @@
       <c r="Z219" s="3"/>
       <c r="AA219" s="3"/>
     </row>
-    <row r="220" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="220">
       <c r="A220" s="3"/>
       <c r="B220" s="3"/>
       <c r="C220" s="3"/>
@@ -7642,7 +7694,7 @@
       <c r="Z220" s="3"/>
       <c r="AA220" s="3"/>
     </row>
-    <row r="221" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="221">
       <c r="A221" s="3"/>
       <c r="B221" s="3"/>
       <c r="C221" s="3"/>
@@ -7671,7 +7723,7 @@
       <c r="Z221" s="3"/>
       <c r="AA221" s="3"/>
     </row>
-    <row r="222" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="222">
       <c r="A222" s="3"/>
       <c r="B222" s="3"/>
       <c r="C222" s="3"/>
@@ -7700,7 +7752,7 @@
       <c r="Z222" s="3"/>
       <c r="AA222" s="3"/>
     </row>
-    <row r="223" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="223">
       <c r="A223" s="3"/>
       <c r="B223" s="3"/>
       <c r="C223" s="3"/>
@@ -7729,7 +7781,7 @@
       <c r="Z223" s="3"/>
       <c r="AA223" s="3"/>
     </row>
-    <row r="224" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="224">
       <c r="A224" s="3"/>
       <c r="B224" s="3"/>
       <c r="C224" s="3"/>
@@ -7758,7 +7810,7 @@
       <c r="Z224" s="3"/>
       <c r="AA224" s="3"/>
     </row>
-    <row r="225" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="225">
       <c r="A225" s="3"/>
       <c r="B225" s="3"/>
       <c r="C225" s="3"/>
@@ -7787,7 +7839,7 @@
       <c r="Z225" s="3"/>
       <c r="AA225" s="3"/>
     </row>
-    <row r="226" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="226">
       <c r="A226" s="3"/>
       <c r="B226" s="3"/>
       <c r="C226" s="3"/>
@@ -7816,7 +7868,7 @@
       <c r="Z226" s="3"/>
       <c r="AA226" s="3"/>
     </row>
-    <row r="227" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="227">
       <c r="A227" s="3"/>
       <c r="B227" s="3"/>
       <c r="C227" s="3"/>
@@ -7845,7 +7897,7 @@
       <c r="Z227" s="3"/>
       <c r="AA227" s="3"/>
     </row>
-    <row r="228" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="228">
       <c r="A228" s="3"/>
       <c r="B228" s="3"/>
       <c r="C228" s="3"/>
@@ -7874,7 +7926,7 @@
       <c r="Z228" s="3"/>
       <c r="AA228" s="3"/>
     </row>
-    <row r="229" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="229">
       <c r="A229" s="3"/>
       <c r="B229" s="3"/>
       <c r="C229" s="3"/>
@@ -7903,7 +7955,7 @@
       <c r="Z229" s="3"/>
       <c r="AA229" s="3"/>
     </row>
-    <row r="230" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="230">
       <c r="A230" s="3"/>
       <c r="B230" s="3"/>
       <c r="C230" s="3"/>
@@ -7932,7 +7984,7 @@
       <c r="Z230" s="3"/>
       <c r="AA230" s="3"/>
     </row>
-    <row r="231" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="231">
       <c r="A231" s="3"/>
       <c r="B231" s="3"/>
       <c r="C231" s="3"/>
@@ -7961,7 +8013,7 @@
       <c r="Z231" s="3"/>
       <c r="AA231" s="3"/>
     </row>
-    <row r="232" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="232">
       <c r="A232" s="3"/>
       <c r="B232" s="3"/>
       <c r="C232" s="3"/>
@@ -7990,7 +8042,7 @@
       <c r="Z232" s="3"/>
       <c r="AA232" s="3"/>
     </row>
-    <row r="233" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="233">
       <c r="A233" s="3"/>
       <c r="B233" s="3"/>
       <c r="C233" s="3"/>
@@ -8019,7 +8071,7 @@
       <c r="Z233" s="3"/>
       <c r="AA233" s="3"/>
     </row>
-    <row r="234" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="234">
       <c r="A234" s="3"/>
       <c r="B234" s="3"/>
       <c r="C234" s="3"/>
@@ -8048,7 +8100,7 @@
       <c r="Z234" s="3"/>
       <c r="AA234" s="3"/>
     </row>
-    <row r="235" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="235">
       <c r="A235" s="3"/>
       <c r="B235" s="3"/>
       <c r="C235" s="3"/>
@@ -8077,7 +8129,7 @@
       <c r="Z235" s="3"/>
       <c r="AA235" s="3"/>
     </row>
-    <row r="236" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="236">
       <c r="A236" s="3"/>
       <c r="B236" s="3"/>
       <c r="C236" s="3"/>
@@ -8106,7 +8158,7 @@
       <c r="Z236" s="3"/>
       <c r="AA236" s="3"/>
     </row>
-    <row r="237" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="237">
       <c r="A237" s="3"/>
       <c r="B237" s="3"/>
       <c r="C237" s="3"/>
@@ -8135,7 +8187,7 @@
       <c r="Z237" s="3"/>
       <c r="AA237" s="3"/>
     </row>
-    <row r="238" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="238">
       <c r="A238" s="3"/>
       <c r="B238" s="3"/>
       <c r="C238" s="3"/>
@@ -8164,7 +8216,7 @@
       <c r="Z238" s="3"/>
       <c r="AA238" s="3"/>
     </row>
-    <row r="239" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="239">
       <c r="A239" s="3"/>
       <c r="B239" s="3"/>
       <c r="C239" s="3"/>
@@ -8193,7 +8245,7 @@
       <c r="Z239" s="3"/>
       <c r="AA239" s="3"/>
     </row>
-    <row r="240" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="240">
       <c r="A240" s="3"/>
       <c r="B240" s="3"/>
       <c r="C240" s="3"/>
@@ -8222,7 +8274,7 @@
       <c r="Z240" s="3"/>
       <c r="AA240" s="3"/>
     </row>
-    <row r="241" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="241">
       <c r="A241" s="3"/>
       <c r="B241" s="3"/>
       <c r="C241" s="3"/>
@@ -8251,7 +8303,7 @@
       <c r="Z241" s="3"/>
       <c r="AA241" s="3"/>
     </row>
-    <row r="242" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="242">
       <c r="A242" s="3"/>
       <c r="B242" s="3"/>
       <c r="C242" s="3"/>
@@ -8280,7 +8332,7 @@
       <c r="Z242" s="3"/>
       <c r="AA242" s="3"/>
     </row>
-    <row r="243" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="243">
       <c r="A243" s="3"/>
       <c r="B243" s="3"/>
       <c r="C243" s="3"/>
@@ -8309,7 +8361,7 @@
       <c r="Z243" s="3"/>
       <c r="AA243" s="3"/>
     </row>
-    <row r="244" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="244">
       <c r="A244" s="3"/>
       <c r="B244" s="3"/>
       <c r="C244" s="3"/>
@@ -8338,7 +8390,7 @@
       <c r="Z244" s="3"/>
       <c r="AA244" s="3"/>
     </row>
-    <row r="245" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="245">
       <c r="A245" s="3"/>
       <c r="B245" s="3"/>
       <c r="C245" s="3"/>
@@ -8367,7 +8419,7 @@
       <c r="Z245" s="3"/>
       <c r="AA245" s="3"/>
     </row>
-    <row r="246" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="246">
       <c r="A246" s="3"/>
       <c r="B246" s="3"/>
       <c r="C246" s="3"/>
@@ -8396,7 +8448,7 @@
       <c r="Z246" s="3"/>
       <c r="AA246" s="3"/>
     </row>
-    <row r="247" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="247">
       <c r="A247" s="3"/>
       <c r="B247" s="3"/>
       <c r="C247" s="3"/>
@@ -8425,7 +8477,7 @@
       <c r="Z247" s="3"/>
       <c r="AA247" s="3"/>
     </row>
-    <row r="248" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="248">
       <c r="A248" s="3"/>
       <c r="B248" s="3"/>
       <c r="C248" s="3"/>
@@ -8454,7 +8506,7 @@
       <c r="Z248" s="3"/>
       <c r="AA248" s="3"/>
     </row>
-    <row r="249" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="249">
       <c r="A249" s="3"/>
       <c r="B249" s="3"/>
       <c r="C249" s="3"/>
@@ -8483,7 +8535,7 @@
       <c r="Z249" s="3"/>
       <c r="AA249" s="3"/>
     </row>
-    <row r="250" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="250">
       <c r="A250" s="3"/>
       <c r="B250" s="3"/>
       <c r="C250" s="3"/>
@@ -8512,7 +8564,7 @@
       <c r="Z250" s="3"/>
       <c r="AA250" s="3"/>
     </row>
-    <row r="251" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="251">
       <c r="A251" s="3"/>
       <c r="B251" s="3"/>
       <c r="C251" s="3"/>
@@ -8541,7 +8593,7 @@
       <c r="Z251" s="3"/>
       <c r="AA251" s="3"/>
     </row>
-    <row r="252" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="252">
       <c r="A252" s="3"/>
       <c r="B252" s="3"/>
       <c r="C252" s="3"/>
@@ -8570,7 +8622,7 @@
       <c r="Z252" s="3"/>
       <c r="AA252" s="3"/>
     </row>
-    <row r="253" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="253">
       <c r="A253" s="3"/>
       <c r="B253" s="3"/>
       <c r="C253" s="3"/>
@@ -8599,7 +8651,7 @@
       <c r="Z253" s="3"/>
       <c r="AA253" s="3"/>
     </row>
-    <row r="254" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="254">
       <c r="A254" s="3"/>
       <c r="B254" s="3"/>
       <c r="C254" s="3"/>
@@ -8628,7 +8680,7 @@
       <c r="Z254" s="3"/>
       <c r="AA254" s="3"/>
     </row>
-    <row r="255" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="255">
       <c r="A255" s="3"/>
       <c r="B255" s="3"/>
       <c r="C255" s="3"/>
@@ -8657,7 +8709,7 @@
       <c r="Z255" s="3"/>
       <c r="AA255" s="3"/>
     </row>
-    <row r="256" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="256">
       <c r="A256" s="3"/>
       <c r="B256" s="3"/>
       <c r="C256" s="3"/>
@@ -8686,7 +8738,7 @@
       <c r="Z256" s="3"/>
       <c r="AA256" s="3"/>
     </row>
-    <row r="257" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="257">
       <c r="A257" s="3"/>
       <c r="B257" s="3"/>
       <c r="C257" s="3"/>
@@ -8715,7 +8767,7 @@
       <c r="Z257" s="3"/>
       <c r="AA257" s="3"/>
     </row>
-    <row r="258" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="258">
       <c r="A258" s="3"/>
       <c r="B258" s="3"/>
       <c r="C258" s="3"/>
@@ -8744,7 +8796,7 @@
       <c r="Z258" s="3"/>
       <c r="AA258" s="3"/>
     </row>
-    <row r="259" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="259">
       <c r="A259" s="3"/>
       <c r="B259" s="3"/>
       <c r="C259" s="3"/>
@@ -8773,7 +8825,7 @@
       <c r="Z259" s="3"/>
       <c r="AA259" s="3"/>
     </row>
-    <row r="260" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="260">
       <c r="A260" s="3"/>
       <c r="B260" s="3"/>
       <c r="C260" s="3"/>
@@ -8802,7 +8854,7 @@
       <c r="Z260" s="3"/>
       <c r="AA260" s="3"/>
     </row>
-    <row r="261" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="261">
       <c r="A261" s="3"/>
       <c r="B261" s="3"/>
       <c r="C261" s="3"/>
@@ -8831,7 +8883,7 @@
       <c r="Z261" s="3"/>
       <c r="AA261" s="3"/>
     </row>
-    <row r="262" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="262">
       <c r="A262" s="3"/>
       <c r="B262" s="3"/>
       <c r="C262" s="3"/>
@@ -8860,7 +8912,7 @@
       <c r="Z262" s="3"/>
       <c r="AA262" s="3"/>
     </row>
-    <row r="263" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="263">
       <c r="A263" s="3"/>
       <c r="B263" s="3"/>
       <c r="C263" s="3"/>
@@ -8889,7 +8941,7 @@
       <c r="Z263" s="3"/>
       <c r="AA263" s="3"/>
     </row>
-    <row r="264" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="264">
       <c r="A264" s="3"/>
       <c r="B264" s="3"/>
       <c r="C264" s="3"/>
@@ -8918,7 +8970,7 @@
       <c r="Z264" s="3"/>
       <c r="AA264" s="3"/>
     </row>
-    <row r="265" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="265">
       <c r="A265" s="3"/>
       <c r="B265" s="3"/>
       <c r="C265" s="3"/>
@@ -8947,7 +8999,7 @@
       <c r="Z265" s="3"/>
       <c r="AA265" s="3"/>
     </row>
-    <row r="266" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="266">
       <c r="A266" s="3"/>
       <c r="B266" s="3"/>
       <c r="C266" s="3"/>
@@ -8976,7 +9028,7 @@
       <c r="Z266" s="3"/>
       <c r="AA266" s="3"/>
     </row>
-    <row r="267" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="267">
       <c r="A267" s="3"/>
       <c r="B267" s="3"/>
       <c r="C267" s="3"/>
@@ -9005,7 +9057,7 @@
       <c r="Z267" s="3"/>
       <c r="AA267" s="3"/>
     </row>
-    <row r="268" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="268">
       <c r="A268" s="3"/>
       <c r="B268" s="3"/>
       <c r="C268" s="3"/>
@@ -9034,7 +9086,7 @@
       <c r="Z268" s="3"/>
       <c r="AA268" s="3"/>
     </row>
-    <row r="269" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="269">
       <c r="A269" s="3"/>
       <c r="B269" s="3"/>
       <c r="C269" s="3"/>
@@ -9063,7 +9115,7 @@
       <c r="Z269" s="3"/>
       <c r="AA269" s="3"/>
     </row>
-    <row r="270" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="270">
       <c r="A270" s="3"/>
       <c r="B270" s="3"/>
       <c r="C270" s="3"/>
@@ -9092,7 +9144,7 @@
       <c r="Z270" s="3"/>
       <c r="AA270" s="3"/>
     </row>
-    <row r="271" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="271">
       <c r="A271" s="3"/>
       <c r="B271" s="3"/>
       <c r="C271" s="3"/>
@@ -9121,7 +9173,7 @@
       <c r="Z271" s="3"/>
       <c r="AA271" s="3"/>
     </row>
-    <row r="272" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="272">
       <c r="A272" s="3"/>
       <c r="B272" s="3"/>
       <c r="C272" s="3"/>
@@ -9150,7 +9202,7 @@
       <c r="Z272" s="3"/>
       <c r="AA272" s="3"/>
     </row>
-    <row r="273" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="273">
       <c r="A273" s="3"/>
       <c r="B273" s="3"/>
       <c r="C273" s="3"/>
@@ -9179,7 +9231,7 @@
       <c r="Z273" s="3"/>
       <c r="AA273" s="3"/>
     </row>
-    <row r="274" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="274">
       <c r="A274" s="3"/>
       <c r="B274" s="3"/>
       <c r="C274" s="3"/>
@@ -9208,7 +9260,7 @@
       <c r="Z274" s="3"/>
       <c r="AA274" s="3"/>
     </row>
-    <row r="275" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="275">
       <c r="A275" s="3"/>
       <c r="B275" s="3"/>
       <c r="C275" s="3"/>
@@ -9237,7 +9289,7 @@
       <c r="Z275" s="3"/>
       <c r="AA275" s="3"/>
     </row>
-    <row r="276" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="276">
       <c r="A276" s="3"/>
       <c r="B276" s="3"/>
       <c r="C276" s="3"/>
@@ -9266,7 +9318,7 @@
       <c r="Z276" s="3"/>
       <c r="AA276" s="3"/>
     </row>
-    <row r="277" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="277">
       <c r="A277" s="3"/>
       <c r="B277" s="3"/>
       <c r="C277" s="3"/>
@@ -9295,7 +9347,7 @@
       <c r="Z277" s="3"/>
       <c r="AA277" s="3"/>
     </row>
-    <row r="278" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="278">
       <c r="A278" s="3"/>
       <c r="B278" s="3"/>
       <c r="C278" s="3"/>
@@ -9324,7 +9376,7 @@
       <c r="Z278" s="3"/>
       <c r="AA278" s="3"/>
     </row>
-    <row r="279" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="279">
       <c r="A279" s="3"/>
       <c r="B279" s="3"/>
       <c r="C279" s="3"/>
@@ -9353,7 +9405,7 @@
       <c r="Z279" s="3"/>
       <c r="AA279" s="3"/>
     </row>
-    <row r="280" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="280">
       <c r="A280" s="3"/>
       <c r="B280" s="3"/>
       <c r="C280" s="3"/>
@@ -9382,7 +9434,7 @@
       <c r="Z280" s="3"/>
       <c r="AA280" s="3"/>
     </row>
-    <row r="281" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="281">
       <c r="A281" s="3"/>
       <c r="B281" s="3"/>
       <c r="C281" s="3"/>
@@ -9411,7 +9463,7 @@
       <c r="Z281" s="3"/>
       <c r="AA281" s="3"/>
     </row>
-    <row r="282" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="282">
       <c r="A282" s="3"/>
       <c r="B282" s="3"/>
       <c r="C282" s="3"/>
@@ -9440,7 +9492,7 @@
       <c r="Z282" s="3"/>
       <c r="AA282" s="3"/>
     </row>
-    <row r="283" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="283">
       <c r="A283" s="3"/>
       <c r="B283" s="3"/>
       <c r="C283" s="3"/>
@@ -9469,7 +9521,7 @@
       <c r="Z283" s="3"/>
       <c r="AA283" s="3"/>
     </row>
-    <row r="284" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="284">
       <c r="A284" s="3"/>
       <c r="B284" s="3"/>
       <c r="C284" s="3"/>
@@ -9498,7 +9550,7 @@
       <c r="Z284" s="3"/>
       <c r="AA284" s="3"/>
     </row>
-    <row r="285" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="285">
       <c r="A285" s="3"/>
       <c r="B285" s="3"/>
       <c r="C285" s="3"/>
@@ -9527,7 +9579,7 @@
       <c r="Z285" s="3"/>
       <c r="AA285" s="3"/>
     </row>
-    <row r="286" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="286">
       <c r="A286" s="3"/>
       <c r="B286" s="3"/>
       <c r="C286" s="3"/>
@@ -9556,7 +9608,7 @@
       <c r="Z286" s="3"/>
       <c r="AA286" s="3"/>
     </row>
-    <row r="287" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="287">
       <c r="A287" s="3"/>
       <c r="B287" s="3"/>
       <c r="C287" s="3"/>
@@ -9585,7 +9637,7 @@
       <c r="Z287" s="3"/>
       <c r="AA287" s="3"/>
     </row>
-    <row r="288" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="288">
       <c r="A288" s="3"/>
       <c r="B288" s="3"/>
       <c r="C288" s="3"/>
@@ -9614,7 +9666,7 @@
       <c r="Z288" s="3"/>
       <c r="AA288" s="3"/>
     </row>
-    <row r="289" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="289">
       <c r="A289" s="3"/>
       <c r="B289" s="3"/>
       <c r="C289" s="3"/>
@@ -9643,7 +9695,7 @@
       <c r="Z289" s="3"/>
       <c r="AA289" s="3"/>
     </row>
-    <row r="290" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="290">
       <c r="A290" s="3"/>
       <c r="B290" s="3"/>
       <c r="C290" s="3"/>
@@ -9672,7 +9724,7 @@
       <c r="Z290" s="3"/>
       <c r="AA290" s="3"/>
     </row>
-    <row r="291" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="291">
       <c r="A291" s="3"/>
       <c r="B291" s="3"/>
       <c r="C291" s="3"/>
@@ -9701,7 +9753,7 @@
       <c r="Z291" s="3"/>
       <c r="AA291" s="3"/>
     </row>
-    <row r="292" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="292">
       <c r="A292" s="3"/>
       <c r="B292" s="3"/>
       <c r="C292" s="3"/>
@@ -9730,7 +9782,7 @@
       <c r="Z292" s="3"/>
       <c r="AA292" s="3"/>
     </row>
-    <row r="293" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="293">
       <c r="A293" s="3"/>
       <c r="B293" s="3"/>
       <c r="C293" s="3"/>
@@ -9759,7 +9811,7 @@
       <c r="Z293" s="3"/>
       <c r="AA293" s="3"/>
     </row>
-    <row r="294" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="294">
       <c r="A294" s="3"/>
       <c r="B294" s="3"/>
       <c r="C294" s="3"/>
@@ -9788,7 +9840,7 @@
       <c r="Z294" s="3"/>
       <c r="AA294" s="3"/>
     </row>
-    <row r="295" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="295">
       <c r="A295" s="3"/>
       <c r="B295" s="3"/>
       <c r="C295" s="3"/>
@@ -9817,7 +9869,7 @@
       <c r="Z295" s="3"/>
       <c r="AA295" s="3"/>
     </row>
-    <row r="296" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="296">
       <c r="A296" s="3"/>
       <c r="B296" s="3"/>
       <c r="C296" s="3"/>
@@ -9846,7 +9898,7 @@
       <c r="Z296" s="3"/>
       <c r="AA296" s="3"/>
     </row>
-    <row r="297" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="297">
       <c r="A297" s="3"/>
       <c r="B297" s="3"/>
       <c r="C297" s="3"/>
@@ -9875,7 +9927,7 @@
       <c r="Z297" s="3"/>
       <c r="AA297" s="3"/>
     </row>
-    <row r="298" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="298">
       <c r="A298" s="3"/>
       <c r="B298" s="3"/>
       <c r="C298" s="3"/>
@@ -9904,7 +9956,7 @@
       <c r="Z298" s="3"/>
       <c r="AA298" s="3"/>
     </row>
-    <row r="299" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="299">
       <c r="A299" s="3"/>
       <c r="B299" s="3"/>
       <c r="C299" s="3"/>
@@ -9933,7 +9985,7 @@
       <c r="Z299" s="3"/>
       <c r="AA299" s="3"/>
     </row>
-    <row r="300" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="300">
       <c r="A300" s="3"/>
       <c r="B300" s="3"/>
       <c r="C300" s="3"/>
@@ -9962,7 +10014,7 @@
       <c r="Z300" s="3"/>
       <c r="AA300" s="3"/>
     </row>
-    <row r="301" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="301">
       <c r="A301" s="3"/>
       <c r="B301" s="3"/>
       <c r="C301" s="3"/>
@@ -9991,7 +10043,7 @@
       <c r="Z301" s="3"/>
       <c r="AA301" s="3"/>
     </row>
-    <row r="302" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="302">
       <c r="A302" s="3"/>
       <c r="B302" s="3"/>
       <c r="C302" s="3"/>
@@ -10020,7 +10072,7 @@
       <c r="Z302" s="3"/>
       <c r="AA302" s="3"/>
     </row>
-    <row r="303" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="303">
       <c r="A303" s="3"/>
       <c r="B303" s="3"/>
       <c r="C303" s="3"/>
@@ -10049,7 +10101,7 @@
       <c r="Z303" s="3"/>
       <c r="AA303" s="3"/>
     </row>
-    <row r="304" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="304">
       <c r="A304" s="3"/>
       <c r="B304" s="3"/>
       <c r="C304" s="3"/>
@@ -10078,7 +10130,7 @@
       <c r="Z304" s="3"/>
       <c r="AA304" s="3"/>
     </row>
-    <row r="305" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="305">
       <c r="A305" s="3"/>
       <c r="B305" s="3"/>
       <c r="C305" s="3"/>
@@ -10107,7 +10159,7 @@
       <c r="Z305" s="3"/>
       <c r="AA305" s="3"/>
     </row>
-    <row r="306" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="306">
       <c r="A306" s="3"/>
       <c r="B306" s="3"/>
       <c r="C306" s="3"/>
@@ -10136,7 +10188,7 @@
       <c r="Z306" s="3"/>
       <c r="AA306" s="3"/>
     </row>
-    <row r="307" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="307">
       <c r="A307" s="3"/>
       <c r="B307" s="3"/>
       <c r="C307" s="3"/>
@@ -10165,7 +10217,7 @@
       <c r="Z307" s="3"/>
       <c r="AA307" s="3"/>
     </row>
-    <row r="308" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="308">
       <c r="A308" s="3"/>
       <c r="B308" s="3"/>
       <c r="C308" s="3"/>
@@ -10194,7 +10246,7 @@
       <c r="Z308" s="3"/>
       <c r="AA308" s="3"/>
     </row>
-    <row r="309" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="309">
       <c r="A309" s="3"/>
       <c r="B309" s="3"/>
       <c r="C309" s="3"/>
@@ -10223,7 +10275,7 @@
       <c r="Z309" s="3"/>
       <c r="AA309" s="3"/>
     </row>
-    <row r="310" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="310">
       <c r="A310" s="3"/>
       <c r="B310" s="3"/>
       <c r="C310" s="3"/>
@@ -10252,7 +10304,7 @@
       <c r="Z310" s="3"/>
       <c r="AA310" s="3"/>
     </row>
-    <row r="311" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="311">
       <c r="A311" s="3"/>
       <c r="B311" s="3"/>
       <c r="C311" s="3"/>
@@ -10281,7 +10333,7 @@
       <c r="Z311" s="3"/>
       <c r="AA311" s="3"/>
     </row>
-    <row r="312" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="312">
       <c r="A312" s="3"/>
       <c r="B312" s="3"/>
       <c r="C312" s="3"/>
@@ -10310,7 +10362,7 @@
       <c r="Z312" s="3"/>
       <c r="AA312" s="3"/>
     </row>
-    <row r="313" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="313">
       <c r="A313" s="3"/>
       <c r="B313" s="3"/>
       <c r="C313" s="3"/>
@@ -10339,7 +10391,7 @@
       <c r="Z313" s="3"/>
       <c r="AA313" s="3"/>
     </row>
-    <row r="314" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="314">
       <c r="A314" s="3"/>
       <c r="B314" s="3"/>
       <c r="C314" s="3"/>
@@ -10368,7 +10420,7 @@
       <c r="Z314" s="3"/>
       <c r="AA314" s="3"/>
     </row>
-    <row r="315" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="315">
       <c r="A315" s="3"/>
       <c r="B315" s="3"/>
       <c r="C315" s="3"/>
@@ -10397,7 +10449,7 @@
       <c r="Z315" s="3"/>
       <c r="AA315" s="3"/>
     </row>
-    <row r="316" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="316">
       <c r="A316" s="3"/>
       <c r="B316" s="3"/>
       <c r="C316" s="3"/>
@@ -10426,7 +10478,7 @@
       <c r="Z316" s="3"/>
       <c r="AA316" s="3"/>
     </row>
-    <row r="317" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="317">
       <c r="A317" s="3"/>
       <c r="B317" s="3"/>
       <c r="C317" s="3"/>
@@ -10455,7 +10507,7 @@
       <c r="Z317" s="3"/>
       <c r="AA317" s="3"/>
     </row>
-    <row r="318" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="318">
       <c r="A318" s="3"/>
       <c r="B318" s="3"/>
       <c r="C318" s="3"/>
@@ -10484,7 +10536,7 @@
       <c r="Z318" s="3"/>
       <c r="AA318" s="3"/>
     </row>
-    <row r="319" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="319">
       <c r="A319" s="3"/>
       <c r="B319" s="3"/>
       <c r="C319" s="3"/>
@@ -10513,7 +10565,7 @@
       <c r="Z319" s="3"/>
       <c r="AA319" s="3"/>
     </row>
-    <row r="320" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="320">
       <c r="A320" s="3"/>
       <c r="B320" s="3"/>
       <c r="C320" s="3"/>
@@ -10542,7 +10594,7 @@
       <c r="Z320" s="3"/>
       <c r="AA320" s="3"/>
     </row>
-    <row r="321" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="321">
       <c r="A321" s="3"/>
       <c r="B321" s="3"/>
       <c r="C321" s="3"/>
@@ -10571,7 +10623,7 @@
       <c r="Z321" s="3"/>
       <c r="AA321" s="3"/>
     </row>
-    <row r="322" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="322">
       <c r="A322" s="3"/>
       <c r="B322" s="3"/>
       <c r="C322" s="3"/>
@@ -10600,7 +10652,7 @@
       <c r="Z322" s="3"/>
       <c r="AA322" s="3"/>
     </row>
-    <row r="323" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="323">
       <c r="A323" s="3"/>
       <c r="B323" s="3"/>
       <c r="C323" s="3"/>
@@ -10629,7 +10681,7 @@
       <c r="Z323" s="3"/>
       <c r="AA323" s="3"/>
     </row>
-    <row r="324" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="324">
       <c r="A324" s="3"/>
       <c r="B324" s="3"/>
       <c r="C324" s="3"/>
@@ -10658,7 +10710,7 @@
       <c r="Z324" s="3"/>
       <c r="AA324" s="3"/>
     </row>
-    <row r="325" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="325">
       <c r="A325" s="3"/>
       <c r="B325" s="3"/>
       <c r="C325" s="3"/>
@@ -10687,7 +10739,7 @@
       <c r="Z325" s="3"/>
       <c r="AA325" s="3"/>
     </row>
-    <row r="326" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="326">
       <c r="A326" s="3"/>
       <c r="B326" s="3"/>
       <c r="C326" s="3"/>
@@ -10716,7 +10768,7 @@
       <c r="Z326" s="3"/>
       <c r="AA326" s="3"/>
     </row>
-    <row r="327" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="327">
       <c r="A327" s="3"/>
       <c r="B327" s="3"/>
       <c r="C327" s="3"/>
@@ -10745,7 +10797,7 @@
       <c r="Z327" s="3"/>
       <c r="AA327" s="3"/>
     </row>
-    <row r="328" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="328">
       <c r="A328" s="3"/>
       <c r="B328" s="3"/>
       <c r="C328" s="3"/>
@@ -10774,7 +10826,7 @@
       <c r="Z328" s="3"/>
       <c r="AA328" s="3"/>
     </row>
-    <row r="329" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="329">
       <c r="A329" s="3"/>
       <c r="B329" s="3"/>
       <c r="C329" s="3"/>
@@ -10803,7 +10855,7 @@
       <c r="Z329" s="3"/>
       <c r="AA329" s="3"/>
     </row>
-    <row r="330" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="330">
       <c r="A330" s="3"/>
       <c r="B330" s="3"/>
       <c r="C330" s="3"/>
@@ -10832,7 +10884,7 @@
       <c r="Z330" s="3"/>
       <c r="AA330" s="3"/>
     </row>
-    <row r="331" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="331">
       <c r="A331" s="3"/>
       <c r="B331" s="3"/>
       <c r="C331" s="3"/>
@@ -10861,7 +10913,7 @@
       <c r="Z331" s="3"/>
       <c r="AA331" s="3"/>
     </row>
-    <row r="332" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="332">
       <c r="A332" s="3"/>
       <c r="B332" s="3"/>
       <c r="C332" s="3"/>
@@ -10890,7 +10942,7 @@
       <c r="Z332" s="3"/>
       <c r="AA332" s="3"/>
     </row>
-    <row r="333" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="333">
       <c r="A333" s="3"/>
       <c r="B333" s="3"/>
       <c r="C333" s="3"/>
@@ -10919,7 +10971,7 @@
       <c r="Z333" s="3"/>
       <c r="AA333" s="3"/>
     </row>
-    <row r="334" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="334">
       <c r="A334" s="3"/>
       <c r="B334" s="3"/>
       <c r="C334" s="3"/>
@@ -10948,7 +11000,7 @@
       <c r="Z334" s="3"/>
       <c r="AA334" s="3"/>
     </row>
-    <row r="335" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="335">
       <c r="A335" s="3"/>
       <c r="B335" s="3"/>
       <c r="C335" s="3"/>
@@ -10977,7 +11029,7 @@
       <c r="Z335" s="3"/>
       <c r="AA335" s="3"/>
     </row>
-    <row r="336" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="336">
       <c r="A336" s="3"/>
       <c r="B336" s="3"/>
       <c r="C336" s="3"/>
@@ -11006,7 +11058,7 @@
       <c r="Z336" s="3"/>
       <c r="AA336" s="3"/>
     </row>
-    <row r="337" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="337">
       <c r="A337" s="3"/>
       <c r="B337" s="3"/>
       <c r="C337" s="3"/>
@@ -11035,7 +11087,7 @@
       <c r="Z337" s="3"/>
       <c r="AA337" s="3"/>
     </row>
-    <row r="338" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="338">
       <c r="A338" s="3"/>
       <c r="B338" s="3"/>
       <c r="C338" s="3"/>
@@ -11064,7 +11116,7 @@
       <c r="Z338" s="3"/>
       <c r="AA338" s="3"/>
     </row>
-    <row r="339" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="339">
       <c r="A339" s="3"/>
       <c r="B339" s="3"/>
       <c r="C339" s="3"/>
@@ -11093,7 +11145,7 @@
       <c r="Z339" s="3"/>
       <c r="AA339" s="3"/>
     </row>
-    <row r="340" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="340">
       <c r="A340" s="3"/>
       <c r="B340" s="3"/>
       <c r="C340" s="3"/>
@@ -11122,7 +11174,7 @@
       <c r="Z340" s="3"/>
       <c r="AA340" s="3"/>
     </row>
-    <row r="341" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="341">
       <c r="A341" s="3"/>
       <c r="B341" s="3"/>
       <c r="C341" s="3"/>
@@ -11151,7 +11203,7 @@
       <c r="Z341" s="3"/>
       <c r="AA341" s="3"/>
     </row>
-    <row r="342" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="342">
       <c r="A342" s="3"/>
       <c r="B342" s="3"/>
       <c r="C342" s="3"/>
@@ -11180,7 +11232,7 @@
       <c r="Z342" s="3"/>
       <c r="AA342" s="3"/>
     </row>
-    <row r="343" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="343">
       <c r="A343" s="3"/>
       <c r="B343" s="3"/>
       <c r="C343" s="3"/>
@@ -11209,7 +11261,7 @@
       <c r="Z343" s="3"/>
       <c r="AA343" s="3"/>
     </row>
-    <row r="344" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="344">
       <c r="A344" s="3"/>
       <c r="B344" s="3"/>
       <c r="C344" s="3"/>
@@ -11238,7 +11290,7 @@
       <c r="Z344" s="3"/>
       <c r="AA344" s="3"/>
     </row>
-    <row r="345" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="345">
       <c r="A345" s="3"/>
       <c r="B345" s="3"/>
       <c r="C345" s="3"/>
@@ -11267,7 +11319,7 @@
       <c r="Z345" s="3"/>
       <c r="AA345" s="3"/>
     </row>
-    <row r="346" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="346">
       <c r="A346" s="3"/>
       <c r="B346" s="3"/>
       <c r="C346" s="3"/>
@@ -11296,7 +11348,7 @@
       <c r="Z346" s="3"/>
       <c r="AA346" s="3"/>
     </row>
-    <row r="347" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="347">
       <c r="A347" s="3"/>
       <c r="B347" s="3"/>
       <c r="C347" s="3"/>
@@ -11325,7 +11377,7 @@
       <c r="Z347" s="3"/>
       <c r="AA347" s="3"/>
     </row>
-    <row r="348" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="348">
       <c r="A348" s="3"/>
       <c r="B348" s="3"/>
       <c r="C348" s="3"/>
@@ -11354,7 +11406,7 @@
       <c r="Z348" s="3"/>
       <c r="AA348" s="3"/>
     </row>
-    <row r="349" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="349">
       <c r="A349" s="3"/>
       <c r="B349" s="3"/>
       <c r="C349" s="3"/>
@@ -11383,7 +11435,7 @@
       <c r="Z349" s="3"/>
       <c r="AA349" s="3"/>
     </row>
-    <row r="350" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="350">
       <c r="A350" s="3"/>
       <c r="B350" s="3"/>
       <c r="C350" s="3"/>
@@ -11412,7 +11464,7 @@
       <c r="Z350" s="3"/>
       <c r="AA350" s="3"/>
     </row>
-    <row r="351" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="351">
       <c r="A351" s="3"/>
       <c r="B351" s="3"/>
       <c r="C351" s="3"/>
@@ -11441,7 +11493,7 @@
       <c r="Z351" s="3"/>
       <c r="AA351" s="3"/>
     </row>
-    <row r="352" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="352">
       <c r="A352" s="3"/>
       <c r="B352" s="3"/>
       <c r="C352" s="3"/>
@@ -11470,7 +11522,7 @@
       <c r="Z352" s="3"/>
       <c r="AA352" s="3"/>
     </row>
-    <row r="353" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="353">
       <c r="A353" s="3"/>
       <c r="B353" s="3"/>
       <c r="C353" s="3"/>
@@ -11499,7 +11551,7 @@
       <c r="Z353" s="3"/>
       <c r="AA353" s="3"/>
     </row>
-    <row r="354" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="354">
       <c r="A354" s="3"/>
       <c r="B354" s="3"/>
       <c r="C354" s="3"/>
@@ -11528,7 +11580,7 @@
       <c r="Z354" s="3"/>
       <c r="AA354" s="3"/>
     </row>
-    <row r="355" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="355">
       <c r="A355" s="3"/>
       <c r="B355" s="3"/>
       <c r="C355" s="3"/>
@@ -11557,7 +11609,7 @@
       <c r="Z355" s="3"/>
       <c r="AA355" s="3"/>
     </row>
-    <row r="356" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="356">
       <c r="A356" s="3"/>
       <c r="B356" s="3"/>
       <c r="C356" s="3"/>
@@ -11586,7 +11638,7 @@
       <c r="Z356" s="3"/>
       <c r="AA356" s="3"/>
     </row>
-    <row r="357" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="357">
       <c r="A357" s="3"/>
       <c r="B357" s="3"/>
       <c r="C357" s="3"/>
@@ -11615,7 +11667,7 @@
       <c r="Z357" s="3"/>
       <c r="AA357" s="3"/>
     </row>
-    <row r="358" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="358">
       <c r="A358" s="3"/>
       <c r="B358" s="3"/>
       <c r="C358" s="3"/>
@@ -11644,7 +11696,7 @@
       <c r="Z358" s="3"/>
       <c r="AA358" s="3"/>
     </row>
-    <row r="359" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="359">
       <c r="A359" s="3"/>
       <c r="B359" s="3"/>
       <c r="C359" s="3"/>
@@ -11673,7 +11725,7 @@
       <c r="Z359" s="3"/>
       <c r="AA359" s="3"/>
     </row>
-    <row r="360" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="360">
       <c r="A360" s="3"/>
       <c r="B360" s="3"/>
       <c r="C360" s="3"/>
@@ -11702,7 +11754,7 @@
       <c r="Z360" s="3"/>
       <c r="AA360" s="3"/>
     </row>
-    <row r="361" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="361">
       <c r="A361" s="3"/>
       <c r="B361" s="3"/>
       <c r="C361" s="3"/>
@@ -11731,7 +11783,7 @@
       <c r="Z361" s="3"/>
       <c r="AA361" s="3"/>
     </row>
-    <row r="362" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="362">
       <c r="A362" s="3"/>
       <c r="B362" s="3"/>
       <c r="C362" s="3"/>
@@ -11760,7 +11812,7 @@
       <c r="Z362" s="3"/>
       <c r="AA362" s="3"/>
     </row>
-    <row r="363" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="363">
       <c r="A363" s="3"/>
       <c r="B363" s="3"/>
       <c r="C363" s="3"/>
@@ -11789,7 +11841,7 @@
       <c r="Z363" s="3"/>
       <c r="AA363" s="3"/>
     </row>
-    <row r="364" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="364">
       <c r="A364" s="3"/>
       <c r="B364" s="3"/>
       <c r="C364" s="3"/>
@@ -11818,7 +11870,7 @@
       <c r="Z364" s="3"/>
       <c r="AA364" s="3"/>
     </row>
-    <row r="365" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="365">
       <c r="A365" s="3"/>
       <c r="B365" s="3"/>
       <c r="C365" s="3"/>
@@ -11847,7 +11899,7 @@
       <c r="Z365" s="3"/>
       <c r="AA365" s="3"/>
     </row>
-    <row r="366" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="366">
       <c r="A366" s="3"/>
       <c r="B366" s="3"/>
       <c r="C366" s="3"/>
@@ -11876,7 +11928,7 @@
       <c r="Z366" s="3"/>
       <c r="AA366" s="3"/>
     </row>
-    <row r="367" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="367">
       <c r="A367" s="3"/>
       <c r="B367" s="3"/>
       <c r="C367" s="3"/>
@@ -11905,7 +11957,7 @@
       <c r="Z367" s="3"/>
       <c r="AA367" s="3"/>
     </row>
-    <row r="368" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="368">
       <c r="A368" s="3"/>
       <c r="B368" s="3"/>
       <c r="C368" s="3"/>
@@ -11934,7 +11986,7 @@
       <c r="Z368" s="3"/>
       <c r="AA368" s="3"/>
     </row>
-    <row r="369" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="369">
       <c r="A369" s="3"/>
       <c r="B369" s="3"/>
       <c r="C369" s="3"/>
@@ -11963,7 +12015,7 @@
       <c r="Z369" s="3"/>
       <c r="AA369" s="3"/>
     </row>
-    <row r="370" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="370">
       <c r="A370" s="3"/>
       <c r="B370" s="3"/>
       <c r="C370" s="3"/>
@@ -11992,7 +12044,7 @@
       <c r="Z370" s="3"/>
       <c r="AA370" s="3"/>
     </row>
-    <row r="371" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="371">
       <c r="A371" s="3"/>
       <c r="B371" s="3"/>
       <c r="C371" s="3"/>
@@ -12021,7 +12073,7 @@
       <c r="Z371" s="3"/>
       <c r="AA371" s="3"/>
     </row>
-    <row r="372" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="372">
       <c r="A372" s="3"/>
       <c r="B372" s="3"/>
       <c r="C372" s="3"/>
@@ -12050,7 +12102,7 @@
       <c r="Z372" s="3"/>
       <c r="AA372" s="3"/>
     </row>
-    <row r="373" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="373">
       <c r="A373" s="3"/>
       <c r="B373" s="3"/>
       <c r="C373" s="3"/>
@@ -12079,7 +12131,7 @@
       <c r="Z373" s="3"/>
       <c r="AA373" s="3"/>
     </row>
-    <row r="374" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="374">
       <c r="A374" s="3"/>
       <c r="B374" s="3"/>
       <c r="C374" s="3"/>
@@ -12108,7 +12160,7 @@
       <c r="Z374" s="3"/>
       <c r="AA374" s="3"/>
     </row>
-    <row r="375" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="375">
       <c r="A375" s="3"/>
       <c r="B375" s="3"/>
       <c r="C375" s="3"/>
@@ -12137,7 +12189,7 @@
       <c r="Z375" s="3"/>
       <c r="AA375" s="3"/>
     </row>
-    <row r="376" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="376">
       <c r="A376" s="3"/>
       <c r="B376" s="3"/>
       <c r="C376" s="3"/>
@@ -12166,7 +12218,7 @@
       <c r="Z376" s="3"/>
       <c r="AA376" s="3"/>
     </row>
-    <row r="377" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="377">
       <c r="A377" s="3"/>
       <c r="B377" s="3"/>
       <c r="C377" s="3"/>
@@ -12195,7 +12247,7 @@
       <c r="Z377" s="3"/>
       <c r="AA377" s="3"/>
     </row>
-    <row r="378" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="378">
       <c r="A378" s="3"/>
       <c r="B378" s="3"/>
       <c r="C378" s="3"/>
@@ -12224,7 +12276,7 @@
       <c r="Z378" s="3"/>
       <c r="AA378" s="3"/>
     </row>
-    <row r="379" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="379">
       <c r="A379" s="3"/>
       <c r="B379" s="3"/>
       <c r="C379" s="3"/>
@@ -12253,7 +12305,7 @@
       <c r="Z379" s="3"/>
       <c r="AA379" s="3"/>
     </row>
-    <row r="380" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="380">
       <c r="A380" s="3"/>
       <c r="B380" s="3"/>
       <c r="C380" s="3"/>
@@ -12282,7 +12334,7 @@
       <c r="Z380" s="3"/>
       <c r="AA380" s="3"/>
     </row>
-    <row r="381" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="381">
       <c r="A381" s="3"/>
       <c r="B381" s="3"/>
       <c r="C381" s="3"/>
@@ -12311,7 +12363,7 @@
       <c r="Z381" s="3"/>
       <c r="AA381" s="3"/>
     </row>
-    <row r="382" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="382">
       <c r="A382" s="3"/>
       <c r="B382" s="3"/>
       <c r="C382" s="3"/>
@@ -12340,7 +12392,7 @@
       <c r="Z382" s="3"/>
       <c r="AA382" s="3"/>
     </row>
-    <row r="383" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="383">
       <c r="A383" s="3"/>
       <c r="B383" s="3"/>
       <c r="C383" s="3"/>
@@ -12369,7 +12421,7 @@
       <c r="Z383" s="3"/>
       <c r="AA383" s="3"/>
     </row>
-    <row r="384" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="384">
       <c r="A384" s="3"/>
       <c r="B384" s="3"/>
       <c r="C384" s="3"/>
@@ -12398,7 +12450,7 @@
       <c r="Z384" s="3"/>
       <c r="AA384" s="3"/>
     </row>
-    <row r="385" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="385">
       <c r="A385" s="3"/>
       <c r="B385" s="3"/>
       <c r="C385" s="3"/>
@@ -12427,7 +12479,7 @@
       <c r="Z385" s="3"/>
       <c r="AA385" s="3"/>
     </row>
-    <row r="386" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="386">
       <c r="A386" s="3"/>
       <c r="B386" s="3"/>
       <c r="C386" s="3"/>
@@ -12456,7 +12508,7 @@
       <c r="Z386" s="3"/>
       <c r="AA386" s="3"/>
     </row>
-    <row r="387" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="387">
       <c r="A387" s="3"/>
       <c r="B387" s="3"/>
       <c r="C387" s="3"/>
@@ -12485,7 +12537,7 @@
       <c r="Z387" s="3"/>
       <c r="AA387" s="3"/>
     </row>
-    <row r="388" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="388">
       <c r="A388" s="3"/>
       <c r="B388" s="3"/>
       <c r="C388" s="3"/>
@@ -12514,7 +12566,7 @@
       <c r="Z388" s="3"/>
       <c r="AA388" s="3"/>
     </row>
-    <row r="389" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="389">
       <c r="A389" s="3"/>
       <c r="B389" s="3"/>
       <c r="C389" s="3"/>
@@ -12543,7 +12595,7 @@
       <c r="Z389" s="3"/>
       <c r="AA389" s="3"/>
     </row>
-    <row r="390" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="390">
       <c r="A390" s="3"/>
       <c r="B390" s="3"/>
       <c r="C390" s="3"/>
@@ -12572,7 +12624,7 @@
       <c r="Z390" s="3"/>
       <c r="AA390" s="3"/>
     </row>
-    <row r="391" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="391">
       <c r="A391" s="3"/>
       <c r="B391" s="3"/>
       <c r="C391" s="3"/>
@@ -12601,7 +12653,7 @@
       <c r="Z391" s="3"/>
       <c r="AA391" s="3"/>
     </row>
-    <row r="392" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="392">
       <c r="A392" s="3"/>
       <c r="B392" s="3"/>
       <c r="C392" s="3"/>
@@ -12630,7 +12682,7 @@
       <c r="Z392" s="3"/>
       <c r="AA392" s="3"/>
     </row>
-    <row r="393" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="393">
       <c r="A393" s="3"/>
       <c r="B393" s="3"/>
       <c r="C393" s="3"/>
@@ -12659,7 +12711,7 @@
       <c r="Z393" s="3"/>
       <c r="AA393" s="3"/>
     </row>
-    <row r="394" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="394">
       <c r="A394" s="3"/>
       <c r="B394" s="3"/>
       <c r="C394" s="3"/>
@@ -12688,7 +12740,7 @@
       <c r="Z394" s="3"/>
       <c r="AA394" s="3"/>
     </row>
-    <row r="395" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="395">
       <c r="A395" s="3"/>
       <c r="B395" s="3"/>
       <c r="C395" s="3"/>
@@ -12717,7 +12769,7 @@
       <c r="Z395" s="3"/>
       <c r="AA395" s="3"/>
     </row>
-    <row r="396" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="396">
       <c r="A396" s="3"/>
       <c r="B396" s="3"/>
       <c r="C396" s="3"/>
@@ -12746,7 +12798,7 @@
       <c r="Z396" s="3"/>
       <c r="AA396" s="3"/>
     </row>
-    <row r="397" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="397">
       <c r="A397" s="3"/>
       <c r="B397" s="3"/>
       <c r="C397" s="3"/>
@@ -12775,7 +12827,7 @@
       <c r="Z397" s="3"/>
       <c r="AA397" s="3"/>
     </row>
-    <row r="398" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="398">
       <c r="A398" s="3"/>
       <c r="B398" s="3"/>
       <c r="C398" s="3"/>
@@ -12804,7 +12856,7 @@
       <c r="Z398" s="3"/>
       <c r="AA398" s="3"/>
     </row>
-    <row r="399" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="399">
       <c r="A399" s="3"/>
       <c r="B399" s="3"/>
       <c r="C399" s="3"/>
@@ -12833,7 +12885,7 @@
       <c r="Z399" s="3"/>
       <c r="AA399" s="3"/>
     </row>
-    <row r="400" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="400">
       <c r="A400" s="3"/>
       <c r="B400" s="3"/>
       <c r="C400" s="3"/>
@@ -12862,7 +12914,7 @@
       <c r="Z400" s="3"/>
       <c r="AA400" s="3"/>
     </row>
-    <row r="401" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="401">
       <c r="A401" s="3"/>
       <c r="B401" s="3"/>
       <c r="C401" s="3"/>
@@ -12891,7 +12943,7 @@
       <c r="Z401" s="3"/>
       <c r="AA401" s="3"/>
     </row>
-    <row r="402" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="402">
       <c r="A402" s="3"/>
       <c r="B402" s="3"/>
       <c r="C402" s="3"/>
@@ -12920,7 +12972,7 @@
       <c r="Z402" s="3"/>
       <c r="AA402" s="3"/>
     </row>
-    <row r="403" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="403">
       <c r="A403" s="3"/>
       <c r="B403" s="3"/>
       <c r="C403" s="3"/>
@@ -12949,7 +13001,7 @@
       <c r="Z403" s="3"/>
       <c r="AA403" s="3"/>
     </row>
-    <row r="404" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="404">
       <c r="A404" s="3"/>
       <c r="B404" s="3"/>
       <c r="C404" s="3"/>
@@ -12978,7 +13030,7 @@
       <c r="Z404" s="3"/>
       <c r="AA404" s="3"/>
     </row>
-    <row r="405" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="405">
       <c r="A405" s="3"/>
       <c r="B405" s="3"/>
       <c r="C405" s="3"/>
@@ -13007,7 +13059,7 @@
       <c r="Z405" s="3"/>
       <c r="AA405" s="3"/>
     </row>
-    <row r="406" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="406">
       <c r="A406" s="3"/>
       <c r="B406" s="3"/>
       <c r="C406" s="3"/>
@@ -13036,7 +13088,7 @@
       <c r="Z406" s="3"/>
       <c r="AA406" s="3"/>
     </row>
-    <row r="407" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="407">
       <c r="A407" s="3"/>
       <c r="B407" s="3"/>
       <c r="C407" s="3"/>
@@ -13065,7 +13117,7 @@
       <c r="Z407" s="3"/>
       <c r="AA407" s="3"/>
     </row>
-    <row r="408" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="408">
       <c r="A408" s="3"/>
       <c r="B408" s="3"/>
       <c r="C408" s="3"/>
@@ -13094,7 +13146,7 @@
       <c r="Z408" s="3"/>
       <c r="AA408" s="3"/>
     </row>
-    <row r="409" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="409">
       <c r="A409" s="3"/>
       <c r="B409" s="3"/>
       <c r="C409" s="3"/>
@@ -13123,7 +13175,7 @@
       <c r="Z409" s="3"/>
       <c r="AA409" s="3"/>
     </row>
-    <row r="410" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="410">
       <c r="A410" s="3"/>
       <c r="B410" s="3"/>
       <c r="C410" s="3"/>
@@ -13152,7 +13204,7 @@
       <c r="Z410" s="3"/>
       <c r="AA410" s="3"/>
     </row>
-    <row r="411" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="411">
       <c r="A411" s="3"/>
       <c r="B411" s="3"/>
       <c r="C411" s="3"/>
@@ -13181,7 +13233,7 @@
       <c r="Z411" s="3"/>
       <c r="AA411" s="3"/>
     </row>
-    <row r="412" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="412">
       <c r="A412" s="3"/>
       <c r="B412" s="3"/>
       <c r="C412" s="3"/>
@@ -13210,7 +13262,7 @@
       <c r="Z412" s="3"/>
       <c r="AA412" s="3"/>
     </row>
-    <row r="413" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="413">
       <c r="A413" s="3"/>
       <c r="B413" s="3"/>
       <c r="C413" s="3"/>
@@ -13239,7 +13291,7 @@
       <c r="Z413" s="3"/>
       <c r="AA413" s="3"/>
     </row>
-    <row r="414" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="414">
       <c r="A414" s="3"/>
       <c r="B414" s="3"/>
       <c r="C414" s="3"/>
@@ -13268,7 +13320,7 @@
       <c r="Z414" s="3"/>
       <c r="AA414" s="3"/>
     </row>
-    <row r="415" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="415">
       <c r="A415" s="3"/>
       <c r="B415" s="3"/>
       <c r="C415" s="3"/>
@@ -13297,7 +13349,7 @@
       <c r="Z415" s="3"/>
       <c r="AA415" s="3"/>
     </row>
-    <row r="416" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="416">
       <c r="A416" s="3"/>
       <c r="B416" s="3"/>
       <c r="C416" s="3"/>
@@ -13326,7 +13378,7 @@
       <c r="Z416" s="3"/>
       <c r="AA416" s="3"/>
     </row>
-    <row r="417" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="417">
       <c r="A417" s="3"/>
       <c r="B417" s="3"/>
       <c r="C417" s="3"/>
@@ -13355,7 +13407,7 @@
       <c r="Z417" s="3"/>
       <c r="AA417" s="3"/>
     </row>
-    <row r="418" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="418">
       <c r="A418" s="3"/>
       <c r="B418" s="3"/>
       <c r="C418" s="3"/>
@@ -13384,7 +13436,7 @@
       <c r="Z418" s="3"/>
       <c r="AA418" s="3"/>
     </row>
-    <row r="419" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="419">
       <c r="A419" s="3"/>
       <c r="B419" s="3"/>
       <c r="C419" s="3"/>
@@ -13413,7 +13465,7 @@
       <c r="Z419" s="3"/>
       <c r="AA419" s="3"/>
     </row>
-    <row r="420" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="420">
       <c r="A420" s="3"/>
       <c r="B420" s="3"/>
       <c r="C420" s="3"/>
@@ -13442,7 +13494,7 @@
       <c r="Z420" s="3"/>
       <c r="AA420" s="3"/>
     </row>
-    <row r="421" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="421">
       <c r="A421" s="3"/>
       <c r="B421" s="3"/>
       <c r="C421" s="3"/>
@@ -13471,7 +13523,7 @@
       <c r="Z421" s="3"/>
       <c r="AA421" s="3"/>
     </row>
-    <row r="422" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="422">
       <c r="A422" s="3"/>
       <c r="B422" s="3"/>
       <c r="C422" s="3"/>
@@ -13500,7 +13552,7 @@
       <c r="Z422" s="3"/>
       <c r="AA422" s="3"/>
     </row>
-    <row r="423" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="423">
       <c r="A423" s="3"/>
       <c r="B423" s="3"/>
       <c r="C423" s="3"/>
@@ -13529,7 +13581,7 @@
       <c r="Z423" s="3"/>
       <c r="AA423" s="3"/>
     </row>
-    <row r="424" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="424">
       <c r="A424" s="3"/>
       <c r="B424" s="3"/>
       <c r="C424" s="3"/>
@@ -13558,7 +13610,7 @@
       <c r="Z424" s="3"/>
       <c r="AA424" s="3"/>
     </row>
-    <row r="425" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="425">
       <c r="A425" s="3"/>
       <c r="B425" s="3"/>
       <c r="C425" s="3"/>
@@ -13587,7 +13639,7 @@
       <c r="Z425" s="3"/>
       <c r="AA425" s="3"/>
     </row>
-    <row r="426" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="426">
       <c r="A426" s="3"/>
       <c r="B426" s="3"/>
       <c r="C426" s="3"/>
@@ -13616,7 +13668,7 @@
       <c r="Z426" s="3"/>
       <c r="AA426" s="3"/>
     </row>
-    <row r="427" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="427">
       <c r="A427" s="3"/>
       <c r="B427" s="3"/>
       <c r="C427" s="3"/>
@@ -13645,7 +13697,7 @@
       <c r="Z427" s="3"/>
       <c r="AA427" s="3"/>
     </row>
-    <row r="428" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="428">
       <c r="A428" s="3"/>
       <c r="B428" s="3"/>
       <c r="C428" s="3"/>
@@ -13674,7 +13726,7 @@
       <c r="Z428" s="3"/>
       <c r="AA428" s="3"/>
     </row>
-    <row r="429" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="429">
       <c r="A429" s="3"/>
       <c r="B429" s="3"/>
       <c r="C429" s="3"/>
@@ -13703,7 +13755,7 @@
       <c r="Z429" s="3"/>
       <c r="AA429" s="3"/>
     </row>
-    <row r="430" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="430">
       <c r="A430" s="3"/>
       <c r="B430" s="3"/>
       <c r="C430" s="3"/>
@@ -13732,7 +13784,7 @@
       <c r="Z430" s="3"/>
       <c r="AA430" s="3"/>
     </row>
-    <row r="431" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="431">
       <c r="A431" s="3"/>
       <c r="B431" s="3"/>
       <c r="C431" s="3"/>
@@ -13761,7 +13813,7 @@
       <c r="Z431" s="3"/>
       <c r="AA431" s="3"/>
     </row>
-    <row r="432" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="432">
       <c r="A432" s="3"/>
       <c r="B432" s="3"/>
       <c r="C432" s="3"/>
@@ -13790,7 +13842,7 @@
       <c r="Z432" s="3"/>
       <c r="AA432" s="3"/>
     </row>
-    <row r="433" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="433">
       <c r="A433" s="3"/>
       <c r="B433" s="3"/>
       <c r="C433" s="3"/>
@@ -13819,7 +13871,7 @@
       <c r="Z433" s="3"/>
       <c r="AA433" s="3"/>
     </row>
-    <row r="434" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="434">
       <c r="A434" s="3"/>
       <c r="B434" s="3"/>
       <c r="C434" s="3"/>
@@ -13848,7 +13900,7 @@
       <c r="Z434" s="3"/>
       <c r="AA434" s="3"/>
     </row>
-    <row r="435" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="435">
       <c r="A435" s="3"/>
       <c r="B435" s="3"/>
       <c r="C435" s="3"/>
@@ -13877,7 +13929,7 @@
       <c r="Z435" s="3"/>
       <c r="AA435" s="3"/>
     </row>
-    <row r="436" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="436">
       <c r="A436" s="3"/>
       <c r="B436" s="3"/>
       <c r="C436" s="3"/>
@@ -13906,7 +13958,7 @@
       <c r="Z436" s="3"/>
       <c r="AA436" s="3"/>
     </row>
-    <row r="437" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="437">
       <c r="A437" s="3"/>
       <c r="B437" s="3"/>
       <c r="C437" s="3"/>
@@ -13935,7 +13987,7 @@
       <c r="Z437" s="3"/>
       <c r="AA437" s="3"/>
     </row>
-    <row r="438" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="438">
       <c r="A438" s="3"/>
       <c r="B438" s="3"/>
       <c r="C438" s="3"/>
@@ -13964,7 +14016,7 @@
       <c r="Z438" s="3"/>
       <c r="AA438" s="3"/>
     </row>
-    <row r="439" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="439">
       <c r="A439" s="3"/>
       <c r="B439" s="3"/>
       <c r="C439" s="3"/>
@@ -13993,7 +14045,7 @@
       <c r="Z439" s="3"/>
       <c r="AA439" s="3"/>
     </row>
-    <row r="440" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="440">
       <c r="A440" s="3"/>
       <c r="B440" s="3"/>
       <c r="C440" s="3"/>
@@ -14022,7 +14074,7 @@
       <c r="Z440" s="3"/>
       <c r="AA440" s="3"/>
     </row>
-    <row r="441" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="441">
       <c r="A441" s="3"/>
       <c r="B441" s="3"/>
       <c r="C441" s="3"/>
@@ -14051,7 +14103,7 @@
       <c r="Z441" s="3"/>
       <c r="AA441" s="3"/>
     </row>
-    <row r="442" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="442">
       <c r="A442" s="3"/>
       <c r="B442" s="3"/>
       <c r="C442" s="3"/>
@@ -14080,7 +14132,7 @@
       <c r="Z442" s="3"/>
       <c r="AA442" s="3"/>
     </row>
-    <row r="443" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="443">
       <c r="A443" s="3"/>
       <c r="B443" s="3"/>
       <c r="C443" s="3"/>
@@ -14109,7 +14161,7 @@
       <c r="Z443" s="3"/>
       <c r="AA443" s="3"/>
     </row>
-    <row r="444" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="444">
       <c r="A444" s="3"/>
       <c r="B444" s="3"/>
       <c r="C444" s="3"/>
@@ -14138,7 +14190,7 @@
       <c r="Z444" s="3"/>
       <c r="AA444" s="3"/>
     </row>
-    <row r="445" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="445">
       <c r="A445" s="3"/>
       <c r="B445" s="3"/>
       <c r="C445" s="3"/>
@@ -14167,7 +14219,7 @@
       <c r="Z445" s="3"/>
       <c r="AA445" s="3"/>
     </row>
-    <row r="446" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="446">
       <c r="A446" s="3"/>
       <c r="B446" s="3"/>
       <c r="C446" s="3"/>
@@ -14196,7 +14248,7 @@
       <c r="Z446" s="3"/>
       <c r="AA446" s="3"/>
     </row>
-    <row r="447" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="447">
       <c r="A447" s="3"/>
       <c r="B447" s="3"/>
       <c r="C447" s="3"/>
@@ -14225,7 +14277,7 @@
       <c r="Z447" s="3"/>
       <c r="AA447" s="3"/>
     </row>
-    <row r="448" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="448">
       <c r="A448" s="3"/>
       <c r="B448" s="3"/>
       <c r="C448" s="3"/>
@@ -14254,7 +14306,7 @@
       <c r="Z448" s="3"/>
       <c r="AA448" s="3"/>
     </row>
-    <row r="449" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="449">
       <c r="A449" s="3"/>
       <c r="B449" s="3"/>
       <c r="C449" s="3"/>
@@ -14283,7 +14335,7 @@
       <c r="Z449" s="3"/>
       <c r="AA449" s="3"/>
     </row>
-    <row r="450" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="450">
       <c r="A450" s="3"/>
       <c r="B450" s="3"/>
       <c r="C450" s="3"/>
@@ -14312,7 +14364,7 @@
       <c r="Z450" s="3"/>
       <c r="AA450" s="3"/>
     </row>
-    <row r="451" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="451">
       <c r="A451" s="3"/>
       <c r="B451" s="3"/>
       <c r="C451" s="3"/>
@@ -14341,7 +14393,7 @@
       <c r="Z451" s="3"/>
       <c r="AA451" s="3"/>
     </row>
-    <row r="452" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="452">
       <c r="A452" s="3"/>
       <c r="B452" s="3"/>
       <c r="C452" s="3"/>
@@ -14370,7 +14422,7 @@
       <c r="Z452" s="3"/>
       <c r="AA452" s="3"/>
     </row>
-    <row r="453" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="453">
       <c r="A453" s="3"/>
       <c r="B453" s="3"/>
       <c r="C453" s="3"/>
@@ -14399,7 +14451,7 @@
       <c r="Z453" s="3"/>
       <c r="AA453" s="3"/>
     </row>
-    <row r="454" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="454">
       <c r="A454" s="3"/>
       <c r="B454" s="3"/>
       <c r="C454" s="3"/>
@@ -14428,7 +14480,7 @@
       <c r="Z454" s="3"/>
       <c r="AA454" s="3"/>
     </row>
-    <row r="455" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="455">
       <c r="A455" s="3"/>
       <c r="B455" s="3"/>
       <c r="C455" s="3"/>
@@ -14457,7 +14509,7 @@
       <c r="Z455" s="3"/>
       <c r="AA455" s="3"/>
     </row>
-    <row r="456" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="456">
       <c r="A456" s="3"/>
       <c r="B456" s="3"/>
       <c r="C456" s="3"/>
@@ -14486,7 +14538,7 @@
       <c r="Z456" s="3"/>
       <c r="AA456" s="3"/>
     </row>
-    <row r="457" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="457">
       <c r="A457" s="3"/>
       <c r="B457" s="3"/>
       <c r="C457" s="3"/>
@@ -14515,7 +14567,7 @@
       <c r="Z457" s="3"/>
       <c r="AA457" s="3"/>
     </row>
-    <row r="458" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="458">
       <c r="A458" s="3"/>
       <c r="B458" s="3"/>
       <c r="C458" s="3"/>
@@ -14544,7 +14596,7 @@
       <c r="Z458" s="3"/>
       <c r="AA458" s="3"/>
     </row>
-    <row r="459" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="459">
       <c r="A459" s="3"/>
       <c r="B459" s="3"/>
       <c r="C459" s="3"/>
@@ -14573,7 +14625,7 @@
       <c r="Z459" s="3"/>
       <c r="AA459" s="3"/>
     </row>
-    <row r="460" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="460">
       <c r="A460" s="3"/>
       <c r="B460" s="3"/>
       <c r="C460" s="3"/>
@@ -14602,7 +14654,7 @@
       <c r="Z460" s="3"/>
       <c r="AA460" s="3"/>
     </row>
-    <row r="461" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="461">
       <c r="A461" s="3"/>
       <c r="B461" s="3"/>
       <c r="C461" s="3"/>
@@ -14631,7 +14683,7 @@
       <c r="Z461" s="3"/>
       <c r="AA461" s="3"/>
     </row>
-    <row r="462" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="462">
       <c r="A462" s="3"/>
       <c r="B462" s="3"/>
       <c r="C462" s="3"/>
@@ -14660,7 +14712,7 @@
       <c r="Z462" s="3"/>
       <c r="AA462" s="3"/>
     </row>
-    <row r="463" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="463">
       <c r="A463" s="3"/>
       <c r="B463" s="3"/>
       <c r="C463" s="3"/>
@@ -14689,7 +14741,7 @@
       <c r="Z463" s="3"/>
       <c r="AA463" s="3"/>
     </row>
-    <row r="464" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="464">
       <c r="A464" s="3"/>
       <c r="B464" s="3"/>
       <c r="C464" s="3"/>
@@ -14718,7 +14770,7 @@
       <c r="Z464" s="3"/>
       <c r="AA464" s="3"/>
     </row>
-    <row r="465" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="465">
       <c r="A465" s="3"/>
       <c r="B465" s="3"/>
       <c r="C465" s="3"/>
@@ -14747,7 +14799,7 @@
       <c r="Z465" s="3"/>
       <c r="AA465" s="3"/>
     </row>
-    <row r="466" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="466">
       <c r="A466" s="3"/>
       <c r="B466" s="3"/>
       <c r="C466" s="3"/>
@@ -14776,7 +14828,7 @@
       <c r="Z466" s="3"/>
       <c r="AA466" s="3"/>
     </row>
-    <row r="467" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="467">
       <c r="A467" s="3"/>
       <c r="B467" s="3"/>
       <c r="C467" s="3"/>
@@ -14805,7 +14857,7 @@
       <c r="Z467" s="3"/>
       <c r="AA467" s="3"/>
     </row>
-    <row r="468" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="468">
       <c r="A468" s="3"/>
       <c r="B468" s="3"/>
       <c r="C468" s="3"/>
@@ -14834,7 +14886,7 @@
       <c r="Z468" s="3"/>
       <c r="AA468" s="3"/>
     </row>
-    <row r="469" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="469">
       <c r="A469" s="3"/>
       <c r="B469" s="3"/>
       <c r="C469" s="3"/>
@@ -14863,7 +14915,7 @@
       <c r="Z469" s="3"/>
       <c r="AA469" s="3"/>
     </row>
-    <row r="470" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="470">
       <c r="A470" s="3"/>
       <c r="B470" s="3"/>
       <c r="C470" s="3"/>
@@ -14892,7 +14944,7 @@
       <c r="Z470" s="3"/>
       <c r="AA470" s="3"/>
     </row>
-    <row r="471" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="471">
       <c r="A471" s="3"/>
       <c r="B471" s="3"/>
       <c r="C471" s="3"/>
@@ -14921,7 +14973,7 @@
       <c r="Z471" s="3"/>
       <c r="AA471" s="3"/>
     </row>
-    <row r="472" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="472">
       <c r="A472" s="3"/>
       <c r="B472" s="3"/>
       <c r="C472" s="3"/>
@@ -14950,7 +15002,7 @@
       <c r="Z472" s="3"/>
       <c r="AA472" s="3"/>
     </row>
-    <row r="473" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="473">
       <c r="A473" s="3"/>
       <c r="B473" s="3"/>
       <c r="C473" s="3"/>
@@ -14979,7 +15031,7 @@
       <c r="Z473" s="3"/>
       <c r="AA473" s="3"/>
     </row>
-    <row r="474" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="474">
       <c r="A474" s="3"/>
       <c r="B474" s="3"/>
       <c r="C474" s="3"/>
@@ -15008,7 +15060,7 @@
       <c r="Z474" s="3"/>
       <c r="AA474" s="3"/>
     </row>
-    <row r="475" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="475">
       <c r="A475" s="3"/>
       <c r="B475" s="3"/>
       <c r="C475" s="3"/>
@@ -15037,7 +15089,7 @@
       <c r="Z475" s="3"/>
       <c r="AA475" s="3"/>
     </row>
-    <row r="476" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="476">
       <c r="A476" s="3"/>
       <c r="B476" s="3"/>
       <c r="C476" s="3"/>
@@ -15066,7 +15118,7 @@
       <c r="Z476" s="3"/>
       <c r="AA476" s="3"/>
     </row>
-    <row r="477" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="477">
       <c r="A477" s="3"/>
       <c r="B477" s="3"/>
       <c r="C477" s="3"/>
@@ -15095,7 +15147,7 @@
       <c r="Z477" s="3"/>
       <c r="AA477" s="3"/>
     </row>
-    <row r="478" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="478">
       <c r="A478" s="3"/>
       <c r="B478" s="3"/>
       <c r="C478" s="3"/>
@@ -15124,7 +15176,7 @@
       <c r="Z478" s="3"/>
       <c r="AA478" s="3"/>
     </row>
-    <row r="479" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="479">
       <c r="A479" s="3"/>
       <c r="B479" s="3"/>
       <c r="C479" s="3"/>
@@ -15153,7 +15205,7 @@
       <c r="Z479" s="3"/>
       <c r="AA479" s="3"/>
     </row>
-    <row r="480" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="480">
       <c r="A480" s="3"/>
       <c r="B480" s="3"/>
       <c r="C480" s="3"/>
@@ -15182,7 +15234,7 @@
       <c r="Z480" s="3"/>
       <c r="AA480" s="3"/>
     </row>
-    <row r="481" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="481">
       <c r="A481" s="3"/>
       <c r="B481" s="3"/>
       <c r="C481" s="3"/>
@@ -15211,7 +15263,7 @@
       <c r="Z481" s="3"/>
       <c r="AA481" s="3"/>
     </row>
-    <row r="482" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="482">
       <c r="A482" s="3"/>
       <c r="B482" s="3"/>
       <c r="C482" s="3"/>
@@ -15240,7 +15292,7 @@
       <c r="Z482" s="3"/>
       <c r="AA482" s="3"/>
     </row>
-    <row r="483" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="483">
       <c r="A483" s="3"/>
       <c r="B483" s="3"/>
       <c r="C483" s="3"/>
@@ -15269,7 +15321,7 @@
       <c r="Z483" s="3"/>
       <c r="AA483" s="3"/>
     </row>
-    <row r="484" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="484">
       <c r="A484" s="3"/>
       <c r="B484" s="3"/>
       <c r="C484" s="3"/>
@@ -15298,7 +15350,7 @@
       <c r="Z484" s="3"/>
       <c r="AA484" s="3"/>
     </row>
-    <row r="485" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="485">
       <c r="A485" s="3"/>
       <c r="B485" s="3"/>
       <c r="C485" s="3"/>
@@ -15327,7 +15379,7 @@
       <c r="Z485" s="3"/>
       <c r="AA485" s="3"/>
     </row>
-    <row r="486" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="486">
       <c r="A486" s="3"/>
       <c r="B486" s="3"/>
       <c r="C486" s="3"/>
@@ -15356,7 +15408,7 @@
       <c r="Z486" s="3"/>
       <c r="AA486" s="3"/>
     </row>
-    <row r="487" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="487">
       <c r="A487" s="3"/>
       <c r="B487" s="3"/>
       <c r="C487" s="3"/>
@@ -15385,7 +15437,7 @@
       <c r="Z487" s="3"/>
       <c r="AA487" s="3"/>
     </row>
-    <row r="488" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="488">
       <c r="A488" s="3"/>
       <c r="B488" s="3"/>
       <c r="C488" s="3"/>
@@ -15414,7 +15466,7 @@
       <c r="Z488" s="3"/>
       <c r="AA488" s="3"/>
     </row>
-    <row r="489" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="489">
       <c r="A489" s="3"/>
       <c r="B489" s="3"/>
       <c r="C489" s="3"/>
@@ -15443,7 +15495,7 @@
       <c r="Z489" s="3"/>
       <c r="AA489" s="3"/>
     </row>
-    <row r="490" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="490">
       <c r="A490" s="3"/>
       <c r="B490" s="3"/>
       <c r="C490" s="3"/>
@@ -15472,7 +15524,7 @@
       <c r="Z490" s="3"/>
       <c r="AA490" s="3"/>
     </row>
-    <row r="491" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="491">
       <c r="A491" s="3"/>
       <c r="B491" s="3"/>
       <c r="C491" s="3"/>
@@ -15501,7 +15553,7 @@
       <c r="Z491" s="3"/>
       <c r="AA491" s="3"/>
     </row>
-    <row r="492" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="492">
       <c r="A492" s="3"/>
       <c r="B492" s="3"/>
       <c r="C492" s="3"/>
@@ -15530,7 +15582,7 @@
       <c r="Z492" s="3"/>
       <c r="AA492" s="3"/>
     </row>
-    <row r="493" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="493">
       <c r="A493" s="3"/>
       <c r="B493" s="3"/>
       <c r="C493" s="3"/>
@@ -15559,7 +15611,7 @@
       <c r="Z493" s="3"/>
       <c r="AA493" s="3"/>
     </row>
-    <row r="494" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="494">
       <c r="A494" s="3"/>
       <c r="B494" s="3"/>
       <c r="C494" s="3"/>
@@ -15588,7 +15640,7 @@
       <c r="Z494" s="3"/>
       <c r="AA494" s="3"/>
     </row>
-    <row r="495" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="495">
       <c r="A495" s="3"/>
       <c r="B495" s="3"/>
       <c r="C495" s="3"/>
@@ -15617,7 +15669,7 @@
       <c r="Z495" s="3"/>
       <c r="AA495" s="3"/>
     </row>
-    <row r="496" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="496">
       <c r="A496" s="3"/>
       <c r="B496" s="3"/>
       <c r="C496" s="3"/>
@@ -15646,7 +15698,7 @@
       <c r="Z496" s="3"/>
       <c r="AA496" s="3"/>
     </row>
-    <row r="497" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="497">
       <c r="A497" s="3"/>
       <c r="B497" s="3"/>
       <c r="C497" s="3"/>
@@ -15675,7 +15727,7 @@
       <c r="Z497" s="3"/>
       <c r="AA497" s="3"/>
     </row>
-    <row r="498" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="498">
       <c r="A498" s="3"/>
       <c r="B498" s="3"/>
       <c r="C498" s="3"/>
@@ -15704,7 +15756,7 @@
       <c r="Z498" s="3"/>
       <c r="AA498" s="3"/>
     </row>
-    <row r="499" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="499">
       <c r="A499" s="3"/>
       <c r="B499" s="3"/>
       <c r="C499" s="3"/>
@@ -15733,7 +15785,7 @@
       <c r="Z499" s="3"/>
       <c r="AA499" s="3"/>
     </row>
-    <row r="500" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="500">
       <c r="A500" s="3"/>
       <c r="B500" s="3"/>
       <c r="C500" s="3"/>
@@ -15762,7 +15814,7 @@
       <c r="Z500" s="3"/>
       <c r="AA500" s="3"/>
     </row>
-    <row r="501" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="501">
       <c r="A501" s="3"/>
       <c r="B501" s="3"/>
       <c r="C501" s="3"/>
@@ -15791,7 +15843,7 @@
       <c r="Z501" s="3"/>
       <c r="AA501" s="3"/>
     </row>
-    <row r="502" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="502">
       <c r="A502" s="3"/>
       <c r="B502" s="3"/>
       <c r="C502" s="3"/>
@@ -15820,7 +15872,7 @@
       <c r="Z502" s="3"/>
       <c r="AA502" s="3"/>
     </row>
-    <row r="503" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="503">
       <c r="A503" s="3"/>
       <c r="B503" s="3"/>
       <c r="C503" s="3"/>
@@ -15849,7 +15901,7 @@
       <c r="Z503" s="3"/>
       <c r="AA503" s="3"/>
     </row>
-    <row r="504" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="504">
       <c r="A504" s="3"/>
       <c r="B504" s="3"/>
       <c r="C504" s="3"/>
@@ -15878,7 +15930,7 @@
       <c r="Z504" s="3"/>
       <c r="AA504" s="3"/>
     </row>
-    <row r="505" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="505">
       <c r="A505" s="3"/>
       <c r="B505" s="3"/>
       <c r="C505" s="3"/>
@@ -15907,7 +15959,7 @@
       <c r="Z505" s="3"/>
       <c r="AA505" s="3"/>
     </row>
-    <row r="506" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="506">
       <c r="A506" s="3"/>
       <c r="B506" s="3"/>
       <c r="C506" s="3"/>
@@ -15936,7 +15988,7 @@
       <c r="Z506" s="3"/>
       <c r="AA506" s="3"/>
     </row>
-    <row r="507" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="507">
       <c r="A507" s="3"/>
       <c r="B507" s="3"/>
       <c r="C507" s="3"/>
@@ -15965,7 +16017,7 @@
       <c r="Z507" s="3"/>
       <c r="AA507" s="3"/>
     </row>
-    <row r="508" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="508">
       <c r="A508" s="3"/>
       <c r="B508" s="3"/>
       <c r="C508" s="3"/>
@@ -15994,7 +16046,7 @@
       <c r="Z508" s="3"/>
       <c r="AA508" s="3"/>
     </row>
-    <row r="509" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="509">
       <c r="A509" s="3"/>
       <c r="B509" s="3"/>
       <c r="C509" s="3"/>
@@ -16023,7 +16075,7 @@
       <c r="Z509" s="3"/>
       <c r="AA509" s="3"/>
     </row>
-    <row r="510" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="510">
       <c r="A510" s="3"/>
       <c r="B510" s="3"/>
       <c r="C510" s="3"/>
@@ -16052,7 +16104,7 @@
       <c r="Z510" s="3"/>
       <c r="AA510" s="3"/>
     </row>
-    <row r="511" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="511">
       <c r="A511" s="3"/>
       <c r="B511" s="3"/>
       <c r="C511" s="3"/>
@@ -16081,7 +16133,7 @@
       <c r="Z511" s="3"/>
       <c r="AA511" s="3"/>
     </row>
-    <row r="512" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="512">
       <c r="A512" s="3"/>
       <c r="B512" s="3"/>
       <c r="C512" s="3"/>
@@ -16110,7 +16162,7 @@
       <c r="Z512" s="3"/>
       <c r="AA512" s="3"/>
     </row>
-    <row r="513" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="513">
       <c r="A513" s="3"/>
       <c r="B513" s="3"/>
       <c r="C513" s="3"/>
@@ -16139,7 +16191,7 @@
       <c r="Z513" s="3"/>
       <c r="AA513" s="3"/>
     </row>
-    <row r="514" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="514">
       <c r="A514" s="3"/>
       <c r="B514" s="3"/>
       <c r="C514" s="3"/>
@@ -16168,7 +16220,7 @@
       <c r="Z514" s="3"/>
       <c r="AA514" s="3"/>
     </row>
-    <row r="515" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="515">
       <c r="A515" s="3"/>
       <c r="B515" s="3"/>
       <c r="C515" s="3"/>
@@ -16197,7 +16249,7 @@
       <c r="Z515" s="3"/>
       <c r="AA515" s="3"/>
     </row>
-    <row r="516" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="516">
       <c r="A516" s="3"/>
       <c r="B516" s="3"/>
       <c r="C516" s="3"/>
@@ -16226,7 +16278,7 @@
       <c r="Z516" s="3"/>
       <c r="AA516" s="3"/>
     </row>
-    <row r="517" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="517">
       <c r="A517" s="3"/>
       <c r="B517" s="3"/>
       <c r="C517" s="3"/>
@@ -16255,7 +16307,7 @@
       <c r="Z517" s="3"/>
       <c r="AA517" s="3"/>
     </row>
-    <row r="518" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="518">
       <c r="A518" s="3"/>
       <c r="B518" s="3"/>
       <c r="C518" s="3"/>
@@ -16284,7 +16336,7 @@
       <c r="Z518" s="3"/>
       <c r="AA518" s="3"/>
     </row>
-    <row r="519" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="519">
       <c r="A519" s="3"/>
       <c r="B519" s="3"/>
       <c r="C519" s="3"/>
@@ -16313,7 +16365,7 @@
       <c r="Z519" s="3"/>
       <c r="AA519" s="3"/>
     </row>
-    <row r="520" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="520">
       <c r="A520" s="3"/>
       <c r="B520" s="3"/>
       <c r="C520" s="3"/>
@@ -16342,7 +16394,7 @@
       <c r="Z520" s="3"/>
       <c r="AA520" s="3"/>
     </row>
-    <row r="521" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="521">
       <c r="A521" s="3"/>
       <c r="B521" s="3"/>
       <c r="C521" s="3"/>
@@ -16371,7 +16423,7 @@
       <c r="Z521" s="3"/>
       <c r="AA521" s="3"/>
     </row>
-    <row r="522" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="522">
       <c r="A522" s="3"/>
       <c r="B522" s="3"/>
       <c r="C522" s="3"/>
@@ -16400,7 +16452,7 @@
       <c r="Z522" s="3"/>
       <c r="AA522" s="3"/>
     </row>
-    <row r="523" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="523">
       <c r="A523" s="3"/>
       <c r="B523" s="3"/>
       <c r="C523" s="3"/>
@@ -16429,7 +16481,7 @@
       <c r="Z523" s="3"/>
       <c r="AA523" s="3"/>
     </row>
-    <row r="524" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="524">
       <c r="A524" s="3"/>
       <c r="B524" s="3"/>
       <c r="C524" s="3"/>
@@ -16458,7 +16510,7 @@
       <c r="Z524" s="3"/>
       <c r="AA524" s="3"/>
     </row>
-    <row r="525" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="525">
       <c r="A525" s="3"/>
       <c r="B525" s="3"/>
       <c r="C525" s="3"/>
@@ -16487,7 +16539,7 @@
       <c r="Z525" s="3"/>
       <c r="AA525" s="3"/>
     </row>
-    <row r="526" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="526">
       <c r="A526" s="3"/>
       <c r="B526" s="3"/>
       <c r="C526" s="3"/>
@@ -16516,7 +16568,7 @@
       <c r="Z526" s="3"/>
       <c r="AA526" s="3"/>
     </row>
-    <row r="527" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="527">
       <c r="A527" s="3"/>
       <c r="B527" s="3"/>
       <c r="C527" s="3"/>
@@ -16545,7 +16597,7 @@
       <c r="Z527" s="3"/>
       <c r="AA527" s="3"/>
     </row>
-    <row r="528" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="528">
       <c r="A528" s="3"/>
       <c r="B528" s="3"/>
       <c r="C528" s="3"/>
@@ -16574,7 +16626,7 @@
       <c r="Z528" s="3"/>
       <c r="AA528" s="3"/>
     </row>
-    <row r="529" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="529">
       <c r="A529" s="3"/>
       <c r="B529" s="3"/>
       <c r="C529" s="3"/>
@@ -16603,7 +16655,7 @@
       <c r="Z529" s="3"/>
       <c r="AA529" s="3"/>
     </row>
-    <row r="530" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="530">
       <c r="A530" s="3"/>
       <c r="B530" s="3"/>
       <c r="C530" s="3"/>
@@ -16632,7 +16684,7 @@
       <c r="Z530" s="3"/>
       <c r="AA530" s="3"/>
     </row>
-    <row r="531" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="531">
       <c r="A531" s="3"/>
       <c r="B531" s="3"/>
       <c r="C531" s="3"/>
@@ -16661,7 +16713,7 @@
       <c r="Z531" s="3"/>
       <c r="AA531" s="3"/>
     </row>
-    <row r="532" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="532">
       <c r="A532" s="3"/>
       <c r="B532" s="3"/>
       <c r="C532" s="3"/>
@@ -16690,7 +16742,7 @@
       <c r="Z532" s="3"/>
       <c r="AA532" s="3"/>
     </row>
-    <row r="533" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="533">
       <c r="A533" s="3"/>
       <c r="B533" s="3"/>
       <c r="C533" s="3"/>
@@ -16719,7 +16771,7 @@
       <c r="Z533" s="3"/>
       <c r="AA533" s="3"/>
     </row>
-    <row r="534" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="534">
       <c r="A534" s="3"/>
       <c r="B534" s="3"/>
       <c r="C534" s="3"/>
@@ -16748,7 +16800,7 @@
       <c r="Z534" s="3"/>
       <c r="AA534" s="3"/>
     </row>
-    <row r="535" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="535">
       <c r="A535" s="3"/>
       <c r="B535" s="3"/>
       <c r="C535" s="3"/>
@@ -16777,7 +16829,7 @@
       <c r="Z535" s="3"/>
       <c r="AA535" s="3"/>
     </row>
-    <row r="536" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="536">
       <c r="A536" s="3"/>
       <c r="B536" s="3"/>
       <c r="C536" s="3"/>
@@ -16806,7 +16858,7 @@
       <c r="Z536" s="3"/>
       <c r="AA536" s="3"/>
     </row>
-    <row r="537" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="537">
       <c r="A537" s="3"/>
       <c r="B537" s="3"/>
       <c r="C537" s="3"/>
@@ -16835,7 +16887,7 @@
       <c r="Z537" s="3"/>
       <c r="AA537" s="3"/>
     </row>
-    <row r="538" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="538">
       <c r="A538" s="3"/>
       <c r="B538" s="3"/>
       <c r="C538" s="3"/>
@@ -16864,7 +16916,7 @@
       <c r="Z538" s="3"/>
       <c r="AA538" s="3"/>
     </row>
-    <row r="539" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="539">
       <c r="A539" s="3"/>
       <c r="B539" s="3"/>
       <c r="C539" s="3"/>
@@ -16893,7 +16945,7 @@
       <c r="Z539" s="3"/>
       <c r="AA539" s="3"/>
     </row>
-    <row r="540" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="540">
       <c r="A540" s="3"/>
       <c r="B540" s="3"/>
       <c r="C540" s="3"/>
@@ -16922,7 +16974,7 @@
       <c r="Z540" s="3"/>
       <c r="AA540" s="3"/>
     </row>
-    <row r="541" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="541">
       <c r="A541" s="3"/>
       <c r="B541" s="3"/>
       <c r="C541" s="3"/>
@@ -16951,7 +17003,7 @@
       <c r="Z541" s="3"/>
       <c r="AA541" s="3"/>
     </row>
-    <row r="542" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="542">
       <c r="A542" s="3"/>
       <c r="B542" s="3"/>
       <c r="C542" s="3"/>
@@ -16980,7 +17032,7 @@
       <c r="Z542" s="3"/>
       <c r="AA542" s="3"/>
     </row>
-    <row r="543" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="543">
       <c r="A543" s="3"/>
       <c r="B543" s="3"/>
       <c r="C543" s="3"/>
@@ -17009,7 +17061,7 @@
       <c r="Z543" s="3"/>
       <c r="AA543" s="3"/>
     </row>
-    <row r="544" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="544">
       <c r="A544" s="3"/>
       <c r="B544" s="3"/>
       <c r="C544" s="3"/>
@@ -17038,7 +17090,7 @@
       <c r="Z544" s="3"/>
       <c r="AA544" s="3"/>
     </row>
-    <row r="545" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="545">
       <c r="A545" s="3"/>
       <c r="B545" s="3"/>
       <c r="C545" s="3"/>
@@ -17067,7 +17119,7 @@
       <c r="Z545" s="3"/>
       <c r="AA545" s="3"/>
     </row>
-    <row r="546" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="546">
       <c r="A546" s="3"/>
       <c r="B546" s="3"/>
       <c r="C546" s="3"/>
@@ -17096,7 +17148,7 @@
       <c r="Z546" s="3"/>
       <c r="AA546" s="3"/>
     </row>
-    <row r="547" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="547">
       <c r="A547" s="3"/>
       <c r="B547" s="3"/>
       <c r="C547" s="3"/>
@@ -17125,7 +17177,7 @@
       <c r="Z547" s="3"/>
       <c r="AA547" s="3"/>
     </row>
-    <row r="548" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="548">
       <c r="A548" s="3"/>
       <c r="B548" s="3"/>
       <c r="C548" s="3"/>
@@ -17154,7 +17206,7 @@
       <c r="Z548" s="3"/>
       <c r="AA548" s="3"/>
     </row>
-    <row r="549" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="549">
       <c r="A549" s="3"/>
       <c r="B549" s="3"/>
       <c r="C549" s="3"/>
@@ -17183,7 +17235,7 @@
       <c r="Z549" s="3"/>
       <c r="AA549" s="3"/>
     </row>
-    <row r="550" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="550">
       <c r="A550" s="3"/>
       <c r="B550" s="3"/>
       <c r="C550" s="3"/>
@@ -17212,7 +17264,7 @@
       <c r="Z550" s="3"/>
       <c r="AA550" s="3"/>
     </row>
-    <row r="551" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="551">
       <c r="A551" s="3"/>
       <c r="B551" s="3"/>
       <c r="C551" s="3"/>
@@ -17241,7 +17293,7 @@
       <c r="Z551" s="3"/>
       <c r="AA551" s="3"/>
     </row>
-    <row r="552" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="552">
       <c r="A552" s="3"/>
       <c r="B552" s="3"/>
       <c r="C552" s="3"/>
@@ -17270,7 +17322,7 @@
       <c r="Z552" s="3"/>
       <c r="AA552" s="3"/>
     </row>
-    <row r="553" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="553">
       <c r="A553" s="3"/>
       <c r="B553" s="3"/>
       <c r="C553" s="3"/>
@@ -17299,7 +17351,7 @@
       <c r="Z553" s="3"/>
       <c r="AA553" s="3"/>
     </row>
-    <row r="554" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="554">
       <c r="A554" s="3"/>
       <c r="B554" s="3"/>
       <c r="C554" s="3"/>
@@ -17328,7 +17380,7 @@
       <c r="Z554" s="3"/>
       <c r="AA554" s="3"/>
     </row>
-    <row r="555" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="555">
       <c r="A555" s="3"/>
       <c r="B555" s="3"/>
       <c r="C555" s="3"/>
@@ -17357,7 +17409,7 @@
       <c r="Z555" s="3"/>
       <c r="AA555" s="3"/>
     </row>
-    <row r="556" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="556">
       <c r="A556" s="3"/>
       <c r="B556" s="3"/>
       <c r="C556" s="3"/>
@@ -17386,7 +17438,7 @@
       <c r="Z556" s="3"/>
       <c r="AA556" s="3"/>
     </row>
-    <row r="557" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="557">
       <c r="A557" s="3"/>
       <c r="B557" s="3"/>
       <c r="C557" s="3"/>
@@ -17415,7 +17467,7 @@
       <c r="Z557" s="3"/>
       <c r="AA557" s="3"/>
     </row>
-    <row r="558" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="558">
       <c r="A558" s="3"/>
       <c r="B558" s="3"/>
       <c r="C558" s="3"/>
@@ -17444,7 +17496,7 @@
       <c r="Z558" s="3"/>
       <c r="AA558" s="3"/>
     </row>
-    <row r="559" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="559">
       <c r="A559" s="3"/>
       <c r="B559" s="3"/>
       <c r="C559" s="3"/>
@@ -17473,7 +17525,7 @@
       <c r="Z559" s="3"/>
       <c r="AA559" s="3"/>
     </row>
-    <row r="560" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="560">
       <c r="A560" s="3"/>
       <c r="B560" s="3"/>
       <c r="C560" s="3"/>
@@ -17502,7 +17554,7 @@
       <c r="Z560" s="3"/>
       <c r="AA560" s="3"/>
     </row>
-    <row r="561" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="561">
       <c r="A561" s="3"/>
       <c r="B561" s="3"/>
       <c r="C561" s="3"/>
@@ -17531,7 +17583,7 @@
       <c r="Z561" s="3"/>
       <c r="AA561" s="3"/>
     </row>
-    <row r="562" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="562">
       <c r="A562" s="3"/>
       <c r="B562" s="3"/>
       <c r="C562" s="3"/>
@@ -17560,7 +17612,7 @@
       <c r="Z562" s="3"/>
       <c r="AA562" s="3"/>
     </row>
-    <row r="563" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="563">
       <c r="A563" s="3"/>
       <c r="B563" s="3"/>
       <c r="C563" s="3"/>
@@ -17589,7 +17641,7 @@
       <c r="Z563" s="3"/>
       <c r="AA563" s="3"/>
     </row>
-    <row r="564" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="564">
       <c r="A564" s="3"/>
       <c r="B564" s="3"/>
       <c r="C564" s="3"/>
@@ -17618,7 +17670,7 @@
       <c r="Z564" s="3"/>
       <c r="AA564" s="3"/>
     </row>
-    <row r="565" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="565">
       <c r="A565" s="3"/>
       <c r="B565" s="3"/>
       <c r="C565" s="3"/>
@@ -17647,7 +17699,7 @@
       <c r="Z565" s="3"/>
       <c r="AA565" s="3"/>
     </row>
-    <row r="566" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="566">
       <c r="A566" s="3"/>
       <c r="B566" s="3"/>
       <c r="C566" s="3"/>
@@ -17676,7 +17728,7 @@
       <c r="Z566" s="3"/>
       <c r="AA566" s="3"/>
     </row>
-    <row r="567" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="567">
       <c r="A567" s="3"/>
       <c r="B567" s="3"/>
       <c r="C567" s="3"/>
@@ -17705,7 +17757,7 @@
       <c r="Z567" s="3"/>
       <c r="AA567" s="3"/>
     </row>
-    <row r="568" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="568">
       <c r="A568" s="3"/>
       <c r="B568" s="3"/>
       <c r="C568" s="3"/>
@@ -17734,7 +17786,7 @@
       <c r="Z568" s="3"/>
       <c r="AA568" s="3"/>
     </row>
-    <row r="569" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="569">
       <c r="A569" s="3"/>
       <c r="B569" s="3"/>
       <c r="C569" s="3"/>
@@ -17763,7 +17815,7 @@
       <c r="Z569" s="3"/>
       <c r="AA569" s="3"/>
     </row>
-    <row r="570" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="570">
       <c r="A570" s="3"/>
       <c r="B570" s="3"/>
       <c r="C570" s="3"/>
@@ -17792,7 +17844,7 @@
       <c r="Z570" s="3"/>
       <c r="AA570" s="3"/>
     </row>
-    <row r="571" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="571">
       <c r="A571" s="3"/>
       <c r="B571" s="3"/>
       <c r="C571" s="3"/>
@@ -17821,7 +17873,7 @@
       <c r="Z571" s="3"/>
       <c r="AA571" s="3"/>
     </row>
-    <row r="572" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="572">
       <c r="A572" s="3"/>
       <c r="B572" s="3"/>
       <c r="C572" s="3"/>
@@ -17850,7 +17902,7 @@
       <c r="Z572" s="3"/>
       <c r="AA572" s="3"/>
     </row>
-    <row r="573" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="573">
       <c r="A573" s="3"/>
       <c r="B573" s="3"/>
       <c r="C573" s="3"/>
@@ -17879,7 +17931,7 @@
       <c r="Z573" s="3"/>
       <c r="AA573" s="3"/>
     </row>
-    <row r="574" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="574">
       <c r="A574" s="3"/>
       <c r="B574" s="3"/>
       <c r="C574" s="3"/>
@@ -17908,7 +17960,7 @@
       <c r="Z574" s="3"/>
       <c r="AA574" s="3"/>
     </row>
-    <row r="575" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="575">
       <c r="A575" s="3"/>
       <c r="B575" s="3"/>
       <c r="C575" s="3"/>
@@ -17937,7 +17989,7 @@
       <c r="Z575" s="3"/>
       <c r="AA575" s="3"/>
     </row>
-    <row r="576" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="576">
       <c r="A576" s="3"/>
       <c r="B576" s="3"/>
       <c r="C576" s="3"/>
@@ -17966,7 +18018,7 @@
       <c r="Z576" s="3"/>
       <c r="AA576" s="3"/>
     </row>
-    <row r="577" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="577">
       <c r="A577" s="3"/>
       <c r="B577" s="3"/>
       <c r="C577" s="3"/>
@@ -17995,7 +18047,7 @@
       <c r="Z577" s="3"/>
       <c r="AA577" s="3"/>
     </row>
-    <row r="578" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="578">
       <c r="A578" s="3"/>
       <c r="B578" s="3"/>
       <c r="C578" s="3"/>
@@ -18024,7 +18076,7 @@
       <c r="Z578" s="3"/>
       <c r="AA578" s="3"/>
     </row>
-    <row r="579" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="579">
       <c r="A579" s="3"/>
       <c r="B579" s="3"/>
       <c r="C579" s="3"/>
@@ -18053,7 +18105,7 @@
       <c r="Z579" s="3"/>
       <c r="AA579" s="3"/>
     </row>
-    <row r="580" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="580">
       <c r="A580" s="3"/>
       <c r="B580" s="3"/>
       <c r="C580" s="3"/>
@@ -18082,7 +18134,7 @@
       <c r="Z580" s="3"/>
       <c r="AA580" s="3"/>
     </row>
-    <row r="581" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="581">
       <c r="A581" s="3"/>
       <c r="B581" s="3"/>
       <c r="C581" s="3"/>
@@ -18111,7 +18163,7 @@
       <c r="Z581" s="3"/>
       <c r="AA581" s="3"/>
     </row>
-    <row r="582" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="582">
       <c r="A582" s="3"/>
       <c r="B582" s="3"/>
       <c r="C582" s="3"/>
@@ -18140,7 +18192,7 @@
       <c r="Z582" s="3"/>
       <c r="AA582" s="3"/>
     </row>
-    <row r="583" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="583">
       <c r="A583" s="3"/>
       <c r="B583" s="3"/>
       <c r="C583" s="3"/>
@@ -18169,7 +18221,7 @@
       <c r="Z583" s="3"/>
       <c r="AA583" s="3"/>
     </row>
-    <row r="584" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="584">
       <c r="A584" s="3"/>
       <c r="B584" s="3"/>
       <c r="C584" s="3"/>
@@ -18198,7 +18250,7 @@
       <c r="Z584" s="3"/>
       <c r="AA584" s="3"/>
     </row>
-    <row r="585" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="585">
       <c r="A585" s="3"/>
       <c r="B585" s="3"/>
       <c r="C585" s="3"/>
@@ -18227,7 +18279,7 @@
       <c r="Z585" s="3"/>
       <c r="AA585" s="3"/>
     </row>
-    <row r="586" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="586">
       <c r="A586" s="3"/>
       <c r="B586" s="3"/>
       <c r="C586" s="3"/>
@@ -18256,7 +18308,7 @@
       <c r="Z586" s="3"/>
       <c r="AA586" s="3"/>
     </row>
-    <row r="587" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="587">
       <c r="A587" s="3"/>
       <c r="B587" s="3"/>
       <c r="C587" s="3"/>
@@ -18285,7 +18337,7 @@
       <c r="Z587" s="3"/>
       <c r="AA587" s="3"/>
     </row>
-    <row r="588" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="588">
       <c r="A588" s="3"/>
       <c r="B588" s="3"/>
       <c r="C588" s="3"/>
@@ -18314,7 +18366,7 @@
       <c r="Z588" s="3"/>
       <c r="AA588" s="3"/>
     </row>
-    <row r="589" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="589">
       <c r="A589" s="3"/>
       <c r="B589" s="3"/>
       <c r="C589" s="3"/>
@@ -18343,7 +18395,7 @@
       <c r="Z589" s="3"/>
       <c r="AA589" s="3"/>
     </row>
-    <row r="590" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="590">
       <c r="A590" s="3"/>
       <c r="B590" s="3"/>
       <c r="C590" s="3"/>
@@ -18372,7 +18424,7 @@
       <c r="Z590" s="3"/>
       <c r="AA590" s="3"/>
     </row>
-    <row r="591" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="591">
       <c r="A591" s="3"/>
       <c r="B591" s="3"/>
       <c r="C591" s="3"/>
@@ -18401,7 +18453,7 @@
       <c r="Z591" s="3"/>
       <c r="AA591" s="3"/>
     </row>
-    <row r="592" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="592">
       <c r="A592" s="3"/>
       <c r="B592" s="3"/>
       <c r="C592" s="3"/>
@@ -18430,7 +18482,7 @@
       <c r="Z592" s="3"/>
       <c r="AA592" s="3"/>
     </row>
-    <row r="593" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="593">
       <c r="A593" s="3"/>
       <c r="B593" s="3"/>
       <c r="C593" s="3"/>
@@ -18459,7 +18511,7 @@
       <c r="Z593" s="3"/>
       <c r="AA593" s="3"/>
     </row>
-    <row r="594" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="594">
       <c r="A594" s="3"/>
       <c r="B594" s="3"/>
       <c r="C594" s="3"/>
@@ -18488,7 +18540,7 @@
       <c r="Z594" s="3"/>
       <c r="AA594" s="3"/>
     </row>
-    <row r="595" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="595">
       <c r="A595" s="3"/>
       <c r="B595" s="3"/>
       <c r="C595" s="3"/>
@@ -18517,7 +18569,7 @@
       <c r="Z595" s="3"/>
       <c r="AA595" s="3"/>
     </row>
-    <row r="596" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="596">
       <c r="A596" s="3"/>
       <c r="B596" s="3"/>
       <c r="C596" s="3"/>
@@ -18546,7 +18598,7 @@
       <c r="Z596" s="3"/>
       <c r="AA596" s="3"/>
     </row>
-    <row r="597" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="597">
       <c r="A597" s="3"/>
       <c r="B597" s="3"/>
       <c r="C597" s="3"/>
@@ -18575,7 +18627,7 @@
       <c r="Z597" s="3"/>
       <c r="AA597" s="3"/>
     </row>
-    <row r="598" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="598">
       <c r="A598" s="3"/>
       <c r="B598" s="3"/>
       <c r="C598" s="3"/>
@@ -18604,7 +18656,7 @@
       <c r="Z598" s="3"/>
       <c r="AA598" s="3"/>
     </row>
-    <row r="599" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="599">
       <c r="A599" s="3"/>
       <c r="B599" s="3"/>
       <c r="C599" s="3"/>
@@ -18633,7 +18685,7 @@
       <c r="Z599" s="3"/>
       <c r="AA599" s="3"/>
     </row>
-    <row r="600" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="600">
       <c r="A600" s="3"/>
       <c r="B600" s="3"/>
       <c r="C600" s="3"/>
@@ -18662,7 +18714,7 @@
       <c r="Z600" s="3"/>
       <c r="AA600" s="3"/>
     </row>
-    <row r="601" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="601">
       <c r="A601" s="3"/>
       <c r="B601" s="3"/>
       <c r="C601" s="3"/>
@@ -18691,7 +18743,7 @@
       <c r="Z601" s="3"/>
       <c r="AA601" s="3"/>
     </row>
-    <row r="602" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="602">
       <c r="A602" s="3"/>
       <c r="B602" s="3"/>
       <c r="C602" s="3"/>
@@ -18720,7 +18772,7 @@
       <c r="Z602" s="3"/>
       <c r="AA602" s="3"/>
     </row>
-    <row r="603" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="603">
       <c r="A603" s="3"/>
       <c r="B603" s="3"/>
       <c r="C603" s="3"/>
@@ -18749,7 +18801,7 @@
       <c r="Z603" s="3"/>
       <c r="AA603" s="3"/>
     </row>
-    <row r="604" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="604">
       <c r="A604" s="3"/>
       <c r="B604" s="3"/>
       <c r="C604" s="3"/>
@@ -18778,7 +18830,7 @@
       <c r="Z604" s="3"/>
       <c r="AA604" s="3"/>
     </row>
-    <row r="605" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="605">
       <c r="A605" s="3"/>
       <c r="B605" s="3"/>
       <c r="C605" s="3"/>
@@ -18807,7 +18859,7 @@
       <c r="Z605" s="3"/>
       <c r="AA605" s="3"/>
     </row>
-    <row r="606" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="606">
       <c r="A606" s="3"/>
       <c r="B606" s="3"/>
       <c r="C606" s="3"/>
@@ -18836,7 +18888,7 @@
       <c r="Z606" s="3"/>
       <c r="AA606" s="3"/>
     </row>
-    <row r="607" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="607">
       <c r="A607" s="3"/>
       <c r="B607" s="3"/>
       <c r="C607" s="3"/>
@@ -18865,7 +18917,7 @@
       <c r="Z607" s="3"/>
       <c r="AA607" s="3"/>
     </row>
-    <row r="608" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="608">
       <c r="A608" s="3"/>
       <c r="B608" s="3"/>
       <c r="C608" s="3"/>
@@ -18894,7 +18946,7 @@
       <c r="Z608" s="3"/>
       <c r="AA608" s="3"/>
     </row>
-    <row r="609" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="609">
       <c r="A609" s="3"/>
       <c r="B609" s="3"/>
       <c r="C609" s="3"/>
@@ -18923,7 +18975,7 @@
       <c r="Z609" s="3"/>
       <c r="AA609" s="3"/>
     </row>
-    <row r="610" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="610">
       <c r="A610" s="3"/>
       <c r="B610" s="3"/>
       <c r="C610" s="3"/>
@@ -18952,7 +19004,7 @@
       <c r="Z610" s="3"/>
       <c r="AA610" s="3"/>
     </row>
-    <row r="611" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="611">
       <c r="A611" s="3"/>
       <c r="B611" s="3"/>
       <c r="C611" s="3"/>
@@ -18981,7 +19033,7 @@
       <c r="Z611" s="3"/>
       <c r="AA611" s="3"/>
     </row>
-    <row r="612" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="612">
       <c r="A612" s="3"/>
       <c r="B612" s="3"/>
       <c r="C612" s="3"/>
@@ -19010,7 +19062,7 @@
       <c r="Z612" s="3"/>
       <c r="AA612" s="3"/>
     </row>
-    <row r="613" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="613">
       <c r="A613" s="3"/>
       <c r="B613" s="3"/>
       <c r="C613" s="3"/>
@@ -19039,7 +19091,7 @@
       <c r="Z613" s="3"/>
       <c r="AA613" s="3"/>
     </row>
-    <row r="614" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="614">
       <c r="A614" s="3"/>
       <c r="B614" s="3"/>
       <c r="C614" s="3"/>
@@ -19068,7 +19120,7 @@
       <c r="Z614" s="3"/>
       <c r="AA614" s="3"/>
     </row>
-    <row r="615" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="615">
       <c r="A615" s="3"/>
       <c r="B615" s="3"/>
       <c r="C615" s="3"/>
@@ -19097,7 +19149,7 @@
       <c r="Z615" s="3"/>
       <c r="AA615" s="3"/>
     </row>
-    <row r="616" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="616">
       <c r="A616" s="3"/>
       <c r="B616" s="3"/>
       <c r="C616" s="3"/>
@@ -19126,7 +19178,7 @@
       <c r="Z616" s="3"/>
       <c r="AA616" s="3"/>
     </row>
-    <row r="617" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="617">
       <c r="A617" s="3"/>
       <c r="B617" s="3"/>
       <c r="C617" s="3"/>
@@ -19155,7 +19207,7 @@
       <c r="Z617" s="3"/>
       <c r="AA617" s="3"/>
     </row>
-    <row r="618" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="618">
       <c r="A618" s="3"/>
       <c r="B618" s="3"/>
       <c r="C618" s="3"/>
@@ -19184,7 +19236,7 @@
       <c r="Z618" s="3"/>
       <c r="AA618" s="3"/>
     </row>
-    <row r="619" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="619">
       <c r="A619" s="3"/>
       <c r="B619" s="3"/>
       <c r="C619" s="3"/>
@@ -19213,7 +19265,7 @@
       <c r="Z619" s="3"/>
       <c r="AA619" s="3"/>
     </row>
-    <row r="620" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="620">
       <c r="A620" s="3"/>
       <c r="B620" s="3"/>
       <c r="C620" s="3"/>
@@ -19242,7 +19294,7 @@
       <c r="Z620" s="3"/>
       <c r="AA620" s="3"/>
     </row>
-    <row r="621" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="621">
       <c r="A621" s="3"/>
       <c r="B621" s="3"/>
       <c r="C621" s="3"/>
@@ -19271,7 +19323,7 @@
       <c r="Z621" s="3"/>
       <c r="AA621" s="3"/>
     </row>
-    <row r="622" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="622">
       <c r="A622" s="3"/>
       <c r="B622" s="3"/>
       <c r="C622" s="3"/>
@@ -19300,7 +19352,7 @@
       <c r="Z622" s="3"/>
       <c r="AA622" s="3"/>
     </row>
-    <row r="623" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="623">
       <c r="A623" s="3"/>
       <c r="B623" s="3"/>
       <c r="C623" s="3"/>
@@ -19329,7 +19381,7 @@
       <c r="Z623" s="3"/>
       <c r="AA623" s="3"/>
     </row>
-    <row r="624" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="624">
       <c r="A624" s="3"/>
       <c r="B624" s="3"/>
       <c r="C624" s="3"/>
@@ -19358,7 +19410,7 @@
       <c r="Z624" s="3"/>
       <c r="AA624" s="3"/>
     </row>
-    <row r="625" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="625">
       <c r="A625" s="3"/>
       <c r="B625" s="3"/>
       <c r="C625" s="3"/>
@@ -19387,7 +19439,7 @@
       <c r="Z625" s="3"/>
       <c r="AA625" s="3"/>
     </row>
-    <row r="626" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="626">
       <c r="A626" s="3"/>
       <c r="B626" s="3"/>
       <c r="C626" s="3"/>
@@ -19416,7 +19468,7 @@
       <c r="Z626" s="3"/>
       <c r="AA626" s="3"/>
     </row>
-    <row r="627" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="627">
       <c r="A627" s="3"/>
       <c r="B627" s="3"/>
       <c r="C627" s="3"/>
@@ -19445,7 +19497,7 @@
       <c r="Z627" s="3"/>
       <c r="AA627" s="3"/>
     </row>
-    <row r="628" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="628">
       <c r="A628" s="3"/>
       <c r="B628" s="3"/>
       <c r="C628" s="3"/>
@@ -19474,7 +19526,7 @@
       <c r="Z628" s="3"/>
       <c r="AA628" s="3"/>
     </row>
-    <row r="629" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="629">
       <c r="A629" s="3"/>
       <c r="B629" s="3"/>
       <c r="C629" s="3"/>
@@ -19503,7 +19555,7 @@
       <c r="Z629" s="3"/>
       <c r="AA629" s="3"/>
     </row>
-    <row r="630" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="630">
       <c r="A630" s="3"/>
       <c r="B630" s="3"/>
       <c r="C630" s="3"/>
@@ -19532,7 +19584,7 @@
       <c r="Z630" s="3"/>
       <c r="AA630" s="3"/>
     </row>
-    <row r="631" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="631">
       <c r="A631" s="3"/>
       <c r="B631" s="3"/>
       <c r="C631" s="3"/>
@@ -19561,7 +19613,7 @@
       <c r="Z631" s="3"/>
       <c r="AA631" s="3"/>
     </row>
-    <row r="632" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="632">
       <c r="A632" s="3"/>
       <c r="B632" s="3"/>
       <c r="C632" s="3"/>
@@ -19590,7 +19642,7 @@
       <c r="Z632" s="3"/>
       <c r="AA632" s="3"/>
     </row>
-    <row r="633" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="633">
       <c r="A633" s="3"/>
       <c r="B633" s="3"/>
       <c r="C633" s="3"/>
@@ -19619,7 +19671,7 @@
       <c r="Z633" s="3"/>
       <c r="AA633" s="3"/>
     </row>
-    <row r="634" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="634">
       <c r="A634" s="3"/>
       <c r="B634" s="3"/>
       <c r="C634" s="3"/>
@@ -19648,7 +19700,7 @@
       <c r="Z634" s="3"/>
       <c r="AA634" s="3"/>
     </row>
-    <row r="635" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="635">
       <c r="A635" s="3"/>
       <c r="B635" s="3"/>
       <c r="C635" s="3"/>
@@ -19677,7 +19729,7 @@
       <c r="Z635" s="3"/>
       <c r="AA635" s="3"/>
     </row>
-    <row r="636" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="636">
       <c r="A636" s="3"/>
       <c r="B636" s="3"/>
       <c r="C636" s="3"/>
@@ -19706,7 +19758,7 @@
       <c r="Z636" s="3"/>
       <c r="AA636" s="3"/>
     </row>
-    <row r="637" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="637">
       <c r="A637" s="3"/>
       <c r="B637" s="3"/>
       <c r="C637" s="3"/>
@@ -19735,7 +19787,7 @@
       <c r="Z637" s="3"/>
       <c r="AA637" s="3"/>
     </row>
-    <row r="638" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="638">
       <c r="A638" s="3"/>
       <c r="B638" s="3"/>
       <c r="C638" s="3"/>
@@ -19764,7 +19816,7 @@
       <c r="Z638" s="3"/>
       <c r="AA638" s="3"/>
     </row>
-    <row r="639" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="639">
       <c r="A639" s="3"/>
       <c r="B639" s="3"/>
       <c r="C639" s="3"/>
@@ -19793,7 +19845,7 @@
       <c r="Z639" s="3"/>
       <c r="AA639" s="3"/>
     </row>
-    <row r="640" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="640">
       <c r="A640" s="3"/>
       <c r="B640" s="3"/>
       <c r="C640" s="3"/>
@@ -19822,7 +19874,7 @@
       <c r="Z640" s="3"/>
       <c r="AA640" s="3"/>
     </row>
-    <row r="641" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="641">
       <c r="A641" s="3"/>
       <c r="B641" s="3"/>
       <c r="C641" s="3"/>
@@ -19851,7 +19903,7 @@
       <c r="Z641" s="3"/>
       <c r="AA641" s="3"/>
     </row>
-    <row r="642" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="642">
       <c r="A642" s="3"/>
       <c r="B642" s="3"/>
       <c r="C642" s="3"/>
@@ -19880,7 +19932,7 @@
       <c r="Z642" s="3"/>
       <c r="AA642" s="3"/>
     </row>
-    <row r="643" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="643">
       <c r="A643" s="3"/>
       <c r="B643" s="3"/>
       <c r="C643" s="3"/>
@@ -19909,7 +19961,7 @@
       <c r="Z643" s="3"/>
       <c r="AA643" s="3"/>
     </row>
-    <row r="644" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="644">
       <c r="A644" s="3"/>
       <c r="B644" s="3"/>
       <c r="C644" s="3"/>
@@ -19938,7 +19990,7 @@
       <c r="Z644" s="3"/>
       <c r="AA644" s="3"/>
     </row>
-    <row r="645" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="645">
       <c r="A645" s="3"/>
       <c r="B645" s="3"/>
       <c r="C645" s="3"/>
@@ -19967,7 +20019,7 @@
       <c r="Z645" s="3"/>
       <c r="AA645" s="3"/>
     </row>
-    <row r="646" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="646">
       <c r="A646" s="3"/>
       <c r="B646" s="3"/>
       <c r="C646" s="3"/>
@@ -19996,7 +20048,7 @@
       <c r="Z646" s="3"/>
       <c r="AA646" s="3"/>
     </row>
-    <row r="647" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="647">
       <c r="A647" s="3"/>
       <c r="B647" s="3"/>
       <c r="C647" s="3"/>
@@ -20025,7 +20077,7 @@
       <c r="Z647" s="3"/>
       <c r="AA647" s="3"/>
     </row>
-    <row r="648" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="648">
       <c r="A648" s="3"/>
       <c r="B648" s="3"/>
       <c r="C648" s="3"/>
@@ -20054,7 +20106,7 @@
       <c r="Z648" s="3"/>
       <c r="AA648" s="3"/>
     </row>
-    <row r="649" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="649">
       <c r="A649" s="3"/>
       <c r="B649" s="3"/>
       <c r="C649" s="3"/>
@@ -20083,7 +20135,7 @@
       <c r="Z649" s="3"/>
       <c r="AA649" s="3"/>
     </row>
-    <row r="650" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="650">
       <c r="A650" s="3"/>
       <c r="B650" s="3"/>
       <c r="C650" s="3"/>
@@ -20112,7 +20164,7 @@
       <c r="Z650" s="3"/>
       <c r="AA650" s="3"/>
     </row>
-    <row r="651" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="651">
       <c r="A651" s="3"/>
       <c r="B651" s="3"/>
       <c r="C651" s="3"/>
@@ -20141,7 +20193,7 @@
       <c r="Z651" s="3"/>
       <c r="AA651" s="3"/>
     </row>
-    <row r="652" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="652">
       <c r="A652" s="3"/>
       <c r="B652" s="3"/>
       <c r="C652" s="3"/>
@@ -20170,7 +20222,7 @@
       <c r="Z652" s="3"/>
       <c r="AA652" s="3"/>
     </row>
-    <row r="653" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="653">
       <c r="A653" s="3"/>
       <c r="B653" s="3"/>
       <c r="C653" s="3"/>
@@ -20199,7 +20251,7 @@
       <c r="Z653" s="3"/>
       <c r="AA653" s="3"/>
     </row>
-    <row r="654" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="654">
       <c r="A654" s="3"/>
       <c r="B654" s="3"/>
       <c r="C654" s="3"/>
@@ -20228,7 +20280,7 @@
       <c r="Z654" s="3"/>
       <c r="AA654" s="3"/>
     </row>
-    <row r="655" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="655">
       <c r="A655" s="3"/>
       <c r="B655" s="3"/>
       <c r="C655" s="3"/>
@@ -20257,7 +20309,7 @@
       <c r="Z655" s="3"/>
       <c r="AA655" s="3"/>
     </row>
-    <row r="656" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="656">
       <c r="A656" s="3"/>
       <c r="B656" s="3"/>
       <c r="C656" s="3"/>
@@ -20286,7 +20338,7 @@
       <c r="Z656" s="3"/>
       <c r="AA656" s="3"/>
     </row>
-    <row r="657" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="657">
       <c r="A657" s="3"/>
       <c r="B657" s="3"/>
       <c r="C657" s="3"/>
@@ -20315,7 +20367,7 @@
       <c r="Z657" s="3"/>
       <c r="AA657" s="3"/>
     </row>
-    <row r="658" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="658">
       <c r="A658" s="3"/>
       <c r="B658" s="3"/>
       <c r="C658" s="3"/>
@@ -20344,7 +20396,7 @@
       <c r="Z658" s="3"/>
       <c r="AA658" s="3"/>
     </row>
-    <row r="659" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="659">
       <c r="A659" s="3"/>
       <c r="B659" s="3"/>
       <c r="C659" s="3"/>
@@ -20373,7 +20425,7 @@
       <c r="Z659" s="3"/>
       <c r="AA659" s="3"/>
     </row>
-    <row r="660" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="660">
       <c r="A660" s="3"/>
       <c r="B660" s="3"/>
       <c r="C660" s="3"/>
@@ -20402,7 +20454,7 @@
       <c r="Z660" s="3"/>
       <c r="AA660" s="3"/>
     </row>
-    <row r="661" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="661">
       <c r="A661" s="3"/>
       <c r="B661" s="3"/>
       <c r="C661" s="3"/>
@@ -20431,7 +20483,7 @@
       <c r="Z661" s="3"/>
       <c r="AA661" s="3"/>
     </row>
-    <row r="662" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="662">
       <c r="A662" s="3"/>
       <c r="B662" s="3"/>
       <c r="C662" s="3"/>
@@ -20460,7 +20512,7 @@
       <c r="Z662" s="3"/>
       <c r="AA662" s="3"/>
     </row>
-    <row r="663" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="663">
       <c r="A663" s="3"/>
       <c r="B663" s="3"/>
       <c r="C663" s="3"/>
@@ -20489,7 +20541,7 @@
       <c r="Z663" s="3"/>
       <c r="AA663" s="3"/>
     </row>
-    <row r="664" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="664">
       <c r="A664" s="3"/>
       <c r="B664" s="3"/>
       <c r="C664" s="3"/>
@@ -20518,7 +20570,7 @@
       <c r="Z664" s="3"/>
       <c r="AA664" s="3"/>
     </row>
-    <row r="665" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="665">
       <c r="A665" s="3"/>
       <c r="B665" s="3"/>
       <c r="C665" s="3"/>
@@ -20547,7 +20599,7 @@
       <c r="Z665" s="3"/>
       <c r="AA665" s="3"/>
     </row>
-    <row r="666" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="666">
       <c r="A666" s="3"/>
       <c r="B666" s="3"/>
       <c r="C666" s="3"/>
@@ -20576,7 +20628,7 @@
       <c r="Z666" s="3"/>
       <c r="AA666" s="3"/>
     </row>
-    <row r="667" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="667">
       <c r="A667" s="3"/>
       <c r="B667" s="3"/>
       <c r="C667" s="3"/>
@@ -20605,7 +20657,7 @@
       <c r="Z667" s="3"/>
       <c r="AA667" s="3"/>
     </row>
-    <row r="668" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="668">
       <c r="A668" s="3"/>
       <c r="B668" s="3"/>
       <c r="C668" s="3"/>
@@ -20634,7 +20686,7 @@
       <c r="Z668" s="3"/>
       <c r="AA668" s="3"/>
     </row>
-    <row r="669" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="669">
       <c r="A669" s="3"/>
       <c r="B669" s="3"/>
       <c r="C669" s="3"/>
@@ -20663,7 +20715,7 @@
       <c r="Z669" s="3"/>
       <c r="AA669" s="3"/>
     </row>
-    <row r="670" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="670">
       <c r="A670" s="3"/>
       <c r="B670" s="3"/>
       <c r="C670" s="3"/>
@@ -20692,7 +20744,7 @@
       <c r="Z670" s="3"/>
       <c r="AA670" s="3"/>
     </row>
-    <row r="671" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="671">
       <c r="A671" s="3"/>
       <c r="B671" s="3"/>
       <c r="C671" s="3"/>
@@ -20721,7 +20773,7 @@
       <c r="Z671" s="3"/>
       <c r="AA671" s="3"/>
     </row>
-    <row r="672" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="672">
       <c r="A672" s="3"/>
       <c r="B672" s="3"/>
       <c r="C672" s="3"/>
@@ -20750,7 +20802,7 @@
       <c r="Z672" s="3"/>
       <c r="AA672" s="3"/>
     </row>
-    <row r="673" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="673">
       <c r="A673" s="3"/>
       <c r="B673" s="3"/>
       <c r="C673" s="3"/>
@@ -20779,7 +20831,7 @@
       <c r="Z673" s="3"/>
       <c r="AA673" s="3"/>
     </row>
-    <row r="674" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="674">
       <c r="A674" s="3"/>
       <c r="B674" s="3"/>
       <c r="C674" s="3"/>
@@ -20808,7 +20860,7 @@
       <c r="Z674" s="3"/>
       <c r="AA674" s="3"/>
     </row>
-    <row r="675" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="675">
       <c r="A675" s="3"/>
       <c r="B675" s="3"/>
       <c r="C675" s="3"/>
@@ -20837,7 +20889,7 @@
       <c r="Z675" s="3"/>
       <c r="AA675" s="3"/>
     </row>
-    <row r="676" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="676">
       <c r="A676" s="3"/>
       <c r="B676" s="3"/>
       <c r="C676" s="3"/>
@@ -20866,7 +20918,7 @@
       <c r="Z676" s="3"/>
       <c r="AA676" s="3"/>
     </row>
-    <row r="677" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="677">
       <c r="A677" s="3"/>
       <c r="B677" s="3"/>
       <c r="C677" s="3"/>
@@ -20895,7 +20947,7 @@
       <c r="Z677" s="3"/>
       <c r="AA677" s="3"/>
     </row>
-    <row r="678" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="678">
       <c r="A678" s="3"/>
       <c r="B678" s="3"/>
       <c r="C678" s="3"/>
@@ -20924,7 +20976,7 @@
       <c r="Z678" s="3"/>
       <c r="AA678" s="3"/>
     </row>
-    <row r="679" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="679">
       <c r="A679" s="3"/>
       <c r="B679" s="3"/>
       <c r="C679" s="3"/>
@@ -20953,7 +21005,7 @@
       <c r="Z679" s="3"/>
       <c r="AA679" s="3"/>
     </row>
-    <row r="680" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="680">
       <c r="A680" s="3"/>
       <c r="B680" s="3"/>
       <c r="C680" s="3"/>
@@ -20982,7 +21034,7 @@
       <c r="Z680" s="3"/>
       <c r="AA680" s="3"/>
     </row>
-    <row r="681" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="681">
       <c r="A681" s="3"/>
       <c r="B681" s="3"/>
       <c r="C681" s="3"/>
@@ -21011,7 +21063,7 @@
       <c r="Z681" s="3"/>
       <c r="AA681" s="3"/>
     </row>
-    <row r="682" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="682">
       <c r="A682" s="3"/>
       <c r="B682" s="3"/>
       <c r="C682" s="3"/>
@@ -21040,7 +21092,7 @@
       <c r="Z682" s="3"/>
       <c r="AA682" s="3"/>
     </row>
-    <row r="683" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="683">
       <c r="A683" s="3"/>
       <c r="B683" s="3"/>
       <c r="C683" s="3"/>
@@ -21069,7 +21121,7 @@
       <c r="Z683" s="3"/>
       <c r="AA683" s="3"/>
     </row>
-    <row r="684" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="684">
       <c r="A684" s="3"/>
       <c r="B684" s="3"/>
       <c r="C684" s="3"/>
@@ -21098,7 +21150,7 @@
       <c r="Z684" s="3"/>
       <c r="AA684" s="3"/>
     </row>
-    <row r="685" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="685">
       <c r="A685" s="3"/>
       <c r="B685" s="3"/>
       <c r="C685" s="3"/>
@@ -21127,7 +21179,7 @@
       <c r="Z685" s="3"/>
       <c r="AA685" s="3"/>
     </row>
-    <row r="686" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="686">
       <c r="A686" s="3"/>
       <c r="B686" s="3"/>
       <c r="C686" s="3"/>
@@ -21156,7 +21208,7 @@
       <c r="Z686" s="3"/>
       <c r="AA686" s="3"/>
     </row>
-    <row r="687" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="687">
       <c r="A687" s="3"/>
       <c r="B687" s="3"/>
       <c r="C687" s="3"/>
@@ -21185,7 +21237,7 @@
       <c r="Z687" s="3"/>
       <c r="AA687" s="3"/>
     </row>
-    <row r="688" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="688">
       <c r="A688" s="3"/>
       <c r="B688" s="3"/>
       <c r="C688" s="3"/>
@@ -21214,7 +21266,7 @@
       <c r="Z688" s="3"/>
       <c r="AA688" s="3"/>
     </row>
-    <row r="689" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="689">
       <c r="A689" s="3"/>
       <c r="B689" s="3"/>
       <c r="C689" s="3"/>
@@ -21243,7 +21295,7 @@
       <c r="Z689" s="3"/>
       <c r="AA689" s="3"/>
     </row>
-    <row r="690" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="690">
       <c r="A690" s="3"/>
       <c r="B690" s="3"/>
       <c r="C690" s="3"/>
@@ -21272,7 +21324,7 @@
       <c r="Z690" s="3"/>
       <c r="AA690" s="3"/>
     </row>
-    <row r="691" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="691">
       <c r="A691" s="3"/>
       <c r="B691" s="3"/>
       <c r="C691" s="3"/>
@@ -21301,7 +21353,7 @@
       <c r="Z691" s="3"/>
       <c r="AA691" s="3"/>
     </row>
-    <row r="692" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="692">
       <c r="A692" s="3"/>
       <c r="B692" s="3"/>
       <c r="C692" s="3"/>
@@ -21330,7 +21382,7 @@
       <c r="Z692" s="3"/>
       <c r="AA692" s="3"/>
     </row>
-    <row r="693" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="693">
       <c r="A693" s="3"/>
       <c r="B693" s="3"/>
       <c r="C693" s="3"/>
@@ -21359,7 +21411,7 @@
       <c r="Z693" s="3"/>
       <c r="AA693" s="3"/>
     </row>
-    <row r="694" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="694">
       <c r="A694" s="3"/>
       <c r="B694" s="3"/>
       <c r="C694" s="3"/>
@@ -21388,7 +21440,7 @@
       <c r="Z694" s="3"/>
       <c r="AA694" s="3"/>
     </row>
-    <row r="695" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="695">
       <c r="A695" s="3"/>
       <c r="B695" s="3"/>
       <c r="C695" s="3"/>
@@ -21417,7 +21469,7 @@
       <c r="Z695" s="3"/>
       <c r="AA695" s="3"/>
     </row>
-    <row r="696" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="696">
       <c r="A696" s="3"/>
       <c r="B696" s="3"/>
       <c r="C696" s="3"/>
@@ -21446,7 +21498,7 @@
       <c r="Z696" s="3"/>
       <c r="AA696" s="3"/>
     </row>
-    <row r="697" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="697">
       <c r="A697" s="3"/>
       <c r="B697" s="3"/>
       <c r="C697" s="3"/>
@@ -21475,7 +21527,7 @@
       <c r="Z697" s="3"/>
       <c r="AA697" s="3"/>
     </row>
-    <row r="698" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="698">
       <c r="A698" s="3"/>
       <c r="B698" s="3"/>
       <c r="C698" s="3"/>
@@ -21504,7 +21556,7 @@
       <c r="Z698" s="3"/>
       <c r="AA698" s="3"/>
     </row>
-    <row r="699" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="699">
       <c r="A699" s="3"/>
       <c r="B699" s="3"/>
       <c r="C699" s="3"/>
@@ -21533,7 +21585,7 @@
       <c r="Z699" s="3"/>
       <c r="AA699" s="3"/>
     </row>
-    <row r="700" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="700">
       <c r="A700" s="3"/>
       <c r="B700" s="3"/>
       <c r="C700" s="3"/>
@@ -21562,7 +21614,7 @@
       <c r="Z700" s="3"/>
       <c r="AA700" s="3"/>
     </row>
-    <row r="701" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="701">
       <c r="A701" s="3"/>
       <c r="B701" s="3"/>
       <c r="C701" s="3"/>
@@ -21591,7 +21643,7 @@
       <c r="Z701" s="3"/>
       <c r="AA701" s="3"/>
     </row>
-    <row r="702" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="702">
       <c r="A702" s="3"/>
       <c r="B702" s="3"/>
       <c r="C702" s="3"/>
@@ -21620,7 +21672,7 @@
       <c r="Z702" s="3"/>
       <c r="AA702" s="3"/>
     </row>
-    <row r="703" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="703">
       <c r="A703" s="3"/>
       <c r="B703" s="3"/>
       <c r="C703" s="3"/>
@@ -21649,7 +21701,7 @@
       <c r="Z703" s="3"/>
       <c r="AA703" s="3"/>
     </row>
-    <row r="704" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="704">
       <c r="A704" s="3"/>
       <c r="B704" s="3"/>
       <c r="C704" s="3"/>
@@ -21678,7 +21730,7 @@
       <c r="Z704" s="3"/>
       <c r="AA704" s="3"/>
     </row>
-    <row r="705" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="705">
       <c r="A705" s="3"/>
       <c r="B705" s="3"/>
       <c r="C705" s="3"/>
@@ -21707,7 +21759,7 @@
       <c r="Z705" s="3"/>
       <c r="AA705" s="3"/>
     </row>
-    <row r="706" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="706">
       <c r="A706" s="3"/>
       <c r="B706" s="3"/>
       <c r="C706" s="3"/>
@@ -21736,7 +21788,7 @@
       <c r="Z706" s="3"/>
       <c r="AA706" s="3"/>
     </row>
-    <row r="707" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="707">
       <c r="A707" s="3"/>
       <c r="B707" s="3"/>
       <c r="C707" s="3"/>
@@ -21765,7 +21817,7 @@
       <c r="Z707" s="3"/>
       <c r="AA707" s="3"/>
     </row>
-    <row r="708" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="708">
       <c r="A708" s="3"/>
       <c r="B708" s="3"/>
       <c r="C708" s="3"/>
@@ -21794,7 +21846,7 @@
       <c r="Z708" s="3"/>
       <c r="AA708" s="3"/>
     </row>
-    <row r="709" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="709">
       <c r="A709" s="3"/>
       <c r="B709" s="3"/>
       <c r="C709" s="3"/>
@@ -21823,7 +21875,7 @@
       <c r="Z709" s="3"/>
       <c r="AA709" s="3"/>
     </row>
-    <row r="710" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="710">
       <c r="A710" s="3"/>
       <c r="B710" s="3"/>
       <c r="C710" s="3"/>
@@ -21852,7 +21904,7 @@
       <c r="Z710" s="3"/>
       <c r="AA710" s="3"/>
     </row>
-    <row r="711" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="711">
       <c r="A711" s="3"/>
       <c r="B711" s="3"/>
       <c r="C711" s="3"/>
@@ -21881,7 +21933,7 @@
       <c r="Z711" s="3"/>
       <c r="AA711" s="3"/>
     </row>
-    <row r="712" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="712">
       <c r="A712" s="3"/>
       <c r="B712" s="3"/>
       <c r="C712" s="3"/>
@@ -21910,7 +21962,7 @@
       <c r="Z712" s="3"/>
       <c r="AA712" s="3"/>
     </row>
-    <row r="713" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="713">
       <c r="A713" s="3"/>
       <c r="B713" s="3"/>
       <c r="C713" s="3"/>
@@ -21939,7 +21991,7 @@
       <c r="Z713" s="3"/>
       <c r="AA713" s="3"/>
     </row>
-    <row r="714" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="714">
       <c r="A714" s="3"/>
       <c r="B714" s="3"/>
       <c r="C714" s="3"/>
@@ -21968,7 +22020,7 @@
       <c r="Z714" s="3"/>
       <c r="AA714" s="3"/>
     </row>
-    <row r="715" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="715">
       <c r="A715" s="3"/>
       <c r="B715" s="3"/>
       <c r="C715" s="3"/>
@@ -21997,7 +22049,7 @@
       <c r="Z715" s="3"/>
       <c r="AA715" s="3"/>
     </row>
-    <row r="716" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="716">
       <c r="A716" s="3"/>
       <c r="B716" s="3"/>
       <c r="C716" s="3"/>
@@ -22026,7 +22078,7 @@
       <c r="Z716" s="3"/>
       <c r="AA716" s="3"/>
     </row>
-    <row r="717" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="717">
       <c r="A717" s="3"/>
       <c r="B717" s="3"/>
       <c r="C717" s="3"/>
@@ -22055,7 +22107,7 @@
       <c r="Z717" s="3"/>
       <c r="AA717" s="3"/>
     </row>
-    <row r="718" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="718">
       <c r="A718" s="3"/>
       <c r="B718" s="3"/>
       <c r="C718" s="3"/>
@@ -22084,7 +22136,7 @@
       <c r="Z718" s="3"/>
       <c r="AA718" s="3"/>
     </row>
-    <row r="719" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="719">
       <c r="A719" s="3"/>
       <c r="B719" s="3"/>
       <c r="C719" s="3"/>
@@ -22113,7 +22165,7 @@
       <c r="Z719" s="3"/>
       <c r="AA719" s="3"/>
     </row>
-    <row r="720" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="720">
       <c r="A720" s="3"/>
       <c r="B720" s="3"/>
       <c r="C720" s="3"/>
@@ -22142,7 +22194,7 @@
       <c r="Z720" s="3"/>
       <c r="AA720" s="3"/>
     </row>
-    <row r="721" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="721">
       <c r="A721" s="3"/>
       <c r="B721" s="3"/>
       <c r="C721" s="3"/>
@@ -22171,7 +22223,7 @@
       <c r="Z721" s="3"/>
       <c r="AA721" s="3"/>
     </row>
-    <row r="722" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="722">
       <c r="A722" s="3"/>
       <c r="B722" s="3"/>
       <c r="C722" s="3"/>
@@ -22200,7 +22252,7 @@
       <c r="Z722" s="3"/>
       <c r="AA722" s="3"/>
     </row>
-    <row r="723" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="723">
       <c r="A723" s="3"/>
       <c r="B723" s="3"/>
       <c r="C723" s="3"/>
@@ -22229,7 +22281,7 @@
       <c r="Z723" s="3"/>
       <c r="AA723" s="3"/>
     </row>
-    <row r="724" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="724">
       <c r="A724" s="3"/>
       <c r="B724" s="3"/>
       <c r="C724" s="3"/>
@@ -22258,7 +22310,7 @@
       <c r="Z724" s="3"/>
       <c r="AA724" s="3"/>
     </row>
-    <row r="725" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="725">
       <c r="A725" s="3"/>
       <c r="B725" s="3"/>
       <c r="C725" s="3"/>
@@ -22287,7 +22339,7 @@
       <c r="Z725" s="3"/>
       <c r="AA725" s="3"/>
     </row>
-    <row r="726" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="726">
       <c r="A726" s="3"/>
       <c r="B726" s="3"/>
       <c r="C726" s="3"/>
@@ -22316,7 +22368,7 @@
       <c r="Z726" s="3"/>
       <c r="AA726" s="3"/>
     </row>
-    <row r="727" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="727">
       <c r="A727" s="3"/>
       <c r="B727" s="3"/>
       <c r="C727" s="3"/>
@@ -22345,7 +22397,7 @@
       <c r="Z727" s="3"/>
       <c r="AA727" s="3"/>
     </row>
-    <row r="728" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="728">
       <c r="A728" s="3"/>
       <c r="B728" s="3"/>
       <c r="C728" s="3"/>
@@ -22374,7 +22426,7 @@
       <c r="Z728" s="3"/>
       <c r="AA728" s="3"/>
     </row>
-    <row r="729" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="729">
       <c r="A729" s="3"/>
       <c r="B729" s="3"/>
       <c r="C729" s="3"/>
@@ -22403,7 +22455,7 @@
       <c r="Z729" s="3"/>
       <c r="AA729" s="3"/>
     </row>
-    <row r="730" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="730">
       <c r="A730" s="3"/>
       <c r="B730" s="3"/>
       <c r="C730" s="3"/>
@@ -22432,7 +22484,7 @@
       <c r="Z730" s="3"/>
       <c r="AA730" s="3"/>
     </row>
-    <row r="731" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="731">
       <c r="A731" s="3"/>
       <c r="B731" s="3"/>
       <c r="C731" s="3"/>
@@ -22461,7 +22513,7 @@
       <c r="Z731" s="3"/>
       <c r="AA731" s="3"/>
     </row>
-    <row r="732" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="732">
       <c r="A732" s="3"/>
       <c r="B732" s="3"/>
       <c r="C732" s="3"/>
@@ -22490,7 +22542,7 @@
       <c r="Z732" s="3"/>
       <c r="AA732" s="3"/>
     </row>
-    <row r="733" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="733">
       <c r="A733" s="3"/>
       <c r="B733" s="3"/>
       <c r="C733" s="3"/>
@@ -22519,7 +22571,7 @@
       <c r="Z733" s="3"/>
       <c r="AA733" s="3"/>
     </row>
-    <row r="734" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="734">
       <c r="A734" s="3"/>
       <c r="B734" s="3"/>
       <c r="C734" s="3"/>
@@ -22548,7 +22600,7 @@
       <c r="Z734" s="3"/>
       <c r="AA734" s="3"/>
     </row>
-    <row r="735" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="735">
       <c r="A735" s="3"/>
       <c r="B735" s="3"/>
       <c r="C735" s="3"/>
@@ -22577,7 +22629,7 @@
       <c r="Z735" s="3"/>
       <c r="AA735" s="3"/>
     </row>
-    <row r="736" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="736">
       <c r="A736" s="3"/>
       <c r="B736" s="3"/>
       <c r="C736" s="3"/>
@@ -22606,7 +22658,7 @@
       <c r="Z736" s="3"/>
       <c r="AA736" s="3"/>
     </row>
-    <row r="737" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="737">
       <c r="A737" s="3"/>
       <c r="B737" s="3"/>
       <c r="C737" s="3"/>
@@ -22635,7 +22687,7 @@
       <c r="Z737" s="3"/>
       <c r="AA737" s="3"/>
     </row>
-    <row r="738" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="738">
       <c r="A738" s="3"/>
       <c r="B738" s="3"/>
       <c r="C738" s="3"/>
@@ -22664,7 +22716,7 @@
       <c r="Z738" s="3"/>
       <c r="AA738" s="3"/>
     </row>
-    <row r="739" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="739">
       <c r="A739" s="3"/>
       <c r="B739" s="3"/>
       <c r="C739" s="3"/>
@@ -22693,7 +22745,7 @@
       <c r="Z739" s="3"/>
       <c r="AA739" s="3"/>
     </row>
-    <row r="740" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="740">
       <c r="A740" s="3"/>
       <c r="B740" s="3"/>
       <c r="C740" s="3"/>
@@ -22722,7 +22774,7 @@
       <c r="Z740" s="3"/>
       <c r="AA740" s="3"/>
     </row>
-    <row r="741" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="741">
       <c r="A741" s="3"/>
       <c r="B741" s="3"/>
       <c r="C741" s="3"/>
@@ -22751,7 +22803,7 @@
       <c r="Z741" s="3"/>
       <c r="AA741" s="3"/>
     </row>
-    <row r="742" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="742">
       <c r="A742" s="3"/>
       <c r="B742" s="3"/>
       <c r="C742" s="3"/>
@@ -22780,7 +22832,7 @@
       <c r="Z742" s="3"/>
       <c r="AA742" s="3"/>
     </row>
-    <row r="743" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="743">
       <c r="A743" s="3"/>
       <c r="B743" s="3"/>
       <c r="C743" s="3"/>
@@ -22809,7 +22861,7 @@
       <c r="Z743" s="3"/>
       <c r="AA743" s="3"/>
     </row>
-    <row r="744" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="744">
       <c r="A744" s="3"/>
       <c r="B744" s="3"/>
       <c r="C744" s="3"/>
@@ -22838,7 +22890,7 @@
       <c r="Z744" s="3"/>
       <c r="AA744" s="3"/>
     </row>
-    <row r="745" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="745">
       <c r="A745" s="3"/>
       <c r="B745" s="3"/>
       <c r="C745" s="3"/>
@@ -22867,7 +22919,7 @@
       <c r="Z745" s="3"/>
       <c r="AA745" s="3"/>
     </row>
-    <row r="746" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="746">
       <c r="A746" s="3"/>
       <c r="B746" s="3"/>
       <c r="C746" s="3"/>
@@ -22896,7 +22948,7 @@
       <c r="Z746" s="3"/>
       <c r="AA746" s="3"/>
     </row>
-    <row r="747" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="747">
       <c r="A747" s="3"/>
       <c r="B747" s="3"/>
       <c r="C747" s="3"/>
@@ -22925,7 +22977,7 @@
       <c r="Z747" s="3"/>
       <c r="AA747" s="3"/>
     </row>
-    <row r="748" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="748">
       <c r="A748" s="3"/>
       <c r="B748" s="3"/>
       <c r="C748" s="3"/>
@@ -22954,7 +23006,7 @@
       <c r="Z748" s="3"/>
       <c r="AA748" s="3"/>
     </row>
-    <row r="749" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="749">
       <c r="A749" s="3"/>
       <c r="B749" s="3"/>
       <c r="C749" s="3"/>
@@ -22983,7 +23035,7 @@
       <c r="Z749" s="3"/>
       <c r="AA749" s="3"/>
     </row>
-    <row r="750" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="750">
       <c r="A750" s="3"/>
       <c r="B750" s="3"/>
       <c r="C750" s="3"/>
@@ -23012,7 +23064,7 @@
       <c r="Z750" s="3"/>
       <c r="AA750" s="3"/>
     </row>
-    <row r="751" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="751">
       <c r="A751" s="3"/>
       <c r="B751" s="3"/>
       <c r="C751" s="3"/>
@@ -23041,7 +23093,7 @@
       <c r="Z751" s="3"/>
       <c r="AA751" s="3"/>
     </row>
-    <row r="752" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="752">
       <c r="A752" s="3"/>
       <c r="B752" s="3"/>
       <c r="C752" s="3"/>
@@ -23070,7 +23122,7 @@
       <c r="Z752" s="3"/>
       <c r="AA752" s="3"/>
     </row>
-    <row r="753" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="753">
       <c r="A753" s="3"/>
       <c r="B753" s="3"/>
       <c r="C753" s="3"/>
@@ -23099,7 +23151,7 @@
       <c r="Z753" s="3"/>
       <c r="AA753" s="3"/>
     </row>
-    <row r="754" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="754">
       <c r="A754" s="3"/>
       <c r="B754" s="3"/>
       <c r="C754" s="3"/>
@@ -23128,7 +23180,7 @@
       <c r="Z754" s="3"/>
       <c r="AA754" s="3"/>
     </row>
-    <row r="755" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="755">
       <c r="A755" s="3"/>
       <c r="B755" s="3"/>
       <c r="C755" s="3"/>
@@ -23157,7 +23209,7 @@
       <c r="Z755" s="3"/>
       <c r="AA755" s="3"/>
     </row>
-    <row r="756" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="756">
       <c r="A756" s="3"/>
       <c r="B756" s="3"/>
       <c r="C756" s="3"/>
@@ -23186,7 +23238,7 @@
       <c r="Z756" s="3"/>
       <c r="AA756" s="3"/>
     </row>
-    <row r="757" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="757">
       <c r="A757" s="3"/>
       <c r="B757" s="3"/>
       <c r="C757" s="3"/>
@@ -23215,7 +23267,7 @@
       <c r="Z757" s="3"/>
       <c r="AA757" s="3"/>
     </row>
-    <row r="758" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="758">
       <c r="A758" s="3"/>
       <c r="B758" s="3"/>
       <c r="C758" s="3"/>
@@ -23244,7 +23296,7 @@
       <c r="Z758" s="3"/>
       <c r="AA758" s="3"/>
     </row>
-    <row r="759" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="759">
       <c r="A759" s="3"/>
       <c r="B759" s="3"/>
       <c r="C759" s="3"/>
@@ -23273,7 +23325,7 @@
       <c r="Z759" s="3"/>
       <c r="AA759" s="3"/>
     </row>
-    <row r="760" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="760">
       <c r="A760" s="3"/>
       <c r="B760" s="3"/>
       <c r="C760" s="3"/>
@@ -23302,7 +23354,7 @@
       <c r="Z760" s="3"/>
       <c r="AA760" s="3"/>
     </row>
-    <row r="761" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="761">
       <c r="A761" s="3"/>
       <c r="B761" s="3"/>
       <c r="C761" s="3"/>
@@ -23331,7 +23383,7 @@
       <c r="Z761" s="3"/>
       <c r="AA761" s="3"/>
     </row>
-    <row r="762" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="762">
       <c r="A762" s="3"/>
       <c r="B762" s="3"/>
       <c r="C762" s="3"/>
@@ -23360,7 +23412,7 @@
       <c r="Z762" s="3"/>
       <c r="AA762" s="3"/>
     </row>
-    <row r="763" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="763">
       <c r="A763" s="3"/>
       <c r="B763" s="3"/>
       <c r="C763" s="3"/>
@@ -23389,7 +23441,7 @@
       <c r="Z763" s="3"/>
       <c r="AA763" s="3"/>
     </row>
-    <row r="764" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="764">
       <c r="A764" s="3"/>
       <c r="B764" s="3"/>
       <c r="C764" s="3"/>
@@ -23418,7 +23470,7 @@
       <c r="Z764" s="3"/>
       <c r="AA764" s="3"/>
     </row>
-    <row r="765" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="765">
       <c r="A765" s="3"/>
       <c r="B765" s="3"/>
       <c r="C765" s="3"/>
@@ -23447,7 +23499,7 @@
       <c r="Z765" s="3"/>
       <c r="AA765" s="3"/>
     </row>
-    <row r="766" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="766">
       <c r="A766" s="3"/>
       <c r="B766" s="3"/>
       <c r="C766" s="3"/>
@@ -23476,7 +23528,7 @@
       <c r="Z766" s="3"/>
       <c r="AA766" s="3"/>
     </row>
-    <row r="767" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="767">
       <c r="A767" s="3"/>
       <c r="B767" s="3"/>
       <c r="C767" s="3"/>
@@ -23505,7 +23557,7 @@
       <c r="Z767" s="3"/>
       <c r="AA767" s="3"/>
     </row>
-    <row r="768" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="768">
       <c r="A768" s="3"/>
       <c r="B768" s="3"/>
       <c r="C768" s="3"/>
@@ -23534,7 +23586,7 @@
       <c r="Z768" s="3"/>
       <c r="AA768" s="3"/>
     </row>
-    <row r="769" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="769">
       <c r="A769" s="3"/>
       <c r="B769" s="3"/>
       <c r="C769" s="3"/>
@@ -23563,7 +23615,7 @@
       <c r="Z769" s="3"/>
       <c r="AA769" s="3"/>
     </row>
-    <row r="770" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="770">
       <c r="A770" s="3"/>
       <c r="B770" s="3"/>
       <c r="C770" s="3"/>
@@ -23592,7 +23644,7 @@
       <c r="Z770" s="3"/>
       <c r="AA770" s="3"/>
     </row>
-    <row r="771" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="771">
       <c r="A771" s="3"/>
       <c r="B771" s="3"/>
       <c r="C771" s="3"/>
@@ -23621,7 +23673,7 @@
       <c r="Z771" s="3"/>
       <c r="AA771" s="3"/>
     </row>
-    <row r="772" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="772">
       <c r="A772" s="3"/>
       <c r="B772" s="3"/>
       <c r="C772" s="3"/>
@@ -23650,7 +23702,7 @@
       <c r="Z772" s="3"/>
       <c r="AA772" s="3"/>
     </row>
-    <row r="773" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="773">
       <c r="A773" s="3"/>
       <c r="B773" s="3"/>
       <c r="C773" s="3"/>
@@ -23679,7 +23731,7 @@
       <c r="Z773" s="3"/>
       <c r="AA773" s="3"/>
     </row>
-    <row r="774" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="774">
       <c r="A774" s="3"/>
       <c r="B774" s="3"/>
       <c r="C774" s="3"/>
@@ -23708,7 +23760,7 @@
       <c r="Z774" s="3"/>
       <c r="AA774" s="3"/>
     </row>
-    <row r="775" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="775">
       <c r="A775" s="3"/>
       <c r="B775" s="3"/>
       <c r="C775" s="3"/>
@@ -23737,7 +23789,7 @@
       <c r="Z775" s="3"/>
       <c r="AA775" s="3"/>
     </row>
-    <row r="776" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="776">
       <c r="A776" s="3"/>
       <c r="B776" s="3"/>
       <c r="C776" s="3"/>
@@ -23766,7 +23818,7 @@
       <c r="Z776" s="3"/>
       <c r="AA776" s="3"/>
     </row>
-    <row r="777" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="777">
       <c r="A777" s="3"/>
       <c r="B777" s="3"/>
       <c r="C777" s="3"/>
@@ -23795,7 +23847,7 @@
       <c r="Z777" s="3"/>
       <c r="AA777" s="3"/>
     </row>
-    <row r="778" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="778">
       <c r="A778" s="3"/>
       <c r="B778" s="3"/>
       <c r="C778" s="3"/>
@@ -23824,7 +23876,7 @@
       <c r="Z778" s="3"/>
       <c r="AA778" s="3"/>
     </row>
-    <row r="779" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="779">
       <c r="A779" s="3"/>
       <c r="B779" s="3"/>
       <c r="C779" s="3"/>
@@ -23853,7 +23905,7 @@
       <c r="Z779" s="3"/>
       <c r="AA779" s="3"/>
     </row>
-    <row r="780" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="780">
       <c r="A780" s="3"/>
       <c r="B780" s="3"/>
       <c r="C780" s="3"/>
@@ -23882,7 +23934,7 @@
       <c r="Z780" s="3"/>
       <c r="AA780" s="3"/>
     </row>
-    <row r="781" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="781">
       <c r="A781" s="3"/>
       <c r="B781" s="3"/>
       <c r="C781" s="3"/>
@@ -23911,7 +23963,7 @@
       <c r="Z781" s="3"/>
       <c r="AA781" s="3"/>
     </row>
-    <row r="782" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="782">
       <c r="A782" s="3"/>
       <c r="B782" s="3"/>
       <c r="C782" s="3"/>
@@ -23940,7 +23992,7 @@
       <c r="Z782" s="3"/>
       <c r="AA782" s="3"/>
     </row>
-    <row r="783" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="783">
       <c r="A783" s="3"/>
       <c r="B783" s="3"/>
       <c r="C783" s="3"/>
@@ -23969,7 +24021,7 @@
       <c r="Z783" s="3"/>
       <c r="AA783" s="3"/>
     </row>
-    <row r="784" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="784">
       <c r="A784" s="3"/>
       <c r="B784" s="3"/>
       <c r="C784" s="3"/>
@@ -23998,7 +24050,7 @@
       <c r="Z784" s="3"/>
       <c r="AA784" s="3"/>
     </row>
-    <row r="785" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="785">
       <c r="A785" s="3"/>
       <c r="B785" s="3"/>
       <c r="C785" s="3"/>
@@ -24027,7 +24079,7 @@
       <c r="Z785" s="3"/>
       <c r="AA785" s="3"/>
     </row>
-    <row r="786" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="786">
       <c r="A786" s="3"/>
       <c r="B786" s="3"/>
       <c r="C786" s="3"/>
@@ -24056,7 +24108,7 @@
       <c r="Z786" s="3"/>
       <c r="AA786" s="3"/>
     </row>
-    <row r="787" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="787">
       <c r="A787" s="3"/>
       <c r="B787" s="3"/>
       <c r="C787" s="3"/>
@@ -24085,7 +24137,7 @@
       <c r="Z787" s="3"/>
       <c r="AA787" s="3"/>
     </row>
-    <row r="788" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="788">
       <c r="A788" s="3"/>
       <c r="B788" s="3"/>
       <c r="C788" s="3"/>
@@ -24114,7 +24166,7 @@
       <c r="Z788" s="3"/>
       <c r="AA788" s="3"/>
     </row>
-    <row r="789" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="789">
       <c r="A789" s="3"/>
       <c r="B789" s="3"/>
       <c r="C789" s="3"/>
@@ -24143,7 +24195,7 @@
       <c r="Z789" s="3"/>
       <c r="AA789" s="3"/>
     </row>
-    <row r="790" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="790">
       <c r="A790" s="3"/>
       <c r="B790" s="3"/>
       <c r="C790" s="3"/>
@@ -24172,7 +24224,7 @@
       <c r="Z790" s="3"/>
       <c r="AA790" s="3"/>
     </row>
-    <row r="791" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="791">
       <c r="A791" s="3"/>
       <c r="B791" s="3"/>
       <c r="C791" s="3"/>
@@ -24201,7 +24253,7 @@
       <c r="Z791" s="3"/>
       <c r="AA791" s="3"/>
     </row>
-    <row r="792" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="792">
       <c r="A792" s="3"/>
       <c r="B792" s="3"/>
       <c r="C792" s="3"/>
@@ -24230,7 +24282,7 @@
       <c r="Z792" s="3"/>
       <c r="AA792" s="3"/>
     </row>
-    <row r="793" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="793">
       <c r="A793" s="3"/>
       <c r="B793" s="3"/>
       <c r="C793" s="3"/>
@@ -24259,7 +24311,7 @@
       <c r="Z793" s="3"/>
       <c r="AA793" s="3"/>
     </row>
-    <row r="794" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="794">
       <c r="A794" s="3"/>
       <c r="B794" s="3"/>
       <c r="C794" s="3"/>
@@ -24288,7 +24340,7 @@
       <c r="Z794" s="3"/>
       <c r="AA794" s="3"/>
     </row>
-    <row r="795" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="795">
       <c r="A795" s="3"/>
       <c r="B795" s="3"/>
       <c r="C795" s="3"/>
@@ -24317,7 +24369,7 @@
       <c r="Z795" s="3"/>
       <c r="AA795" s="3"/>
     </row>
-    <row r="796" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="796">
       <c r="A796" s="3"/>
       <c r="B796" s="3"/>
       <c r="C796" s="3"/>
@@ -24346,7 +24398,7 @@
       <c r="Z796" s="3"/>
       <c r="AA796" s="3"/>
     </row>
-    <row r="797" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="797">
       <c r="A797" s="3"/>
       <c r="B797" s="3"/>
       <c r="C797" s="3"/>
@@ -24375,7 +24427,7 @@
       <c r="Z797" s="3"/>
       <c r="AA797" s="3"/>
     </row>
-    <row r="798" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="798">
       <c r="A798" s="3"/>
       <c r="B798" s="3"/>
       <c r="C798" s="3"/>
@@ -24404,7 +24456,7 @@
       <c r="Z798" s="3"/>
       <c r="AA798" s="3"/>
     </row>
-    <row r="799" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="799">
       <c r="A799" s="3"/>
       <c r="B799" s="3"/>
       <c r="C799" s="3"/>
@@ -24433,7 +24485,7 @@
       <c r="Z799" s="3"/>
       <c r="AA799" s="3"/>
     </row>
-    <row r="800" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="800">
       <c r="A800" s="3"/>
       <c r="B800" s="3"/>
       <c r="C800" s="3"/>
@@ -24462,7 +24514,7 @@
       <c r="Z800" s="3"/>
       <c r="AA800" s="3"/>
     </row>
-    <row r="801" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="801">
       <c r="A801" s="3"/>
       <c r="B801" s="3"/>
       <c r="C801" s="3"/>
@@ -24491,7 +24543,7 @@
       <c r="Z801" s="3"/>
       <c r="AA801" s="3"/>
     </row>
-    <row r="802" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="802">
       <c r="A802" s="3"/>
       <c r="B802" s="3"/>
       <c r="C802" s="3"/>
@@ -24520,7 +24572,7 @@
       <c r="Z802" s="3"/>
       <c r="AA802" s="3"/>
     </row>
-    <row r="803" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="803">
       <c r="A803" s="3"/>
       <c r="B803" s="3"/>
       <c r="C803" s="3"/>
@@ -24549,7 +24601,7 @@
       <c r="Z803" s="3"/>
       <c r="AA803" s="3"/>
     </row>
-    <row r="804" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="804">
       <c r="A804" s="3"/>
       <c r="B804" s="3"/>
       <c r="C804" s="3"/>
@@ -24578,7 +24630,7 @@
       <c r="Z804" s="3"/>
       <c r="AA804" s="3"/>
     </row>
-    <row r="805" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="805">
       <c r="A805" s="3"/>
       <c r="B805" s="3"/>
       <c r="C805" s="3"/>
@@ -24607,7 +24659,7 @@
       <c r="Z805" s="3"/>
       <c r="AA805" s="3"/>
     </row>
-    <row r="806" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="806">
       <c r="A806" s="3"/>
       <c r="B806" s="3"/>
       <c r="C806" s="3"/>
@@ -24636,7 +24688,7 @@
       <c r="Z806" s="3"/>
       <c r="AA806" s="3"/>
     </row>
-    <row r="807" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="807">
       <c r="A807" s="3"/>
       <c r="B807" s="3"/>
       <c r="C807" s="3"/>
@@ -24665,7 +24717,7 @@
       <c r="Z807" s="3"/>
       <c r="AA807" s="3"/>
     </row>
-    <row r="808" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="808">
       <c r="A808" s="3"/>
       <c r="B808" s="3"/>
       <c r="C808" s="3"/>
@@ -24694,7 +24746,7 @@
       <c r="Z808" s="3"/>
       <c r="AA808" s="3"/>
     </row>
-    <row r="809" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="809">
       <c r="A809" s="3"/>
       <c r="B809" s="3"/>
       <c r="C809" s="3"/>
@@ -24723,7 +24775,7 @@
       <c r="Z809" s="3"/>
       <c r="AA809" s="3"/>
     </row>
-    <row r="810" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="810">
       <c r="A810" s="3"/>
       <c r="B810" s="3"/>
       <c r="C810" s="3"/>
@@ -24752,7 +24804,7 @@
       <c r="Z810" s="3"/>
       <c r="AA810" s="3"/>
     </row>
-    <row r="811" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="811">
       <c r="A811" s="3"/>
       <c r="B811" s="3"/>
       <c r="C811" s="3"/>
@@ -24781,7 +24833,7 @@
       <c r="Z811" s="3"/>
       <c r="AA811" s="3"/>
     </row>
-    <row r="812" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="812">
       <c r="A812" s="3"/>
       <c r="B812" s="3"/>
       <c r="C812" s="3"/>
@@ -24810,7 +24862,7 @@
       <c r="Z812" s="3"/>
       <c r="AA812" s="3"/>
     </row>
-    <row r="813" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="813">
       <c r="A813" s="3"/>
       <c r="B813" s="3"/>
       <c r="C813" s="3"/>
@@ -24839,7 +24891,7 @@
       <c r="Z813" s="3"/>
       <c r="AA813" s="3"/>
     </row>
-    <row r="814" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="814">
       <c r="A814" s="3"/>
       <c r="B814" s="3"/>
       <c r="C814" s="3"/>
@@ -24868,7 +24920,7 @@
       <c r="Z814" s="3"/>
       <c r="AA814" s="3"/>
     </row>
-    <row r="815" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="815">
       <c r="A815" s="3"/>
       <c r="B815" s="3"/>
       <c r="C815" s="3"/>
@@ -24897,7 +24949,7 @@
       <c r="Z815" s="3"/>
       <c r="AA815" s="3"/>
     </row>
-    <row r="816" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="816">
       <c r="A816" s="3"/>
       <c r="B816" s="3"/>
       <c r="C816" s="3"/>
@@ -24926,7 +24978,7 @@
       <c r="Z816" s="3"/>
       <c r="AA816" s="3"/>
     </row>
-    <row r="817" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="817">
       <c r="A817" s="3"/>
       <c r="B817" s="3"/>
       <c r="C817" s="3"/>
@@ -24955,7 +25007,7 @@
       <c r="Z817" s="3"/>
       <c r="AA817" s="3"/>
     </row>
-    <row r="818" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="818">
       <c r="A818" s="3"/>
       <c r="B818" s="3"/>
       <c r="C818" s="3"/>
@@ -24984,7 +25036,7 @@
       <c r="Z818" s="3"/>
       <c r="AA818" s="3"/>
     </row>
-    <row r="819" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="819">
       <c r="A819" s="3"/>
       <c r="B819" s="3"/>
       <c r="C819" s="3"/>
@@ -25013,7 +25065,7 @@
       <c r="Z819" s="3"/>
       <c r="AA819" s="3"/>
     </row>
-    <row r="820" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="820">
       <c r="A820" s="3"/>
       <c r="B820" s="3"/>
       <c r="C820" s="3"/>
@@ -25042,7 +25094,7 @@
       <c r="Z820" s="3"/>
       <c r="AA820" s="3"/>
     </row>
-    <row r="821" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="821">
       <c r="A821" s="3"/>
       <c r="B821" s="3"/>
       <c r="C821" s="3"/>
@@ -25071,7 +25123,7 @@
       <c r="Z821" s="3"/>
       <c r="AA821" s="3"/>
     </row>
-    <row r="822" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="822">
       <c r="A822" s="3"/>
       <c r="B822" s="3"/>
       <c r="C822" s="3"/>
@@ -25100,7 +25152,7 @@
       <c r="Z822" s="3"/>
       <c r="AA822" s="3"/>
     </row>
-    <row r="823" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="823">
       <c r="A823" s="3"/>
       <c r="B823" s="3"/>
       <c r="C823" s="3"/>
@@ -25129,7 +25181,7 @@
       <c r="Z823" s="3"/>
       <c r="AA823" s="3"/>
     </row>
-    <row r="824" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="824">
       <c r="A824" s="3"/>
       <c r="B824" s="3"/>
       <c r="C824" s="3"/>
@@ -25158,7 +25210,7 @@
       <c r="Z824" s="3"/>
       <c r="AA824" s="3"/>
     </row>
-    <row r="825" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="825">
       <c r="A825" s="3"/>
       <c r="B825" s="3"/>
       <c r="C825" s="3"/>
@@ -25187,7 +25239,7 @@
       <c r="Z825" s="3"/>
       <c r="AA825" s="3"/>
     </row>
-    <row r="826" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="826">
       <c r="A826" s="3"/>
       <c r="B826" s="3"/>
       <c r="C826" s="3"/>
@@ -25216,7 +25268,7 @@
       <c r="Z826" s="3"/>
       <c r="AA826" s="3"/>
     </row>
-    <row r="827" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="827">
       <c r="A827" s="3"/>
       <c r="B827" s="3"/>
       <c r="C827" s="3"/>
@@ -25245,7 +25297,7 @@
       <c r="Z827" s="3"/>
       <c r="AA827" s="3"/>
     </row>
-    <row r="828" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="828">
       <c r="A828" s="3"/>
       <c r="B828" s="3"/>
       <c r="C828" s="3"/>
@@ -25274,7 +25326,7 @@
       <c r="Z828" s="3"/>
       <c r="AA828" s="3"/>
     </row>
-    <row r="829" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="829">
       <c r="A829" s="3"/>
       <c r="B829" s="3"/>
       <c r="C829" s="3"/>
@@ -25303,7 +25355,7 @@
       <c r="Z829" s="3"/>
       <c r="AA829" s="3"/>
     </row>
-    <row r="830" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="830">
       <c r="A830" s="3"/>
       <c r="B830" s="3"/>
       <c r="C830" s="3"/>
@@ -25332,7 +25384,7 @@
       <c r="Z830" s="3"/>
       <c r="AA830" s="3"/>
     </row>
-    <row r="831" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="831">
       <c r="A831" s="3"/>
       <c r="B831" s="3"/>
       <c r="C831" s="3"/>
@@ -25361,7 +25413,7 @@
       <c r="Z831" s="3"/>
       <c r="AA831" s="3"/>
     </row>
-    <row r="832" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="832">
       <c r="A832" s="3"/>
       <c r="B832" s="3"/>
       <c r="C832" s="3"/>
@@ -25390,7 +25442,7 @@
       <c r="Z832" s="3"/>
       <c r="AA832" s="3"/>
     </row>
-    <row r="833" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="833">
       <c r="A833" s="3"/>
       <c r="B833" s="3"/>
       <c r="C833" s="3"/>
@@ -25419,7 +25471,7 @@
       <c r="Z833" s="3"/>
       <c r="AA833" s="3"/>
     </row>
-    <row r="834" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="834">
       <c r="A834" s="3"/>
       <c r="B834" s="3"/>
       <c r="C834" s="3"/>
@@ -25448,7 +25500,7 @@
       <c r="Z834" s="3"/>
       <c r="AA834" s="3"/>
     </row>
-    <row r="835" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="835">
       <c r="A835" s="3"/>
       <c r="B835" s="3"/>
       <c r="C835" s="3"/>
@@ -25477,7 +25529,7 @@
       <c r="Z835" s="3"/>
       <c r="AA835" s="3"/>
     </row>
-    <row r="836" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="836">
       <c r="A836" s="3"/>
       <c r="B836" s="3"/>
       <c r="C836" s="3"/>
@@ -25506,7 +25558,7 @@
       <c r="Z836" s="3"/>
       <c r="AA836" s="3"/>
     </row>
-    <row r="837" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="837">
       <c r="A837" s="3"/>
       <c r="B837" s="3"/>
       <c r="C837" s="3"/>
@@ -25535,7 +25587,7 @@
       <c r="Z837" s="3"/>
       <c r="AA837" s="3"/>
     </row>
-    <row r="838" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="838">
       <c r="A838" s="3"/>
       <c r="B838" s="3"/>
       <c r="C838" s="3"/>
@@ -25564,7 +25616,7 @@
       <c r="Z838" s="3"/>
       <c r="AA838" s="3"/>
     </row>
-    <row r="839" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="839">
       <c r="A839" s="3"/>
       <c r="B839" s="3"/>
       <c r="C839" s="3"/>
@@ -25593,7 +25645,7 @@
       <c r="Z839" s="3"/>
       <c r="AA839" s="3"/>
     </row>
-    <row r="840" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="840">
       <c r="A840" s="3"/>
       <c r="B840" s="3"/>
       <c r="C840" s="3"/>
@@ -25622,7 +25674,7 @@
       <c r="Z840" s="3"/>
       <c r="AA840" s="3"/>
     </row>
-    <row r="841" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="841">
       <c r="A841" s="3"/>
       <c r="B841" s="3"/>
       <c r="C841" s="3"/>
@@ -25651,7 +25703,7 @@
       <c r="Z841" s="3"/>
       <c r="AA841" s="3"/>
     </row>
-    <row r="842" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="842">
       <c r="A842" s="3"/>
       <c r="B842" s="3"/>
       <c r="C842" s="3"/>
@@ -25680,7 +25732,7 @@
       <c r="Z842" s="3"/>
       <c r="AA842" s="3"/>
     </row>
-    <row r="843" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="843">
       <c r="A843" s="3"/>
       <c r="B843" s="3"/>
       <c r="C843" s="3"/>
@@ -25709,7 +25761,7 @@
       <c r="Z843" s="3"/>
       <c r="AA843" s="3"/>
     </row>
-    <row r="844" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="844">
       <c r="A844" s="3"/>
       <c r="B844" s="3"/>
       <c r="C844" s="3"/>
@@ -25738,7 +25790,7 @@
       <c r="Z844" s="3"/>
       <c r="AA844" s="3"/>
     </row>
-    <row r="845" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="845">
       <c r="A845" s="3"/>
       <c r="B845" s="3"/>
       <c r="C845" s="3"/>
@@ -25767,7 +25819,7 @@
       <c r="Z845" s="3"/>
       <c r="AA845" s="3"/>
     </row>
-    <row r="846" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="846">
       <c r="A846" s="3"/>
       <c r="B846" s="3"/>
       <c r="C846" s="3"/>
@@ -25796,7 +25848,7 @@
       <c r="Z846" s="3"/>
       <c r="AA846" s="3"/>
     </row>
-    <row r="847" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="847">
       <c r="A847" s="3"/>
       <c r="B847" s="3"/>
       <c r="C847" s="3"/>
@@ -25825,7 +25877,7 @@
       <c r="Z847" s="3"/>
       <c r="AA847" s="3"/>
     </row>
-    <row r="848" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="848">
       <c r="A848" s="3"/>
       <c r="B848" s="3"/>
       <c r="C848" s="3"/>
@@ -25854,7 +25906,7 @@
       <c r="Z848" s="3"/>
       <c r="AA848" s="3"/>
     </row>
-    <row r="849" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="849">
       <c r="A849" s="3"/>
       <c r="B849" s="3"/>
       <c r="C849" s="3"/>
@@ -25883,7 +25935,7 @@
       <c r="Z849" s="3"/>
       <c r="AA849" s="3"/>
     </row>
-    <row r="850" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="850">
       <c r="A850" s="3"/>
       <c r="B850" s="3"/>
       <c r="C850" s="3"/>
@@ -25912,7 +25964,7 @@
       <c r="Z850" s="3"/>
       <c r="AA850" s="3"/>
     </row>
-    <row r="851" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="851">
       <c r="A851" s="3"/>
       <c r="B851" s="3"/>
       <c r="C851" s="3"/>
@@ -25941,7 +25993,7 @@
       <c r="Z851" s="3"/>
       <c r="AA851" s="3"/>
     </row>
-    <row r="852" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="852">
       <c r="A852" s="3"/>
       <c r="B852" s="3"/>
       <c r="C852" s="3"/>
@@ -25970,7 +26022,7 @@
       <c r="Z852" s="3"/>
       <c r="AA852" s="3"/>
     </row>
-    <row r="853" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="853">
       <c r="A853" s="3"/>
       <c r="B853" s="3"/>
       <c r="C853" s="3"/>
@@ -25999,7 +26051,7 @@
       <c r="Z853" s="3"/>
       <c r="AA853" s="3"/>
     </row>
-    <row r="854" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="854">
       <c r="A854" s="3"/>
       <c r="B854" s="3"/>
       <c r="C854" s="3"/>
@@ -26028,7 +26080,7 @@
       <c r="Z854" s="3"/>
       <c r="AA854" s="3"/>
     </row>
-    <row r="855" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="855">
       <c r="A855" s="3"/>
       <c r="B855" s="3"/>
       <c r="C855" s="3"/>
@@ -26057,7 +26109,7 @@
       <c r="Z855" s="3"/>
       <c r="AA855" s="3"/>
     </row>
-    <row r="856" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="856">
       <c r="A856" s="3"/>
       <c r="B856" s="3"/>
       <c r="C856" s="3"/>
@@ -26086,7 +26138,7 @@
       <c r="Z856" s="3"/>
       <c r="AA856" s="3"/>
     </row>
-    <row r="857" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="857">
       <c r="A857" s="3"/>
       <c r="B857" s="3"/>
       <c r="C857" s="3"/>
@@ -26115,7 +26167,7 @@
       <c r="Z857" s="3"/>
       <c r="AA857" s="3"/>
     </row>
-    <row r="858" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="858">
       <c r="A858" s="3"/>
       <c r="B858" s="3"/>
       <c r="C858" s="3"/>
@@ -26144,7 +26196,7 @@
       <c r="Z858" s="3"/>
       <c r="AA858" s="3"/>
     </row>
-    <row r="859" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="859">
       <c r="A859" s="3"/>
       <c r="B859" s="3"/>
       <c r="C859" s="3"/>
@@ -26173,7 +26225,7 @@
       <c r="Z859" s="3"/>
       <c r="AA859" s="3"/>
     </row>
-    <row r="860" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="860">
       <c r="A860" s="3"/>
       <c r="B860" s="3"/>
       <c r="C860" s="3"/>
@@ -26202,7 +26254,7 @@
       <c r="Z860" s="3"/>
       <c r="AA860" s="3"/>
     </row>
-    <row r="861" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="861">
       <c r="A861" s="3"/>
       <c r="B861" s="3"/>
       <c r="C861" s="3"/>
@@ -26231,7 +26283,7 @@
       <c r="Z861" s="3"/>
       <c r="AA861" s="3"/>
     </row>
-    <row r="862" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="862">
       <c r="A862" s="3"/>
       <c r="B862" s="3"/>
       <c r="C862" s="3"/>
@@ -26260,7 +26312,7 @@
       <c r="Z862" s="3"/>
       <c r="AA862" s="3"/>
     </row>
-    <row r="863" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="863">
       <c r="A863" s="3"/>
       <c r="B863" s="3"/>
       <c r="C863" s="3"/>
@@ -26289,7 +26341,7 @@
       <c r="Z863" s="3"/>
       <c r="AA863" s="3"/>
     </row>
-    <row r="864" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="864">
       <c r="A864" s="3"/>
       <c r="B864" s="3"/>
       <c r="C864" s="3"/>
@@ -26318,7 +26370,7 @@
       <c r="Z864" s="3"/>
       <c r="AA864" s="3"/>
     </row>
-    <row r="865" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="865">
       <c r="A865" s="3"/>
       <c r="B865" s="3"/>
       <c r="C865" s="3"/>
@@ -26347,7 +26399,7 @@
       <c r="Z865" s="3"/>
       <c r="AA865" s="3"/>
     </row>
-    <row r="866" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="866">
       <c r="A866" s="3"/>
       <c r="B866" s="3"/>
       <c r="C866" s="3"/>
@@ -26376,7 +26428,7 @@
       <c r="Z866" s="3"/>
       <c r="AA866" s="3"/>
     </row>
-    <row r="867" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="867">
       <c r="A867" s="3"/>
       <c r="B867" s="3"/>
       <c r="C867" s="3"/>
@@ -26405,7 +26457,7 @@
       <c r="Z867" s="3"/>
       <c r="AA867" s="3"/>
     </row>
-    <row r="868" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="868">
       <c r="A868" s="3"/>
       <c r="B868" s="3"/>
       <c r="C868" s="3"/>
@@ -26434,7 +26486,7 @@
       <c r="Z868" s="3"/>
       <c r="AA868" s="3"/>
     </row>
-    <row r="869" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="869">
       <c r="A869" s="3"/>
       <c r="B869" s="3"/>
       <c r="C869" s="3"/>
@@ -26463,7 +26515,7 @@
       <c r="Z869" s="3"/>
       <c r="AA869" s="3"/>
     </row>
-    <row r="870" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="870">
       <c r="A870" s="3"/>
       <c r="B870" s="3"/>
       <c r="C870" s="3"/>
@@ -26492,7 +26544,7 @@
       <c r="Z870" s="3"/>
       <c r="AA870" s="3"/>
     </row>
-    <row r="871" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="871">
       <c r="A871" s="3"/>
       <c r="B871" s="3"/>
       <c r="C871" s="3"/>
@@ -26521,7 +26573,7 @@
       <c r="Z871" s="3"/>
       <c r="AA871" s="3"/>
     </row>
-    <row r="872" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="872">
       <c r="A872" s="3"/>
       <c r="B872" s="3"/>
       <c r="C872" s="3"/>
@@ -26550,7 +26602,7 @@
       <c r="Z872" s="3"/>
       <c r="AA872" s="3"/>
     </row>
-    <row r="873" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="873">
       <c r="A873" s="3"/>
       <c r="B873" s="3"/>
       <c r="C873" s="3"/>
@@ -26579,7 +26631,7 @@
       <c r="Z873" s="3"/>
       <c r="AA873" s="3"/>
     </row>
-    <row r="874" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="874">
       <c r="A874" s="3"/>
       <c r="B874" s="3"/>
       <c r="C874" s="3"/>
@@ -26608,7 +26660,7 @@
       <c r="Z874" s="3"/>
       <c r="AA874" s="3"/>
     </row>
-    <row r="875" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="875">
       <c r="A875" s="3"/>
       <c r="B875" s="3"/>
       <c r="C875" s="3"/>
@@ -26637,7 +26689,7 @@
       <c r="Z875" s="3"/>
       <c r="AA875" s="3"/>
     </row>
-    <row r="876" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="876">
       <c r="A876" s="3"/>
       <c r="B876" s="3"/>
       <c r="C876" s="3"/>
@@ -26666,7 +26718,7 @@
       <c r="Z876" s="3"/>
       <c r="AA876" s="3"/>
     </row>
-    <row r="877" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="877">
       <c r="A877" s="3"/>
       <c r="B877" s="3"/>
       <c r="C877" s="3"/>
@@ -26695,7 +26747,7 @@
       <c r="Z877" s="3"/>
       <c r="AA877" s="3"/>
     </row>
-    <row r="878" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="878">
       <c r="A878" s="3"/>
       <c r="B878" s="3"/>
       <c r="C878" s="3"/>
@@ -26724,7 +26776,7 @@
       <c r="Z878" s="3"/>
       <c r="AA878" s="3"/>
     </row>
-    <row r="879" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="879">
       <c r="A879" s="3"/>
       <c r="B879" s="3"/>
       <c r="C879" s="3"/>
@@ -26753,7 +26805,7 @@
       <c r="Z879" s="3"/>
       <c r="AA879" s="3"/>
     </row>
-    <row r="880" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="880">
       <c r="A880" s="3"/>
       <c r="B880" s="3"/>
       <c r="C880" s="3"/>
@@ -26782,7 +26834,7 @@
       <c r="Z880" s="3"/>
       <c r="AA880" s="3"/>
     </row>
-    <row r="881" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="881">
       <c r="A881" s="3"/>
       <c r="B881" s="3"/>
       <c r="C881" s="3"/>
@@ -26811,7 +26863,7 @@
       <c r="Z881" s="3"/>
       <c r="AA881" s="3"/>
     </row>
-    <row r="882" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="882">
       <c r="A882" s="3"/>
       <c r="B882" s="3"/>
       <c r="C882" s="3"/>
@@ -26840,7 +26892,7 @@
       <c r="Z882" s="3"/>
       <c r="AA882" s="3"/>
     </row>
-    <row r="883" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="883">
       <c r="A883" s="3"/>
       <c r="B883" s="3"/>
       <c r="C883" s="3"/>
@@ -26869,7 +26921,7 @@
       <c r="Z883" s="3"/>
       <c r="AA883" s="3"/>
     </row>
-    <row r="884" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="884">
       <c r="A884" s="3"/>
       <c r="B884" s="3"/>
       <c r="C884" s="3"/>
@@ -26898,7 +26950,7 @@
       <c r="Z884" s="3"/>
       <c r="AA884" s="3"/>
     </row>
-    <row r="885" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="885">
       <c r="A885" s="3"/>
       <c r="B885" s="3"/>
       <c r="C885" s="3"/>
@@ -26927,7 +26979,7 @@
       <c r="Z885" s="3"/>
       <c r="AA885" s="3"/>
     </row>
-    <row r="886" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="886">
       <c r="A886" s="3"/>
       <c r="B886" s="3"/>
       <c r="C886" s="3"/>
@@ -26956,7 +27008,7 @@
       <c r="Z886" s="3"/>
       <c r="AA886" s="3"/>
     </row>
-    <row r="887" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="887">
       <c r="A887" s="3"/>
       <c r="B887" s="3"/>
       <c r="C887" s="3"/>
@@ -26985,7 +27037,7 @@
       <c r="Z887" s="3"/>
       <c r="AA887" s="3"/>
     </row>
-    <row r="888" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="888">
       <c r="A888" s="3"/>
       <c r="B888" s="3"/>
       <c r="C888" s="3"/>
@@ -27014,7 +27066,7 @@
       <c r="Z888" s="3"/>
       <c r="AA888" s="3"/>
     </row>
-    <row r="889" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="889">
       <c r="A889" s="3"/>
       <c r="B889" s="3"/>
       <c r="C889" s="3"/>
@@ -27043,7 +27095,7 @@
       <c r="Z889" s="3"/>
       <c r="AA889" s="3"/>
     </row>
-    <row r="890" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="890">
       <c r="A890" s="3"/>
       <c r="B890" s="3"/>
       <c r="C890" s="3"/>
@@ -27072,7 +27124,7 @@
       <c r="Z890" s="3"/>
       <c r="AA890" s="3"/>
     </row>
-    <row r="891" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="891">
       <c r="A891" s="3"/>
       <c r="B891" s="3"/>
       <c r="C891" s="3"/>
@@ -27101,7 +27153,7 @@
       <c r="Z891" s="3"/>
       <c r="AA891" s="3"/>
     </row>
-    <row r="892" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="892">
       <c r="A892" s="3"/>
       <c r="B892" s="3"/>
       <c r="C892" s="3"/>
@@ -27130,7 +27182,7 @@
       <c r="Z892" s="3"/>
       <c r="AA892" s="3"/>
     </row>
-    <row r="893" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="893">
       <c r="A893" s="3"/>
       <c r="B893" s="3"/>
       <c r="C893" s="3"/>
@@ -27159,7 +27211,7 @@
       <c r="Z893" s="3"/>
       <c r="AA893" s="3"/>
     </row>
-    <row r="894" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="894">
       <c r="A894" s="3"/>
       <c r="B894" s="3"/>
       <c r="C894" s="3"/>
@@ -27188,7 +27240,7 @@
       <c r="Z894" s="3"/>
       <c r="AA894" s="3"/>
     </row>
-    <row r="895" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="895">
       <c r="A895" s="3"/>
       <c r="B895" s="3"/>
       <c r="C895" s="3"/>
@@ -27217,7 +27269,7 @@
       <c r="Z895" s="3"/>
       <c r="AA895" s="3"/>
     </row>
-    <row r="896" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="896">
       <c r="A896" s="3"/>
       <c r="B896" s="3"/>
       <c r="C896" s="3"/>
@@ -27246,7 +27298,7 @@
       <c r="Z896" s="3"/>
       <c r="AA896" s="3"/>
     </row>
-    <row r="897" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="897">
       <c r="A897" s="3"/>
       <c r="B897" s="3"/>
       <c r="C897" s="3"/>
@@ -27275,7 +27327,7 @@
       <c r="Z897" s="3"/>
       <c r="AA897" s="3"/>
     </row>
-    <row r="898" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="898">
       <c r="A898" s="3"/>
       <c r="B898" s="3"/>
       <c r="C898" s="3"/>
@@ -27304,7 +27356,7 @@
       <c r="Z898" s="3"/>
       <c r="AA898" s="3"/>
     </row>
-    <row r="899" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="899">
       <c r="A899" s="3"/>
       <c r="B899" s="3"/>
       <c r="C899" s="3"/>
@@ -27333,7 +27385,7 @@
       <c r="Z899" s="3"/>
       <c r="AA899" s="3"/>
     </row>
-    <row r="900" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="900">
       <c r="A900" s="3"/>
       <c r="B900" s="3"/>
       <c r="C900" s="3"/>
@@ -27362,7 +27414,7 @@
       <c r="Z900" s="3"/>
       <c r="AA900" s="3"/>
     </row>
-    <row r="901" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="901">
       <c r="A901" s="3"/>
       <c r="B901" s="3"/>
       <c r="C901" s="3"/>
@@ -27391,7 +27443,7 @@
       <c r="Z901" s="3"/>
       <c r="AA901" s="3"/>
     </row>
-    <row r="902" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="902">
       <c r="A902" s="3"/>
       <c r="B902" s="3"/>
       <c r="C902" s="3"/>
@@ -27420,7 +27472,7 @@
       <c r="Z902" s="3"/>
       <c r="AA902" s="3"/>
     </row>
-    <row r="903" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="903">
       <c r="A903" s="3"/>
       <c r="B903" s="3"/>
       <c r="C903" s="3"/>
@@ -27449,7 +27501,7 @@
       <c r="Z903" s="3"/>
       <c r="AA903" s="3"/>
     </row>
-    <row r="904" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="904">
       <c r="A904" s="3"/>
       <c r="B904" s="3"/>
       <c r="C904" s="3"/>
@@ -27478,7 +27530,7 @@
       <c r="Z904" s="3"/>
       <c r="AA904" s="3"/>
     </row>
-    <row r="905" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="905">
       <c r="A905" s="3"/>
       <c r="B905" s="3"/>
       <c r="C905" s="3"/>
@@ -27507,7 +27559,7 @@
       <c r="Z905" s="3"/>
       <c r="AA905" s="3"/>
     </row>
-    <row r="906" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="906">
       <c r="A906" s="3"/>
       <c r="B906" s="3"/>
       <c r="C906" s="3"/>
@@ -27536,7 +27588,7 @@
       <c r="Z906" s="3"/>
       <c r="AA906" s="3"/>
     </row>
-    <row r="907" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="907">
       <c r="A907" s="3"/>
       <c r="B907" s="3"/>
       <c r="C907" s="3"/>
@@ -27565,7 +27617,7 @@
       <c r="Z907" s="3"/>
       <c r="AA907" s="3"/>
     </row>
-    <row r="908" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="908">
       <c r="A908" s="3"/>
       <c r="B908" s="3"/>
       <c r="C908" s="3"/>
@@ -27594,7 +27646,7 @@
       <c r="Z908" s="3"/>
       <c r="AA908" s="3"/>
     </row>
-    <row r="909" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="909">
       <c r="A909" s="3"/>
       <c r="B909" s="3"/>
       <c r="C909" s="3"/>
@@ -27623,7 +27675,7 @@
       <c r="Z909" s="3"/>
       <c r="AA909" s="3"/>
     </row>
-    <row r="910" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="910">
       <c r="A910" s="3"/>
       <c r="B910" s="3"/>
       <c r="C910" s="3"/>
@@ -27652,7 +27704,7 @@
       <c r="Z910" s="3"/>
       <c r="AA910" s="3"/>
     </row>
-    <row r="911" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="911">
       <c r="A911" s="3"/>
       <c r="B911" s="3"/>
       <c r="C911" s="3"/>
@@ -27681,7 +27733,7 @@
       <c r="Z911" s="3"/>
       <c r="AA911" s="3"/>
     </row>
-    <row r="912" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="912">
       <c r="A912" s="3"/>
       <c r="B912" s="3"/>
       <c r="C912" s="3"/>
@@ -27710,7 +27762,7 @@
       <c r="Z912" s="3"/>
       <c r="AA912" s="3"/>
     </row>
-    <row r="913" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="913">
       <c r="A913" s="3"/>
       <c r="B913" s="3"/>
       <c r="C913" s="3"/>
@@ -27739,7 +27791,7 @@
       <c r="Z913" s="3"/>
       <c r="AA913" s="3"/>
     </row>
-    <row r="914" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="914">
       <c r="A914" s="3"/>
       <c r="B914" s="3"/>
       <c r="C914" s="3"/>
@@ -27768,7 +27820,7 @@
       <c r="Z914" s="3"/>
       <c r="AA914" s="3"/>
     </row>
-    <row r="915" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="915">
       <c r="A915" s="3"/>
       <c r="B915" s="3"/>
       <c r="C915" s="3"/>
@@ -27797,7 +27849,7 @@
       <c r="Z915" s="3"/>
       <c r="AA915" s="3"/>
     </row>
-    <row r="916" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="916">
       <c r="A916" s="3"/>
       <c r="B916" s="3"/>
       <c r="C916" s="3"/>
@@ -27826,7 +27878,7 @@
       <c r="Z916" s="3"/>
       <c r="AA916" s="3"/>
     </row>
-    <row r="917" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="917">
       <c r="A917" s="3"/>
       <c r="B917" s="3"/>
       <c r="C917" s="3"/>
@@ -27855,7 +27907,7 @@
       <c r="Z917" s="3"/>
       <c r="AA917" s="3"/>
     </row>
-    <row r="918" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="918">
       <c r="A918" s="3"/>
       <c r="B918" s="3"/>
       <c r="C918" s="3"/>
@@ -27884,7 +27936,7 @@
       <c r="Z918" s="3"/>
       <c r="AA918" s="3"/>
     </row>
-    <row r="919" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="919">
       <c r="A919" s="3"/>
       <c r="B919" s="3"/>
       <c r="C919" s="3"/>
@@ -27913,7 +27965,7 @@
       <c r="Z919" s="3"/>
       <c r="AA919" s="3"/>
     </row>
-    <row r="920" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="920">
       <c r="A920" s="3"/>
       <c r="B920" s="3"/>
       <c r="C920" s="3"/>
@@ -27942,7 +27994,7 @@
       <c r="Z920" s="3"/>
       <c r="AA920" s="3"/>
     </row>
-    <row r="921" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="921">
       <c r="A921" s="3"/>
       <c r="B921" s="3"/>
       <c r="C921" s="3"/>
@@ -27971,7 +28023,7 @@
       <c r="Z921" s="3"/>
       <c r="AA921" s="3"/>
     </row>
-    <row r="922" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="922">
       <c r="A922" s="3"/>
       <c r="B922" s="3"/>
       <c r="C922" s="3"/>
@@ -28000,7 +28052,7 @@
       <c r="Z922" s="3"/>
       <c r="AA922" s="3"/>
     </row>
-    <row r="923" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="923">
       <c r="A923" s="3"/>
       <c r="B923" s="3"/>
       <c r="C923" s="3"/>
@@ -28029,7 +28081,7 @@
       <c r="Z923" s="3"/>
       <c r="AA923" s="3"/>
     </row>
-    <row r="924" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="924">
       <c r="A924" s="3"/>
       <c r="B924" s="3"/>
       <c r="C924" s="3"/>
@@ -28058,7 +28110,7 @@
       <c r="Z924" s="3"/>
       <c r="AA924" s="3"/>
     </row>
-    <row r="925" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="925">
       <c r="A925" s="3"/>
       <c r="B925" s="3"/>
       <c r="C925" s="3"/>
@@ -28087,7 +28139,7 @@
       <c r="Z925" s="3"/>
       <c r="AA925" s="3"/>
     </row>
-    <row r="926" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="926">
       <c r="A926" s="3"/>
       <c r="B926" s="3"/>
       <c r="C926" s="3"/>
@@ -28116,7 +28168,7 @@
       <c r="Z926" s="3"/>
       <c r="AA926" s="3"/>
     </row>
-    <row r="927" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="927">
       <c r="A927" s="3"/>
       <c r="B927" s="3"/>
       <c r="C927" s="3"/>
@@ -28145,7 +28197,7 @@
       <c r="Z927" s="3"/>
       <c r="AA927" s="3"/>
     </row>
-    <row r="928" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="928">
       <c r="A928" s="3"/>
       <c r="B928" s="3"/>
       <c r="C928" s="3"/>
@@ -28174,7 +28226,7 @@
       <c r="Z928" s="3"/>
       <c r="AA928" s="3"/>
     </row>
-    <row r="929" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="929">
       <c r="A929" s="3"/>
       <c r="B929" s="3"/>
       <c r="C929" s="3"/>
@@ -28203,7 +28255,7 @@
       <c r="Z929" s="3"/>
       <c r="AA929" s="3"/>
     </row>
-    <row r="930" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="930">
       <c r="A930" s="3"/>
       <c r="B930" s="3"/>
       <c r="C930" s="3"/>
@@ -28232,7 +28284,7 @@
       <c r="Z930" s="3"/>
       <c r="AA930" s="3"/>
     </row>
-    <row r="931" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="931">
       <c r="A931" s="3"/>
       <c r="B931" s="3"/>
       <c r="C931" s="3"/>
@@ -28261,7 +28313,7 @@
       <c r="Z931" s="3"/>
       <c r="AA931" s="3"/>
     </row>
-    <row r="932" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="932">
       <c r="A932" s="3"/>
       <c r="B932" s="3"/>
       <c r="C932" s="3"/>
@@ -28290,7 +28342,7 @@
       <c r="Z932" s="3"/>
       <c r="AA932" s="3"/>
     </row>
-    <row r="933" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="933">
       <c r="A933" s="3"/>
       <c r="B933" s="3"/>
       <c r="C933" s="3"/>
@@ -28319,7 +28371,7 @@
       <c r="Z933" s="3"/>
       <c r="AA933" s="3"/>
     </row>
-    <row r="934" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="934">
       <c r="A934" s="3"/>
       <c r="B934" s="3"/>
       <c r="C934" s="3"/>
@@ -28348,7 +28400,7 @@
       <c r="Z934" s="3"/>
       <c r="AA934" s="3"/>
     </row>
-    <row r="935" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="935">
       <c r="A935" s="3"/>
       <c r="B935" s="3"/>
       <c r="C935" s="3"/>
@@ -28377,7 +28429,7 @@
       <c r="Z935" s="3"/>
       <c r="AA935" s="3"/>
     </row>
-    <row r="936" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="936">
       <c r="A936" s="3"/>
       <c r="B936" s="3"/>
       <c r="C936" s="3"/>
@@ -28406,7 +28458,7 @@
       <c r="Z936" s="3"/>
       <c r="AA936" s="3"/>
     </row>
-    <row r="937" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="937">
       <c r="A937" s="3"/>
       <c r="B937" s="3"/>
       <c r="C937" s="3"/>
@@ -28435,7 +28487,7 @@
       <c r="Z937" s="3"/>
       <c r="AA937" s="3"/>
     </row>
-    <row r="938" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="938">
       <c r="A938" s="3"/>
       <c r="B938" s="3"/>
       <c r="C938" s="3"/>
@@ -28464,7 +28516,7 @@
       <c r="Z938" s="3"/>
       <c r="AA938" s="3"/>
     </row>
-    <row r="939" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="939">
       <c r="A939" s="3"/>
       <c r="B939" s="3"/>
       <c r="C939" s="3"/>
@@ -28493,7 +28545,7 @@
       <c r="Z939" s="3"/>
       <c r="AA939" s="3"/>
     </row>
-    <row r="940" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="940">
       <c r="A940" s="3"/>
       <c r="B940" s="3"/>
       <c r="C940" s="3"/>
@@ -28522,7 +28574,7 @@
       <c r="Z940" s="3"/>
       <c r="AA940" s="3"/>
     </row>
-    <row r="941" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="941">
       <c r="A941" s="3"/>
       <c r="B941" s="3"/>
       <c r="C941" s="3"/>
@@ -28551,7 +28603,7 @@
       <c r="Z941" s="3"/>
       <c r="AA941" s="3"/>
     </row>
-    <row r="942" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="942">
       <c r="A942" s="3"/>
       <c r="B942" s="3"/>
       <c r="C942" s="3"/>
@@ -28580,7 +28632,7 @@
       <c r="Z942" s="3"/>
       <c r="AA942" s="3"/>
     </row>
-    <row r="943" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="943">
       <c r="A943" s="3"/>
       <c r="B943" s="3"/>
       <c r="C943" s="3"/>
@@ -28609,7 +28661,7 @@
       <c r="Z943" s="3"/>
       <c r="AA943" s="3"/>
     </row>
-    <row r="944" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="944">
       <c r="A944" s="3"/>
       <c r="B944" s="3"/>
       <c r="C944" s="3"/>
@@ -28638,7 +28690,7 @@
       <c r="Z944" s="3"/>
       <c r="AA944" s="3"/>
     </row>
-    <row r="945" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="945">
       <c r="A945" s="3"/>
       <c r="B945" s="3"/>
       <c r="C945" s="3"/>
@@ -28667,7 +28719,7 @@
       <c r="Z945" s="3"/>
       <c r="AA945" s="3"/>
     </row>
-    <row r="946" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="946">
       <c r="A946" s="3"/>
       <c r="B946" s="3"/>
       <c r="C946" s="3"/>
@@ -28696,7 +28748,7 @@
       <c r="Z946" s="3"/>
       <c r="AA946" s="3"/>
     </row>
-    <row r="947" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="947">
       <c r="A947" s="3"/>
       <c r="B947" s="3"/>
       <c r="C947" s="3"/>
@@ -28725,7 +28777,7 @@
       <c r="Z947" s="3"/>
       <c r="AA947" s="3"/>
     </row>
-    <row r="948" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="948">
       <c r="A948" s="3"/>
       <c r="B948" s="3"/>
       <c r="C948" s="3"/>
@@ -28754,7 +28806,7 @@
       <c r="Z948" s="3"/>
       <c r="AA948" s="3"/>
     </row>
-    <row r="949" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="949">
       <c r="A949" s="3"/>
       <c r="B949" s="3"/>
       <c r="C949" s="3"/>
@@ -28783,7 +28835,7 @@
       <c r="Z949" s="3"/>
       <c r="AA949" s="3"/>
     </row>
-    <row r="950" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="950">
       <c r="A950" s="3"/>
       <c r="B950" s="3"/>
       <c r="C950" s="3"/>
@@ -28812,7 +28864,7 @@
       <c r="Z950" s="3"/>
       <c r="AA950" s="3"/>
     </row>
-    <row r="951" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="951">
       <c r="A951" s="3"/>
       <c r="B951" s="3"/>
       <c r="C951" s="3"/>
@@ -28841,7 +28893,7 @@
       <c r="Z951" s="3"/>
       <c r="AA951" s="3"/>
     </row>
-    <row r="952" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="952">
       <c r="A952" s="3"/>
       <c r="B952" s="3"/>
       <c r="C952" s="3"/>
@@ -28870,7 +28922,7 @@
       <c r="Z952" s="3"/>
       <c r="AA952" s="3"/>
     </row>
-    <row r="953" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="953">
       <c r="A953" s="3"/>
       <c r="B953" s="3"/>
       <c r="C953" s="3"/>
@@ -28899,7 +28951,7 @@
       <c r="Z953" s="3"/>
       <c r="AA953" s="3"/>
     </row>
-    <row r="954" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="954">
       <c r="A954" s="3"/>
       <c r="B954" s="3"/>
       <c r="C954" s="3"/>
@@ -28928,7 +28980,7 @@
       <c r="Z954" s="3"/>
       <c r="AA954" s="3"/>
     </row>
-    <row r="955" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="955">
       <c r="A955" s="3"/>
       <c r="B955" s="3"/>
       <c r="C955" s="3"/>
@@ -28957,7 +29009,7 @@
       <c r="Z955" s="3"/>
       <c r="AA955" s="3"/>
     </row>
-    <row r="956" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="956">
       <c r="A956" s="3"/>
       <c r="B956" s="3"/>
       <c r="C956" s="3"/>
@@ -28986,7 +29038,7 @@
       <c r="Z956" s="3"/>
       <c r="AA956" s="3"/>
     </row>
-    <row r="957" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="957">
       <c r="A957" s="3"/>
       <c r="B957" s="3"/>
       <c r="C957" s="3"/>
@@ -29015,7 +29067,7 @@
       <c r="Z957" s="3"/>
       <c r="AA957" s="3"/>
     </row>
-    <row r="958" spans="1:27" ht="17.5" x14ac:dyDescent="0.35">
+    <row r="958">
       <c r="A958" s="3"/>
       <c r="B958" s="3"/>
       <c r="C958" s="3"/>
@@ -29045,7 +29097,6 @@
       <c r="AA958" s="3"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Week_8/Capstone Timesheet_Ripal Patel.xlsx
+++ b/Week_8/Capstone Timesheet_Ripal Patel.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="77">
   <si>
     <t>Week_1</t>
   </si>
@@ -237,6 +237,12 @@
   <si>
     <t>Create Contact US Page UI</t>
   </si>
+  <si>
+    <t>Solve Error for find doctor Page + create Doctor Profile pages for 5 Doctors</t>
+  </si>
+  <si>
+    <t>Services Page UI Connect with Services page and department pages (Controller + model)</t>
+  </si>
 </sst>
 </file>
 
@@ -389,7 +395,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="80">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -609,7 +615,15 @@
     <xf borderId="1" fillId="9" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="9" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="9" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -828,7 +842,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="10.0"/>
-    <col customWidth="1" min="2" max="2" width="62.25"/>
+    <col customWidth="1" min="2" max="2" width="67.5"/>
     <col customWidth="1" min="3" max="3" width="12.25"/>
     <col customWidth="1" min="4" max="4" width="12.13"/>
   </cols>
@@ -4153,9 +4167,15 @@
     </row>
     <row r="99">
       <c r="A99" s="74"/>
-      <c r="B99" s="76"/>
-      <c r="C99" s="71"/>
-      <c r="D99" s="75"/>
+      <c r="B99" s="76" t="s">
+        <v>75</v>
+      </c>
+      <c r="C99" s="73">
+        <v>46089.0</v>
+      </c>
+      <c r="D99" s="75">
+        <v>3.75</v>
+      </c>
       <c r="E99" s="3"/>
       <c r="F99" s="3"/>
       <c r="G99" s="3"/>
@@ -4181,10 +4201,16 @@
       <c r="AA99" s="3"/>
     </row>
     <row r="100">
-      <c r="A100" s="77"/>
-      <c r="B100" s="77"/>
-      <c r="C100" s="77"/>
-      <c r="D100" s="77"/>
+      <c r="A100" s="74"/>
+      <c r="B100" s="76" t="s">
+        <v>76</v>
+      </c>
+      <c r="C100" s="73">
+        <v>46089.0</v>
+      </c>
+      <c r="D100" s="75">
+        <v>4.15</v>
+      </c>
       <c r="E100" s="3"/>
       <c r="F100" s="3"/>
       <c r="G100" s="3"/>
@@ -4210,15 +4236,10 @@
       <c r="AA100" s="3"/>
     </row>
     <row r="101">
-      <c r="A101" s="45"/>
-      <c r="B101" s="46" t="s">
-        <v>15</v>
-      </c>
+      <c r="A101" s="77"/>
+      <c r="B101" s="78"/>
       <c r="C101" s="47"/>
-      <c r="D101" s="41">
-        <f>sum(D91:D96)</f>
-        <v>12.9</v>
-      </c>
+      <c r="D101" s="79"/>
       <c r="E101" s="3"/>
       <c r="F101" s="3"/>
       <c r="G101" s="3"/>
@@ -4244,10 +4265,15 @@
       <c r="AA101" s="3"/>
     </row>
     <row r="102">
-      <c r="A102" s="3"/>
-      <c r="B102" s="3"/>
-      <c r="C102" s="3"/>
-      <c r="D102" s="3"/>
+      <c r="A102" s="45"/>
+      <c r="B102" s="46" t="s">
+        <v>15</v>
+      </c>
+      <c r="C102" s="47"/>
+      <c r="D102" s="41">
+        <f>sum(D91:D100)</f>
+        <v>22.7</v>
+      </c>
       <c r="E102" s="3"/>
       <c r="F102" s="3"/>
       <c r="G102" s="3"/>
@@ -29096,6 +29122,35 @@
       <c r="Z958" s="3"/>
       <c r="AA958" s="3"/>
     </row>
+    <row r="959">
+      <c r="A959" s="3"/>
+      <c r="B959" s="3"/>
+      <c r="C959" s="3"/>
+      <c r="D959" s="3"/>
+      <c r="E959" s="3"/>
+      <c r="F959" s="3"/>
+      <c r="G959" s="3"/>
+      <c r="H959" s="3"/>
+      <c r="I959" s="3"/>
+      <c r="J959" s="3"/>
+      <c r="K959" s="3"/>
+      <c r="L959" s="3"/>
+      <c r="M959" s="3"/>
+      <c r="N959" s="3"/>
+      <c r="O959" s="3"/>
+      <c r="P959" s="3"/>
+      <c r="Q959" s="3"/>
+      <c r="R959" s="3"/>
+      <c r="S959" s="3"/>
+      <c r="T959" s="3"/>
+      <c r="U959" s="3"/>
+      <c r="V959" s="3"/>
+      <c r="W959" s="3"/>
+      <c r="X959" s="3"/>
+      <c r="Y959" s="3"/>
+      <c r="Z959" s="3"/>
+      <c r="AA959" s="3"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Week_8/Capstone Timesheet_Ripal Patel.xlsx
+++ b/Week_8/Capstone Timesheet_Ripal Patel.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="80">
   <si>
     <t>Week_1</t>
   </si>
@@ -243,6 +243,15 @@
   <si>
     <t>Services Page UI Connect with Services page and department pages (Controller + model)</t>
   </si>
+  <si>
+    <t>Implement Book Appointment Form functionality (Controller + Model + Route)</t>
+  </si>
+  <si>
+    <t>Create Appointments Database Table and connect form to MySQL</t>
+  </si>
+  <si>
+    <t>Improve Book Appointment UI and form validation</t>
+  </si>
 </sst>
 </file>
 
@@ -395,7 +404,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="78">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -615,14 +624,8 @@
     <xf borderId="1" fillId="9" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="9" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf borderId="1" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -842,7 +845,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="10.0"/>
-    <col customWidth="1" min="2" max="2" width="67.5"/>
+    <col customWidth="1" min="2" max="2" width="80.63"/>
     <col customWidth="1" min="3" max="3" width="12.25"/>
     <col customWidth="1" min="4" max="4" width="12.13"/>
   </cols>
@@ -4236,10 +4239,16 @@
       <c r="AA100" s="3"/>
     </row>
     <row r="101">
-      <c r="A101" s="77"/>
-      <c r="B101" s="78"/>
-      <c r="C101" s="47"/>
-      <c r="D101" s="79"/>
+      <c r="A101" s="45"/>
+      <c r="B101" s="72" t="s">
+        <v>77</v>
+      </c>
+      <c r="C101" s="73">
+        <v>46090.0</v>
+      </c>
+      <c r="D101" s="77">
+        <v>2.25</v>
+      </c>
       <c r="E101" s="3"/>
       <c r="F101" s="3"/>
       <c r="G101" s="3"/>
@@ -4266,13 +4275,14 @@
     </row>
     <row r="102">
       <c r="A102" s="45"/>
-      <c r="B102" s="46" t="s">
-        <v>15</v>
+      <c r="B102" s="72" t="s">
+        <v>78</v>
       </c>
-      <c r="C102" s="47"/>
-      <c r="D102" s="41">
-        <f>sum(D91:D100)</f>
-        <v>22.7</v>
+      <c r="C102" s="73">
+        <v>46090.0</v>
+      </c>
+      <c r="D102" s="77">
+        <v>1.75</v>
       </c>
       <c r="E102" s="3"/>
       <c r="F102" s="3"/>
@@ -4299,10 +4309,16 @@
       <c r="AA102" s="3"/>
     </row>
     <row r="103">
-      <c r="A103" s="3"/>
-      <c r="B103" s="3"/>
-      <c r="C103" s="3"/>
-      <c r="D103" s="3"/>
+      <c r="A103" s="45"/>
+      <c r="B103" s="72" t="s">
+        <v>79</v>
+      </c>
+      <c r="C103" s="73">
+        <v>46090.0</v>
+      </c>
+      <c r="D103" s="77">
+        <v>1.0</v>
+      </c>
       <c r="E103" s="3"/>
       <c r="F103" s="3"/>
       <c r="G103" s="3"/>
@@ -4328,10 +4344,15 @@
       <c r="AA103" s="3"/>
     </row>
     <row r="104">
-      <c r="A104" s="3"/>
-      <c r="B104" s="3"/>
-      <c r="C104" s="3"/>
-      <c r="D104" s="3"/>
+      <c r="A104" s="45"/>
+      <c r="B104" s="46" t="s">
+        <v>15</v>
+      </c>
+      <c r="C104" s="47"/>
+      <c r="D104" s="41">
+        <f>sum(D91:D103)</f>
+        <v>27.7</v>
+      </c>
       <c r="E104" s="3"/>
       <c r="F104" s="3"/>
       <c r="G104" s="3"/>
@@ -29151,6 +29172,64 @@
       <c r="Z959" s="3"/>
       <c r="AA959" s="3"/>
     </row>
+    <row r="960">
+      <c r="A960" s="3"/>
+      <c r="B960" s="3"/>
+      <c r="C960" s="3"/>
+      <c r="D960" s="3"/>
+      <c r="E960" s="3"/>
+      <c r="F960" s="3"/>
+      <c r="G960" s="3"/>
+      <c r="H960" s="3"/>
+      <c r="I960" s="3"/>
+      <c r="J960" s="3"/>
+      <c r="K960" s="3"/>
+      <c r="L960" s="3"/>
+      <c r="M960" s="3"/>
+      <c r="N960" s="3"/>
+      <c r="O960" s="3"/>
+      <c r="P960" s="3"/>
+      <c r="Q960" s="3"/>
+      <c r="R960" s="3"/>
+      <c r="S960" s="3"/>
+      <c r="T960" s="3"/>
+      <c r="U960" s="3"/>
+      <c r="V960" s="3"/>
+      <c r="W960" s="3"/>
+      <c r="X960" s="3"/>
+      <c r="Y960" s="3"/>
+      <c r="Z960" s="3"/>
+      <c r="AA960" s="3"/>
+    </row>
+    <row r="961">
+      <c r="A961" s="3"/>
+      <c r="B961" s="3"/>
+      <c r="C961" s="3"/>
+      <c r="D961" s="3"/>
+      <c r="E961" s="3"/>
+      <c r="F961" s="3"/>
+      <c r="G961" s="3"/>
+      <c r="H961" s="3"/>
+      <c r="I961" s="3"/>
+      <c r="J961" s="3"/>
+      <c r="K961" s="3"/>
+      <c r="L961" s="3"/>
+      <c r="M961" s="3"/>
+      <c r="N961" s="3"/>
+      <c r="O961" s="3"/>
+      <c r="P961" s="3"/>
+      <c r="Q961" s="3"/>
+      <c r="R961" s="3"/>
+      <c r="S961" s="3"/>
+      <c r="T961" s="3"/>
+      <c r="U961" s="3"/>
+      <c r="V961" s="3"/>
+      <c r="W961" s="3"/>
+      <c r="X961" s="3"/>
+      <c r="Y961" s="3"/>
+      <c r="Z961" s="3"/>
+      <c r="AA961" s="3"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Week_8/Capstone Timesheet_Ripal Patel.xlsx
+++ b/Week_8/Capstone Timesheet_Ripal Patel.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="81">
   <si>
     <t>Week_1</t>
   </si>
@@ -251,6 +251,9 @@
   </si>
   <si>
     <t>Improve Book Appointment UI and form validation</t>
+  </si>
+  <si>
+    <t>Modified some Css &amp; Page in Portfolio</t>
   </si>
 </sst>
 </file>
@@ -4346,12 +4349,13 @@
     <row r="104">
       <c r="A104" s="45"/>
       <c r="B104" s="46" t="s">
-        <v>15</v>
+        <v>80</v>
       </c>
-      <c r="C104" s="47"/>
-      <c r="D104" s="41">
-        <f>sum(D91:D103)</f>
-        <v>27.7</v>
+      <c r="C104" s="73">
+        <v>46092.0</v>
+      </c>
+      <c r="D104" s="77">
+        <v>1.75</v>
       </c>
       <c r="E104" s="3"/>
       <c r="F104" s="3"/>
@@ -4378,10 +4382,15 @@
       <c r="AA104" s="3"/>
     </row>
     <row r="105">
-      <c r="A105" s="3"/>
-      <c r="B105" s="3"/>
-      <c r="C105" s="3"/>
-      <c r="D105" s="3"/>
+      <c r="A105" s="45"/>
+      <c r="B105" s="46" t="s">
+        <v>15</v>
+      </c>
+      <c r="C105" s="47"/>
+      <c r="D105" s="41">
+        <f>sum(D91:D104)</f>
+        <v>29.45</v>
+      </c>
       <c r="E105" s="3"/>
       <c r="F105" s="3"/>
       <c r="G105" s="3"/>
@@ -29230,6 +29239,35 @@
       <c r="Z961" s="3"/>
       <c r="AA961" s="3"/>
     </row>
+    <row r="962">
+      <c r="A962" s="3"/>
+      <c r="B962" s="3"/>
+      <c r="C962" s="3"/>
+      <c r="D962" s="3"/>
+      <c r="E962" s="3"/>
+      <c r="F962" s="3"/>
+      <c r="G962" s="3"/>
+      <c r="H962" s="3"/>
+      <c r="I962" s="3"/>
+      <c r="J962" s="3"/>
+      <c r="K962" s="3"/>
+      <c r="L962" s="3"/>
+      <c r="M962" s="3"/>
+      <c r="N962" s="3"/>
+      <c r="O962" s="3"/>
+      <c r="P962" s="3"/>
+      <c r="Q962" s="3"/>
+      <c r="R962" s="3"/>
+      <c r="S962" s="3"/>
+      <c r="T962" s="3"/>
+      <c r="U962" s="3"/>
+      <c r="V962" s="3"/>
+      <c r="W962" s="3"/>
+      <c r="X962" s="3"/>
+      <c r="Y962" s="3"/>
+      <c r="Z962" s="3"/>
+      <c r="AA962" s="3"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
